--- a/docs/deliverables/Femasys_Territory_Plan_v4.xlsx
+++ b/docs/deliverables/Femasys_Territory_Plan_v4.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="254">
   <si>
     <t xml:space="preserve">FemaSeed U.S. Territory Plan — v1 (Workload-Based Model)</t>
   </si>
@@ -138,6 +138,9 @@
     <t xml:space="preserve">V4 ADDENDUM — 'Kathy - ALL Universe' tab: per-territory view in Kathy's layout (columns E-P), ALL-MD universe. Counts sum Waterfall A rev1 labeled columns only. Reps is a live formula (ROUND(All MDs/300), min 1) that Kathy can overwrite; per-rep loads, Academic Share, Score, and Rank recalculate. Score uses Kathy's weights — All MDs/Rep 20% / All Clinics/Rep 60% / Women 25-44 10% / Median Income 10% / Education 0% — each component min-max normalized 0-100 across the 25 territories.</t>
   </si>
   <si>
+    <t xml:space="preserve">V4.1 — REP CAP CORRECTION (2026-07-22, per Rajiv): 28 reps is a HARD CAP; per-territory rep sizing (ROUND(All MDs/300)) and the largest-remainder 28-cap apportionment were removed as irrelevant. The Reps column on Territory Plan and the Kathy - ALL Universe tab now carry the original (v3) Territory Plan allocation — TX 3, CA-HI 2, all other territories 1 — totaling exactly 28, entered as adjustable inputs. At the ALL-MD universe this is ~657 MDs/rep on average; the plan functions as a prioritization model using the &gt;=10 (4,401) and &gt;=20 (1,476) tiers. Scoring, rankings, and hiring waves are unchanged by this correction (score does not depend on reps on the Territory Plan tab; the Kathy tab score, which weights per-rep loads, now reflects the 28-cap allocation).</t>
+  </si>
+  <si>
     <t xml:space="preserve">Target Universe Definition</t>
   </si>
   <si>
@@ -180,7 +183,7 @@
     <t xml:space="preserve">Volume &gt;=20</t>
   </si>
   <si>
-    <t xml:space="preserve">v3 note (retained): 'The &gt;=5 universe is the only definition where 28 reps lands inside the industry workload band.' v4 selects ALL prescribers per Megan/CEO direction; at 28 reps that is 657 HCPs/rep — far over band — so reps are sized per territory instead (see Territory Plan).</t>
+    <t xml:space="preserve">v3 note (retained): 'The &gt;=5 universe is the only definition where 28 reps lands inside the industry workload band.' v4 selects ALL prescribers per Megan/CEO direction. Rep count is a HARD CAP of 28 (~657 MDs/rep at this universe); the 'Reps @300/rep' column is scenario context only, not a staffing proposal. The 28 are allocated per the original Territory Plan (see Territory Plan tab).</t>
   </si>
   <si>
     <t xml:space="preserve">Source: Waterfall A rev1 (canonical). MDs = All MDs headline. NV Private All MDs derived as Total - Academic (source shows 304, inconsistent with its own totals; see Read Me).</t>
@@ -453,19 +456,13 @@
     <t xml:space="preserve">Anchor Markets</t>
   </si>
   <si>
-    <t xml:space="preserve">Reps Required (headline)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCPs per Rep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Band (275-325)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reps @28 Cap (largest remainder)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HCPs/Rep @28</t>
+    <t xml:space="preserve">Reps (28 cap, v3 allocation — ADJUSTABLE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDs per Rep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clinics per Rep</t>
   </si>
   <si>
     <t xml:space="preserve">Women 25-44 (v3)</t>
@@ -489,12 +486,6 @@
     <t xml:space="preserve">Hire Wave (v4)</t>
   </si>
   <si>
-    <t xml:space="preserve">LR Quota (helper)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LR Remainder (helper)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Houston, Dallas, Austin</t>
   </si>
   <si>
@@ -609,7 +600,7 @@
     <t xml:space="preserve">Greenville, Florence, Spartanburg</t>
   </si>
   <si>
-    <t xml:space="preserve">Reps Required = ROUND(All MDs/300), min 1 — headline staffing sized to the 275-325 HCPs/rep band; totals to the implied national org size. Reps @28 Cap = largest-remainder apportionment of 28 reps by All MDs (comparison view; T24 and T25 receive 0 under it). Women 25-44 and Wtd Income carried from v3 Territory Plan unchanged (blue = input). Score v4 weights: All MDs 47.06% / All Clinics 29.41% / Women 25-44 11.76% / Income 11.76% (see Read Me). Helper columns R:S feed the 28-cap apportionment.</t>
+    <t xml:space="preserve">HARD CAP: 28 reps. The Reps column (blue) carries v3's original Territory Plan allocation (TX 3, CA-HI 2, all others 1 = 28) and is adjustable — per-rep loads, Score, Rank, and Hiring Wave figures recalculate; keep the column total at 28. Per-rep loads against the ALL-MD universe (18,405) average ~657 MDs/rep — use with the &gt;=10 / &gt;=20 tiers on State Market Summary as a prioritization model. Women 25-44 and Wtd Income carried from v3 unchanged (blue = input). Score v4 weights: All MDs 47.06% / All Clinics 29.41% / Women 25-44 11.76% / Income 11.76% (see Read Me).</t>
   </si>
   <si>
     <t xml:space="preserve">Wave</t>
@@ -660,16 +651,16 @@
     <t xml:space="preserve">T19 LA-AR; T18 AL-MS; T20 IN; T23 TN; T24 IA-SD-ND-WY; T25 SC</t>
   </si>
   <si>
-    <t xml:space="preserve">Full national at implied org size</t>
+    <t xml:space="preserve">Full national at the 28 cap</t>
   </si>
   <si>
     <t xml:space="preserve">CAVEAT: rankings are pure opportunity, not mandate-adjusted. Northeast (incl. mandate states) remains in early waves under v3 weights. Verify the current mandate list (Phase 2) and re-sequence before committing hires.</t>
   </si>
   <si>
-    <t xml:space="preserve">v4 notes: waves re-ranked by v4 score (18 of 25 rankings changed vs v3); wave sizes kept at v3's 7/5/7/6 territories. Reps figures use the headline 'Reps Required' sizing (implied org, not the 28 cap). Under the 28-cap comparison view, T24 (IA-SD-ND-WY) and T25 (SC) get 0 reps.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kathy - ALL Universe: all counts sum Waterfall A rev1 labeled columns only (via State Market Summary). Reps (J, blue) is a formula = ROUND(All MDs/300) min 1 — overwrite freely; per-rep loads, score, and rank recalculate.</t>
+    <t xml:space="preserve">v4 notes: waves re-ranked by v4 score (18 of 25 rankings changed vs v3); wave sizes kept at v3's 7/5/7/6 territories. Rep counts use the hard 28-cap allocation from the original (v3) Territory Plan — TX 3, CA-HI 2, all others 1. Cumulative total = 28.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kathy - ALL Universe: all counts sum Waterfall A rev1 labeled columns only (via State Market Summary). Reps (J, blue) = the original Territory Plan 28-rep allocation (TX 3, CA-HI 2, others 1; hard cap 28) — overwrite freely, keep total 28; per-rep loads, Academic Share, Score, and Rank recalculate.</t>
   </si>
   <si>
     <t xml:space="preserve">Weights:</t>
@@ -795,23 +786,21 @@
     <t xml:space="preserve">T25 SC</t>
   </si>
   <si>
-    <t xml:space="preserve">Score = min-max normalization (0-100 across territories) of All MDs/Rep (20%), All Clinics/Rep (60%), Women 25-44 (10%), Median Income (10%); Education 0% (displayed, not scored). Blue cells are inputs: Reps is overwritable; Women 25-44 / Median Income / Education carried from v3 Territory Plan unchanged (v3 census data-quality caveats apply). All MD/clinic counts (F-I) are sums of member states from Waterfall A rev1 labeled columns only, via the State Market Summary tab; stray unlabeled scratch columns in the source were excluded.</t>
+    <t xml:space="preserve">Score = min-max normalization (0-100 across territories) of All MDs/Rep (20%), All Clinics/Rep (60%), Women 25-44 (10%), Median Income (10%); Education 0% (displayed, not scored). Blue cells are inputs: Reps carries the original Territory Plan 28-rep allocation (hard cap); Women 25-44 / Median Income / Education carried from v3 Territory Plan unchanged (v3 census data-quality caveats apply). All MD/clinic counts (F-I) are sums of member states from Waterfall A rev1 labeled columns only; stray unlabeled scratch columns in the source were excluded.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
-    <numFmt numFmtId="166" formatCode="\$#,##0"/>
-    <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
-    <numFmt numFmtId="169" formatCode="General"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0"/>
-    <numFmt numFmtId="171" formatCode="0.0%"/>
-    <numFmt numFmtId="172" formatCode="\$#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="\$#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="\$#,##0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -955,7 +944,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1024,23 +1013,43 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1052,11 +1061,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1064,55 +1069,43 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1368,7 +1361,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="120"/>
@@ -1557,9 +1550,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1591,27 +1589,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B2" s="6" t="n">
         <v>18405</v>
@@ -1625,15 +1623,15 @@
         <v>657</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B3" s="8" t="n">
         <v>8757</v>
@@ -1647,15 +1645,15 @@
         <v>313</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>4401</v>
@@ -1669,13 +1667,13 @@
         <v>157</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>1476</v>
@@ -1689,13 +1687,13 @@
         <v>53</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -1732,7 +1730,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -1756,7 +1754,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -1764,7 +1762,7 @@
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
       <c r="H2" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="11"/>
@@ -1772,7 +1770,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
       <c r="N2" s="11" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
@@ -1782,69 +1780,69 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="H3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="L3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="H3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="M3" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="N3" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="N3" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="S3" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>50</v>
@@ -1901,12 +1899,12 @@
         <v>0</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>294</v>
@@ -1963,12 +1961,12 @@
         <v>4</v>
       </c>
       <c r="T5" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>180</v>
@@ -2025,12 +2023,12 @@
         <v>6</v>
       </c>
       <c r="T6" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>273</v>
@@ -2087,12 +2085,12 @@
         <v>4</v>
       </c>
       <c r="T7" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>1499</v>
@@ -2149,12 +2147,12 @@
         <v>44</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>352</v>
@@ -2211,12 +2209,12 @@
         <v>3</v>
       </c>
       <c r="T9" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>254</v>
@@ -2273,12 +2271,12 @@
         <v>2</v>
       </c>
       <c r="T10" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>34</v>
@@ -2335,12 +2333,12 @@
         <v>0</v>
       </c>
       <c r="T11" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>28</v>
@@ -2397,12 +2395,12 @@
         <v>0</v>
       </c>
       <c r="T12" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>1107</v>
@@ -2459,12 +2457,12 @@
         <v>11</v>
       </c>
       <c r="T13" s="12" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>683</v>
@@ -2521,12 +2519,12 @@
         <v>3</v>
       </c>
       <c r="T14" s="12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>80</v>
@@ -2583,12 +2581,12 @@
         <v>3</v>
       </c>
       <c r="T15" s="12" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>179</v>
@@ -2645,12 +2643,12 @@
         <v>4</v>
       </c>
       <c r="T16" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>102</v>
@@ -2707,12 +2705,12 @@
         <v>3</v>
       </c>
       <c r="T17" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>718</v>
@@ -2769,12 +2767,12 @@
         <v>9</v>
       </c>
       <c r="T18" s="12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>442</v>
@@ -2831,12 +2829,12 @@
         <v>13</v>
       </c>
       <c r="T19" s="12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B20" s="8" t="n">
         <v>176</v>
@@ -2893,12 +2891,12 @@
         <v>3</v>
       </c>
       <c r="T20" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>277</v>
@@ -2955,12 +2953,12 @@
         <v>8</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>297</v>
@@ -3017,12 +3015,12 @@
         <v>7</v>
       </c>
       <c r="T22" s="12" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>353</v>
@@ -3079,12 +3077,12 @@
         <v>3</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>320</v>
@@ -3141,12 +3139,12 @@
         <v>6</v>
       </c>
       <c r="T24" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>110</v>
@@ -3203,12 +3201,12 @@
         <v>1</v>
       </c>
       <c r="T25" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>746</v>
@@ -3265,12 +3263,12 @@
         <v>18</v>
       </c>
       <c r="T26" s="12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>395</v>
@@ -3327,12 +3325,12 @@
         <v>3</v>
       </c>
       <c r="T27" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>387</v>
@@ -3389,12 +3387,12 @@
         <v>12</v>
       </c>
       <c r="T28" s="12" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" s="8" t="n">
         <v>168</v>
@@ -3451,12 +3449,12 @@
         <v>2</v>
       </c>
       <c r="T29" s="12" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" s="8" t="n">
         <v>69</v>
@@ -3513,12 +3511,12 @@
         <v>1</v>
       </c>
       <c r="T30" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B31" s="8" t="n">
         <v>779</v>
@@ -3575,12 +3573,12 @@
         <v>13</v>
       </c>
       <c r="T31" s="12" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B32" s="8" t="n">
         <v>53</v>
@@ -3637,12 +3635,12 @@
         <v>2</v>
       </c>
       <c r="T32" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B33" s="8" t="n">
         <v>142</v>
@@ -3699,12 +3697,12 @@
         <v>2</v>
       </c>
       <c r="T33" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B34" s="8" t="n">
         <v>92</v>
@@ -3761,12 +3759,12 @@
         <v>1</v>
       </c>
       <c r="T34" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B35" s="8" t="n">
         <v>428</v>
@@ -3823,12 +3821,12 @@
         <v>6</v>
       </c>
       <c r="T35" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B36" s="8" t="n">
         <v>86</v>
@@ -3885,12 +3883,12 @@
         <v>0</v>
       </c>
       <c r="T36" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B37" s="8" t="n">
         <v>150</v>
@@ -3947,12 +3945,12 @@
         <v>1</v>
       </c>
       <c r="T37" s="12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B38" s="8" t="n">
         <v>1030</v>
@@ -4009,12 +4007,12 @@
         <v>24</v>
       </c>
       <c r="T38" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B39" s="8" t="n">
         <v>795</v>
@@ -4071,12 +4069,12 @@
         <v>23</v>
       </c>
       <c r="T39" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B40" s="8" t="n">
         <v>193</v>
@@ -4133,12 +4131,12 @@
         <v>4</v>
       </c>
       <c r="T40" s="12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B41" s="8" t="n">
         <v>304</v>
@@ -4195,12 +4193,12 @@
         <v>3</v>
       </c>
       <c r="T41" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B42" s="8" t="n">
         <v>607</v>
@@ -4257,12 +4255,12 @@
         <v>6</v>
       </c>
       <c r="T42" s="12" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B43" s="8" t="n">
         <v>77</v>
@@ -4319,12 +4317,12 @@
         <v>3</v>
       </c>
       <c r="T43" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B44" s="8" t="n">
         <v>364</v>
@@ -4381,12 +4379,12 @@
         <v>5</v>
       </c>
       <c r="T44" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B45" s="8" t="n">
         <v>74</v>
@@ -4443,12 +4441,12 @@
         <v>4</v>
       </c>
       <c r="T45" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B46" s="8" t="n">
         <v>401</v>
@@ -4505,12 +4503,12 @@
         <v>6</v>
       </c>
       <c r="T46" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B47" s="8" t="n">
         <v>1660</v>
@@ -4567,12 +4565,12 @@
         <v>24</v>
       </c>
       <c r="T47" s="12" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B48" s="8" t="n">
         <v>198</v>
@@ -4629,12 +4627,12 @@
         <v>4</v>
       </c>
       <c r="T48" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B49" s="8" t="n">
         <v>478</v>
@@ -4691,12 +4689,12 @@
         <v>8</v>
       </c>
       <c r="T49" s="12" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B50" s="8" t="n">
         <v>32</v>
@@ -4753,12 +4751,12 @@
         <v>3</v>
       </c>
       <c r="T50" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B51" s="8" t="n">
         <v>380</v>
@@ -4815,12 +4813,12 @@
         <v>7</v>
       </c>
       <c r="T51" s="12" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B52" s="8" t="n">
         <v>363</v>
@@ -4877,12 +4875,12 @@
         <v>9</v>
       </c>
       <c r="T52" s="12" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B53" s="8" t="n">
         <v>107</v>
@@ -4939,12 +4937,12 @@
         <v>2</v>
       </c>
       <c r="T53" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B54" s="8" t="n">
         <v>39</v>
@@ -5001,12 +4999,12 @@
         <v>0</v>
       </c>
       <c r="T54" s="12" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B55" s="15" t="n">
         <f aca="false">SUM(B4:B54)</f>
@@ -5103,1931 +5101,1486 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S29"/>
+  <dimension ref="A1:O29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="14" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D1" s="16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E1" s="16" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F1" s="16" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G1" s="16" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H1" s="16" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I1" s="16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J1" s="16" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L1" s="16" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M1" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N1" s="16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="O1" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="P1" s="16" t="s">
         <v>152</v>
       </c>
-      <c r="Q1" s="16" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
+        <v>132</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="R1" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="S1" s="16" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A2,'State Market Summary'!$B$4:$B$54)</f>
         <v>1660</v>
       </c>
-      <c r="E2" s="8" t="n">
+      <c r="E2" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A2,'State Market Summary'!$C$4:$C$54)</f>
         <v>540</v>
       </c>
-      <c r="F2" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D2/300,0))</f>
-        <v>6</v>
-      </c>
-      <c r="G2" s="8" t="n">
+      <c r="F2" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G2" s="18" t="n">
         <f aca="false">ROUND(D2/F2,0)</f>
-        <v>277</v>
-      </c>
-      <c r="H2" s="7" t="str">
-        <f aca="false">IF(G2&lt;275,"UNDER",IF(G2&gt;325,"OVER","IN BAND"))</f>
-        <v>IN BAND</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <f aca="false">INT(R2)+IF(RANK(S2,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
+        <v>553</v>
+      </c>
+      <c r="H2" s="20" t="n">
+        <f aca="false">ROUND(E2/F2,1)</f>
+        <v>180</v>
+      </c>
+      <c r="I2" s="21" t="n">
+        <v>3090173</v>
+      </c>
+      <c r="J2" s="22" t="n">
+        <v>78473</v>
+      </c>
+      <c r="K2" s="23" t="n">
+        <f aca="false">ROUND((40*D2/MAX($D$2:$D$26)+25*E2/MAX($E$2:$E$26)+10*I2/MAX($I$2:$I$26)+10*J2/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>89.1</v>
+      </c>
+      <c r="L2" s="17" t="n">
+        <f aca="false">RANK(K2,$K$2:$K$26)</f>
         <v>2</v>
       </c>
-      <c r="J2" s="8" t="n">
-        <f aca="false">IF(I2=0,"n/a",ROUND(D2/I2,0))</f>
-        <v>830</v>
-      </c>
-      <c r="K2" s="17" t="n">
-        <v>3090173</v>
-      </c>
-      <c r="L2" s="18" t="n">
-        <v>78473</v>
-      </c>
       <c r="M2" s="19" t="n">
-        <f aca="false">ROUND((40*D2/MAX($D$2:$D$26)+25*E2/MAX($E$2:$E$26)+10*K2/MAX($K$2:$K$26)+10*L2/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>89.1</v>
-      </c>
-      <c r="N2" s="7" t="n">
-        <f aca="false">RANK(M2,$M$2:$M$26)</f>
-        <v>2</v>
-      </c>
-      <c r="O2" s="20" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" s="7" t="n">
-        <f aca="false">O2-N2</f>
+        <v>1</v>
+      </c>
+      <c r="N2" s="17" t="n">
+        <f aca="false">M2-L2</f>
         <v>-1</v>
       </c>
-      <c r="Q2" s="7" t="n">
-        <f aca="false">IF(N2&lt;=7,1,IF(N2&lt;=12,2,IF(N2&lt;=19,3,4)))</f>
-        <v>1</v>
-      </c>
-      <c r="R2" s="21" t="n">
-        <f aca="false">D2*28/SUM($D$2:$D$26)</f>
-        <v>2.5254007063298</v>
-      </c>
-      <c r="S2" s="21" t="n">
-        <f aca="false">R2-INT(R2)</f>
-        <v>0.525400706329802</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="8" t="n">
+      <c r="O2" s="17" t="n">
+        <f aca="false">IF(L2&lt;=7,1,IF(L2&lt;=12,2,IF(L2&lt;=19,3,4)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A3,'State Market Summary'!$B$4:$B$54)</f>
         <v>1579</v>
       </c>
-      <c r="E3" s="8" t="n">
+      <c r="E3" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A3,'State Market Summary'!$C$4:$C$54)</f>
         <v>688</v>
       </c>
-      <c r="F3" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D3/300,0))</f>
-        <v>5</v>
-      </c>
-      <c r="G3" s="8" t="n">
+      <c r="F3" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="18" t="n">
         <f aca="false">ROUND(D3/F3,0)</f>
-        <v>316</v>
-      </c>
-      <c r="H3" s="7" t="str">
-        <f aca="false">IF(G3&lt;275,"UNDER",IF(G3&gt;325,"OVER","IN BAND"))</f>
-        <v>IN BAND</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <f aca="false">INT(R3)+IF(RANK(S3,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
+        <v>790</v>
+      </c>
+      <c r="H3" s="20" t="n">
+        <f aca="false">ROUND(E3/F3,1)</f>
+        <v>344</v>
+      </c>
+      <c r="I3" s="21" t="n">
+        <v>3819366</v>
+      </c>
+      <c r="J3" s="22" t="n">
+        <v>97969</v>
+      </c>
+      <c r="K3" s="23" t="n">
+        <f aca="false">ROUND((40*D3/MAX($D$2:$D$26)+25*E3/MAX($E$2:$E$26)+10*I3/MAX($I$2:$I$26)+10*J3/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>97.7</v>
+      </c>
+      <c r="L3" s="17" t="n">
+        <f aca="false">RANK(K3,$K$2:$K$26)</f>
+        <v>1</v>
+      </c>
+      <c r="M3" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="8" t="n">
-        <f aca="false">IF(I3=0,"n/a",ROUND(D3/I3,0))</f>
-        <v>790</v>
-      </c>
-      <c r="K3" s="17" t="n">
-        <v>3819366</v>
-      </c>
-      <c r="L3" s="18" t="n">
-        <v>97969</v>
-      </c>
-      <c r="M3" s="19" t="n">
-        <f aca="false">ROUND((40*D3/MAX($D$2:$D$26)+25*E3/MAX($E$2:$E$26)+10*K3/MAX($K$2:$K$26)+10*L3/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>97.7</v>
-      </c>
-      <c r="N3" s="7" t="n">
-        <f aca="false">RANK(M3,$M$2:$M$26)</f>
-        <v>1</v>
-      </c>
-      <c r="O3" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="P3" s="7" t="n">
-        <f aca="false">O3-N3</f>
-        <v>1</v>
-      </c>
-      <c r="Q3" s="7" t="n">
-        <f aca="false">IF(N3&lt;=7,1,IF(N3&lt;=12,2,IF(N3&lt;=19,3,4)))</f>
-        <v>1</v>
-      </c>
-      <c r="R3" s="21" t="n">
-        <f aca="false">D3*28/SUM($D$2:$D$26)</f>
-        <v>2.40217332246672</v>
-      </c>
-      <c r="S3" s="21" t="n">
-        <f aca="false">R3-INT(R3)</f>
-        <v>0.402173322466721</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="s">
+      <c r="N3" s="17" t="n">
+        <f aca="false">M3-L3</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="17" t="n">
+        <f aca="false">IF(L3&lt;=7,1,IF(L3&lt;=12,2,IF(L3&lt;=19,3,4)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="B4" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="D4" s="8" t="n">
+      <c r="C4" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="D4" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A4,'State Market Summary'!$B$4:$B$54)</f>
         <v>1030</v>
       </c>
-      <c r="E4" s="8" t="n">
+      <c r="E4" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A4,'State Market Summary'!$C$4:$C$54)</f>
         <v>404</v>
       </c>
-      <c r="F4" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D4/300,0))</f>
+      <c r="F4" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="18" t="n">
+        <f aca="false">ROUND(D4/F4,0)</f>
+        <v>1030</v>
+      </c>
+      <c r="H4" s="20" t="n">
+        <f aca="false">ROUND(E4/F4,1)</f>
+        <v>404</v>
+      </c>
+      <c r="I4" s="21" t="n">
+        <v>1726412</v>
+      </c>
+      <c r="J4" s="22" t="n">
+        <v>89542</v>
+      </c>
+      <c r="K4" s="23" t="n">
+        <f aca="false">ROUND((40*D4/MAX($D$2:$D$26)+25*E4/MAX($E$2:$E$26)+10*I4/MAX($I$2:$I$26)+10*J4/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>62.5</v>
+      </c>
+      <c r="L4" s="17" t="n">
+        <f aca="false">RANK(K4,$K$2:$K$26)</f>
         <v>3</v>
       </c>
-      <c r="G4" s="8" t="n">
-        <f aca="false">ROUND(D4/F4,0)</f>
-        <v>343</v>
-      </c>
-      <c r="H4" s="7" t="str">
-        <f aca="false">IF(G4&lt;275,"UNDER",IF(G4&gt;325,"OVER","IN BAND"))</f>
-        <v>OVER</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <f aca="false">INT(R4)+IF(RANK(S4,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>2</v>
-      </c>
-      <c r="J4" s="8" t="n">
-        <f aca="false">IF(I4=0,"n/a",ROUND(D4/I4,0))</f>
-        <v>515</v>
-      </c>
-      <c r="K4" s="17" t="n">
-        <v>1726412</v>
-      </c>
-      <c r="L4" s="18" t="n">
-        <v>89542</v>
-      </c>
       <c r="M4" s="19" t="n">
-        <f aca="false">ROUND((40*D4/MAX($D$2:$D$26)+25*E4/MAX($E$2:$E$26)+10*K4/MAX($K$2:$K$26)+10*L4/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>62.5</v>
-      </c>
-      <c r="N4" s="7" t="n">
-        <f aca="false">RANK(M4,$M$2:$M$26)</f>
         <v>3</v>
       </c>
-      <c r="O4" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="P4" s="7" t="n">
-        <f aca="false">O4-N4</f>
+      <c r="N4" s="17" t="n">
+        <f aca="false">M4-L4</f>
         <v>0</v>
       </c>
-      <c r="Q4" s="7" t="n">
-        <f aca="false">IF(N4&lt;=7,1,IF(N4&lt;=12,2,IF(N4&lt;=19,3,4)))</f>
-        <v>1</v>
-      </c>
-      <c r="R4" s="21" t="n">
-        <f aca="false">D4*28/SUM($D$2:$D$26)</f>
-        <v>1.56696549850584</v>
-      </c>
-      <c r="S4" s="21" t="n">
-        <f aca="false">R4-INT(R4)</f>
-        <v>0.566965498505841</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
+      <c r="O4" s="17" t="n">
+        <f aca="false">IF(L4&lt;=7,1,IF(L4&lt;=12,2,IF(L4&lt;=19,3,4)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D5" s="8" t="n">
+      <c r="C5" s="17" t="s">
+        <v>157</v>
+      </c>
+      <c r="D5" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A5,'State Market Summary'!$B$4:$B$54)</f>
         <v>795</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A5,'State Market Summary'!$C$4:$C$54)</f>
         <v>178</v>
       </c>
-      <c r="F5" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D5/300,0))</f>
-        <v>3</v>
-      </c>
-      <c r="G5" s="8" t="n">
+      <c r="F5" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="18" t="n">
         <f aca="false">ROUND(D5/F5,0)</f>
-        <v>265</v>
-      </c>
-      <c r="H5" s="7" t="str">
-        <f aca="false">IF(G5&lt;275,"UNDER",IF(G5&gt;325,"OVER","IN BAND"))</f>
-        <v>UNDER</v>
-      </c>
-      <c r="I5" s="7" t="n">
-        <f aca="false">INT(R5)+IF(RANK(S5,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J5" s="8" t="n">
-        <f aca="false">IF(I5=0,"n/a",ROUND(D5/I5,0))</f>
         <v>795</v>
       </c>
-      <c r="K5" s="17" t="n">
+      <c r="H5" s="20" t="n">
+        <f aca="false">ROUND(E5/F5,1)</f>
+        <v>178</v>
+      </c>
+      <c r="I5" s="21" t="n">
         <v>1089150</v>
       </c>
-      <c r="L5" s="18" t="n">
+      <c r="J5" s="22" t="n">
         <v>71229</v>
       </c>
+      <c r="K5" s="23" t="n">
+        <f aca="false">ROUND((40*D5/MAX($D$2:$D$26)+25*E5/MAX($E$2:$E$26)+10*I5/MAX($I$2:$I$26)+10*J5/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>42.1</v>
+      </c>
+      <c r="L5" s="17" t="n">
+        <f aca="false">RANK(K5,$K$2:$K$26)</f>
+        <v>10</v>
+      </c>
       <c r="M5" s="19" t="n">
-        <f aca="false">ROUND((40*D5/MAX($D$2:$D$26)+25*E5/MAX($E$2:$E$26)+10*K5/MAX($K$2:$K$26)+10*L5/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>42.1</v>
-      </c>
-      <c r="N5" s="7" t="n">
-        <f aca="false">RANK(M5,$M$2:$M$26)</f>
-        <v>10</v>
-      </c>
-      <c r="O5" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="P5" s="7" t="n">
-        <f aca="false">O5-N5</f>
+      <c r="N5" s="17" t="n">
+        <f aca="false">M5-L5</f>
         <v>-6</v>
       </c>
-      <c r="Q5" s="7" t="n">
-        <f aca="false">IF(N5&lt;=7,1,IF(N5&lt;=12,2,IF(N5&lt;=19,3,4)))</f>
+      <c r="O5" s="17" t="n">
+        <f aca="false">IF(L5&lt;=7,1,IF(L5&lt;=12,2,IF(L5&lt;=19,3,4)))</f>
         <v>2</v>
       </c>
-      <c r="R5" s="21" t="n">
-        <f aca="false">D5*28/SUM($D$2:$D$26)</f>
-        <v>1.20945395273024</v>
-      </c>
-      <c r="S5" s="21" t="n">
-        <f aca="false">R5-INT(R5)</f>
-        <v>0.209453952730236</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B6" s="17" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="D6" s="8" t="n">
+      <c r="C6" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A6,'State Market Summary'!$B$4:$B$54)</f>
         <v>1107</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A6,'State Market Summary'!$C$4:$C$54)</f>
         <v>273</v>
       </c>
-      <c r="F6" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D6/300,0))</f>
-        <v>4</v>
-      </c>
-      <c r="G6" s="8" t="n">
+      <c r="F6" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="18" t="n">
         <f aca="false">ROUND(D6/F6,0)</f>
-        <v>277</v>
-      </c>
-      <c r="H6" s="7" t="str">
-        <f aca="false">IF(G6&lt;275,"UNDER",IF(G6&gt;325,"OVER","IN BAND"))</f>
-        <v>IN BAND</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <f aca="false">INT(R6)+IF(RANK(S6,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>2</v>
-      </c>
-      <c r="J6" s="8" t="n">
-        <f aca="false">IF(I6=0,"n/a",ROUND(D6/I6,0))</f>
-        <v>554</v>
-      </c>
-      <c r="K6" s="17" t="n">
+        <v>1107</v>
+      </c>
+      <c r="H6" s="20" t="n">
+        <f aca="false">ROUND(E6/F6,1)</f>
+        <v>273</v>
+      </c>
+      <c r="I6" s="21" t="n">
         <v>1780020</v>
       </c>
-      <c r="L6" s="18" t="n">
+      <c r="J6" s="22" t="n">
         <v>71602</v>
       </c>
+      <c r="K6" s="23" t="n">
+        <f aca="false">ROUND((40*D6/MAX($D$2:$D$26)+25*E6/MAX($E$2:$E$26)+10*I6/MAX($I$2:$I$26)+10*J6/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>57.1</v>
+      </c>
+      <c r="L6" s="17" t="n">
+        <f aca="false">RANK(K6,$K$2:$K$26)</f>
+        <v>5</v>
+      </c>
       <c r="M6" s="19" t="n">
-        <f aca="false">ROUND((40*D6/MAX($D$2:$D$26)+25*E6/MAX($E$2:$E$26)+10*K6/MAX($K$2:$K$26)+10*L6/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>57.1</v>
-      </c>
-      <c r="N6" s="7" t="n">
-        <f aca="false">RANK(M6,$M$2:$M$26)</f>
         <v>5</v>
       </c>
-      <c r="O6" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="P6" s="7" t="n">
-        <f aca="false">O6-N6</f>
+      <c r="N6" s="17" t="n">
+        <f aca="false">M6-L6</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="7" t="n">
-        <f aca="false">IF(N6&lt;=7,1,IF(N6&lt;=12,2,IF(N6&lt;=19,3,4)))</f>
-        <v>1</v>
-      </c>
-      <c r="R6" s="21" t="n">
-        <f aca="false">D6*28/SUM($D$2:$D$26)</f>
-        <v>1.6841075794621</v>
-      </c>
-      <c r="S6" s="21" t="n">
-        <f aca="false">R6-INT(R6)</f>
-        <v>0.684107579462103</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="D7" s="8" t="n">
+      <c r="O6" s="17" t="n">
+        <f aca="false">IF(L6&lt;=7,1,IF(L6&lt;=12,2,IF(L6&lt;=19,3,4)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="17" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>160</v>
+      </c>
+      <c r="D7" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A7,'State Market Summary'!$B$4:$B$54)</f>
         <v>1035</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="E7" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A7,'State Market Summary'!$C$4:$C$54)</f>
         <v>338</v>
       </c>
-      <c r="F7" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D7/300,0))</f>
-        <v>3</v>
-      </c>
-      <c r="G7" s="8" t="n">
+      <c r="F7" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="18" t="n">
         <f aca="false">ROUND(D7/F7,0)</f>
-        <v>345</v>
-      </c>
-      <c r="H7" s="7" t="str">
-        <f aca="false">IF(G7&lt;275,"UNDER",IF(G7&gt;325,"OVER","IN BAND"))</f>
-        <v>OVER</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <f aca="false">INT(R7)+IF(RANK(S7,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
+        <v>1035</v>
+      </c>
+      <c r="H7" s="20" t="n">
+        <f aca="false">ROUND(E7/F7,1)</f>
+        <v>338</v>
+      </c>
+      <c r="I7" s="21" t="n">
+        <v>1985432</v>
+      </c>
+      <c r="J7" s="22" t="n">
+        <v>89604</v>
+      </c>
+      <c r="K7" s="23" t="n">
+        <f aca="false">ROUND((40*D7/MAX($D$2:$D$26)+25*E7/MAX($E$2:$E$26)+10*I7/MAX($I$2:$I$26)+10*J7/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>60.7</v>
+      </c>
+      <c r="L7" s="17" t="n">
+        <f aca="false">RANK(K7,$K$2:$K$26)</f>
+        <v>4</v>
+      </c>
+      <c r="M7" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="N7" s="17" t="n">
+        <f aca="false">M7-L7</f>
         <v>2</v>
       </c>
-      <c r="J7" s="8" t="n">
-        <f aca="false">IF(I7=0,"n/a",ROUND(D7/I7,0))</f>
-        <v>518</v>
-      </c>
-      <c r="K7" s="17" t="n">
-        <v>1985432</v>
-      </c>
-      <c r="L7" s="18" t="n">
-        <v>89604</v>
-      </c>
-      <c r="M7" s="19" t="n">
-        <f aca="false">ROUND((40*D7/MAX($D$2:$D$26)+25*E7/MAX($E$2:$E$26)+10*K7/MAX($K$2:$K$26)+10*L7/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>60.7</v>
-      </c>
-      <c r="N7" s="7" t="n">
-        <f aca="false">RANK(M7,$M$2:$M$26)</f>
-        <v>4</v>
-      </c>
-      <c r="O7" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="P7" s="7" t="n">
-        <f aca="false">O7-N7</f>
-        <v>2</v>
-      </c>
-      <c r="Q7" s="7" t="n">
-        <f aca="false">IF(N7&lt;=7,1,IF(N7&lt;=12,2,IF(N7&lt;=19,3,4)))</f>
-        <v>1</v>
-      </c>
-      <c r="R7" s="21" t="n">
-        <f aca="false">D7*28/SUM($D$2:$D$26)</f>
-        <v>1.57457212713936</v>
-      </c>
-      <c r="S7" s="21" t="n">
-        <f aca="false">R7-INT(R7)</f>
-        <v>0.574572127139364</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="s">
+      <c r="O7" s="17" t="n">
+        <f aca="false">IF(L7&lt;=7,1,IF(L7&lt;=12,2,IF(L7&lt;=19,3,4)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="D8" s="8" t="n">
+      <c r="C8" s="17" t="s">
+        <v>161</v>
+      </c>
+      <c r="D8" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A8,'State Market Summary'!$B$4:$B$54)</f>
         <v>746</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="E8" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A8,'State Market Summary'!$C$4:$C$54)</f>
         <v>207</v>
       </c>
-      <c r="F8" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D8/300,0))</f>
+      <c r="F8" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <f aca="false">ROUND(D8/F8,0)</f>
+        <v>746</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <f aca="false">ROUND(E8/F8,1)</f>
+        <v>207</v>
+      </c>
+      <c r="I8" s="21" t="n">
+        <v>910821</v>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>72965</v>
+      </c>
+      <c r="K8" s="23" t="n">
+        <f aca="false">ROUND((40*D8/MAX($D$2:$D$26)+25*E8/MAX($E$2:$E$26)+10*I8/MAX($I$2:$I$26)+10*J8/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>41.6</v>
+      </c>
+      <c r="L8" s="17" t="n">
+        <f aca="false">RANK(K8,$K$2:$K$26)</f>
+        <v>11</v>
+      </c>
+      <c r="M8" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="N8" s="17" t="n">
+        <f aca="false">M8-L8</f>
+        <v>-4</v>
+      </c>
+      <c r="O8" s="17" t="n">
+        <f aca="false">IF(L8&lt;=7,1,IF(L8&lt;=12,2,IF(L8&lt;=19,3,4)))</f>
         <v>2</v>
       </c>
-      <c r="G8" s="8" t="n">
-        <f aca="false">ROUND(D8/F8,0)</f>
-        <v>373</v>
-      </c>
-      <c r="H8" s="7" t="str">
-        <f aca="false">IF(G8&lt;275,"UNDER",IF(G8&gt;325,"OVER","IN BAND"))</f>
-        <v>OVER</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <f aca="false">INT(R8)+IF(RANK(S8,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J8" s="8" t="n">
-        <f aca="false">IF(I8=0,"n/a",ROUND(D8/I8,0))</f>
-        <v>746</v>
-      </c>
-      <c r="K8" s="17" t="n">
-        <v>910821</v>
-      </c>
-      <c r="L8" s="18" t="n">
-        <v>72965</v>
-      </c>
-      <c r="M8" s="19" t="n">
-        <f aca="false">ROUND((40*D8/MAX($D$2:$D$26)+25*E8/MAX($E$2:$E$26)+10*K8/MAX($K$2:$K$26)+10*L8/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>41.6</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <f aca="false">RANK(M8,$M$2:$M$26)</f>
-        <v>11</v>
-      </c>
-      <c r="O8" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="P8" s="7" t="n">
-        <f aca="false">O8-N8</f>
-        <v>-4</v>
-      </c>
-      <c r="Q8" s="7" t="n">
-        <f aca="false">IF(N8&lt;=7,1,IF(N8&lt;=12,2,IF(N8&lt;=19,3,4)))</f>
-        <v>2</v>
-      </c>
-      <c r="R8" s="21" t="n">
-        <f aca="false">D8*28/SUM($D$2:$D$26)</f>
-        <v>1.13490899212171</v>
-      </c>
-      <c r="S8" s="21" t="n">
-        <f aca="false">R8-INT(R8)</f>
-        <v>0.134908992121706</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D9" s="8" t="n">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A9,'State Market Summary'!$B$4:$B$54)</f>
         <v>918</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="E9" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A9,'State Market Summary'!$C$4:$C$54)</f>
         <v>279</v>
       </c>
-      <c r="F9" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D9/300,0))</f>
-        <v>3</v>
-      </c>
-      <c r="G9" s="8" t="n">
+      <c r="F9" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="18" t="n">
         <f aca="false">ROUND(D9/F9,0)</f>
-        <v>306</v>
-      </c>
-      <c r="H9" s="7" t="str">
-        <f aca="false">IF(G9&lt;275,"UNDER",IF(G9&gt;325,"OVER","IN BAND"))</f>
-        <v>IN BAND</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <f aca="false">INT(R9)+IF(RANK(S9,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J9" s="8" t="n">
-        <f aca="false">IF(I9=0,"n/a",ROUND(D9/I9,0))</f>
         <v>918</v>
       </c>
-      <c r="K9" s="17" t="n">
+      <c r="H9" s="20" t="n">
+        <f aca="false">ROUND(E9/F9,1)</f>
+        <v>279</v>
+      </c>
+      <c r="I9" s="21" t="n">
         <v>1294309</v>
       </c>
-      <c r="L9" s="18" t="n">
+      <c r="J9" s="22" t="n">
         <v>97019</v>
       </c>
+      <c r="K9" s="23" t="n">
+        <f aca="false">ROUND((40*D9/MAX($D$2:$D$26)+25*E9/MAX($E$2:$E$26)+10*I9/MAX($I$2:$I$26)+10*J9/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>53.6</v>
+      </c>
+      <c r="L9" s="17" t="n">
+        <f aca="false">RANK(K9,$K$2:$K$26)</f>
+        <v>6</v>
+      </c>
       <c r="M9" s="19" t="n">
-        <f aca="false">ROUND((40*D9/MAX($D$2:$D$26)+25*E9/MAX($E$2:$E$26)+10*K9/MAX($K$2:$K$26)+10*L9/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>53.6</v>
-      </c>
-      <c r="N9" s="7" t="n">
-        <f aca="false">RANK(M9,$M$2:$M$26)</f>
-        <v>6</v>
-      </c>
-      <c r="O9" s="20" t="n">
         <v>8</v>
       </c>
-      <c r="P9" s="7" t="n">
-        <f aca="false">O9-N9</f>
+      <c r="N9" s="17" t="n">
+        <f aca="false">M9-L9</f>
         <v>2</v>
       </c>
-      <c r="Q9" s="7" t="n">
-        <f aca="false">IF(N9&lt;=7,1,IF(N9&lt;=12,2,IF(N9&lt;=19,3,4)))</f>
-        <v>1</v>
-      </c>
-      <c r="R9" s="21" t="n">
-        <f aca="false">D9*28/SUM($D$2:$D$26)</f>
-        <v>1.39657701711491</v>
-      </c>
-      <c r="S9" s="21" t="n">
-        <f aca="false">R9-INT(R9)</f>
-        <v>0.396577017114914</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="D10" s="8" t="n">
+      <c r="O9" s="17" t="n">
+        <f aca="false">IF(L9&lt;=7,1,IF(L9&lt;=12,2,IF(L9&lt;=19,3,4)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A10,'State Market Summary'!$B$4:$B$54)</f>
         <v>758</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="E10" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A10,'State Market Summary'!$C$4:$C$54)</f>
         <v>176</v>
       </c>
-      <c r="F10" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D10/300,0))</f>
-        <v>3</v>
-      </c>
-      <c r="G10" s="8" t="n">
+      <c r="F10" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="18" t="n">
         <f aca="false">ROUND(D10/F10,0)</f>
-        <v>253</v>
-      </c>
-      <c r="H10" s="7" t="str">
-        <f aca="false">IF(G10&lt;275,"UNDER",IF(G10&gt;325,"OVER","IN BAND"))</f>
-        <v>UNDER</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <f aca="false">INT(R10)+IF(RANK(S10,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J10" s="8" t="n">
-        <f aca="false">IF(I10=0,"n/a",ROUND(D10/I10,0))</f>
         <v>758</v>
       </c>
-      <c r="K10" s="17" t="n">
+      <c r="H10" s="20" t="n">
+        <f aca="false">ROUND(E10/F10,1)</f>
+        <v>176</v>
+      </c>
+      <c r="I10" s="21" t="n">
         <v>1084210</v>
       </c>
-      <c r="L10" s="18" t="n">
+      <c r="J10" s="22" t="n">
         <v>81797</v>
       </c>
+      <c r="K10" s="23" t="n">
+        <f aca="false">ROUND((40*D10/MAX($D$2:$D$26)+25*E10/MAX($E$2:$E$26)+10*I10/MAX($I$2:$I$26)+10*J10/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>42.2</v>
+      </c>
+      <c r="L10" s="17" t="n">
+        <f aca="false">RANK(K10,$K$2:$K$26)</f>
+        <v>9</v>
+      </c>
       <c r="M10" s="19" t="n">
-        <f aca="false">ROUND((40*D10/MAX($D$2:$D$26)+25*E10/MAX($E$2:$E$26)+10*K10/MAX($K$2:$K$26)+10*L10/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>42.2</v>
-      </c>
-      <c r="N10" s="7" t="n">
-        <f aca="false">RANK(M10,$M$2:$M$26)</f>
         <v>9</v>
       </c>
-      <c r="O10" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="P10" s="7" t="n">
-        <f aca="false">O10-N10</f>
+      <c r="N10" s="17" t="n">
+        <f aca="false">M10-L10</f>
         <v>0</v>
       </c>
-      <c r="Q10" s="7" t="n">
-        <f aca="false">IF(N10&lt;=7,1,IF(N10&lt;=12,2,IF(N10&lt;=19,3,4)))</f>
+      <c r="O10" s="17" t="n">
+        <f aca="false">IF(L10&lt;=7,1,IF(L10&lt;=12,2,IF(L10&lt;=19,3,4)))</f>
         <v>2</v>
       </c>
-      <c r="R10" s="21" t="n">
-        <f aca="false">D10*28/SUM($D$2:$D$26)</f>
-        <v>1.15316490084216</v>
-      </c>
-      <c r="S10" s="21" t="n">
-        <f aca="false">R10-INT(R10)</f>
-        <v>0.153164900842163</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D11" s="8" t="n">
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A11,'State Market Summary'!$B$4:$B$54)</f>
         <v>664</v>
       </c>
-      <c r="E11" s="8" t="n">
+      <c r="E11" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A11,'State Market Summary'!$C$4:$C$54)</f>
         <v>200</v>
       </c>
-      <c r="F11" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D11/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="G11" s="8" t="n">
+      <c r="F11" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="18" t="n">
         <f aca="false">ROUND(D11/F11,0)</f>
-        <v>332</v>
-      </c>
-      <c r="H11" s="7" t="str">
-        <f aca="false">IF(G11&lt;275,"UNDER",IF(G11&gt;325,"OVER","IN BAND"))</f>
-        <v>OVER</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <f aca="false">INT(R11)+IF(RANK(S11,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J11" s="8" t="n">
-        <f aca="false">IF(I11=0,"n/a",ROUND(D11/I11,0))</f>
         <v>664</v>
       </c>
-      <c r="K11" s="17" t="n">
+      <c r="H11" s="20" t="n">
+        <f aca="false">ROUND(E11/F11,1)</f>
+        <v>200</v>
+      </c>
+      <c r="I11" s="21" t="n">
         <v>995376</v>
       </c>
-      <c r="L11" s="18" t="n">
+      <c r="J11" s="22" t="n">
         <v>67472</v>
       </c>
+      <c r="K11" s="23" t="n">
+        <f aca="false">ROUND((40*D11/MAX($D$2:$D$26)+25*E11/MAX($E$2:$E$26)+10*I11/MAX($I$2:$I$26)+10*J11/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>38.5</v>
+      </c>
+      <c r="L11" s="17" t="n">
+        <f aca="false">RANK(K11,$K$2:$K$26)</f>
+        <v>15</v>
+      </c>
       <c r="M11" s="19" t="n">
-        <f aca="false">ROUND((40*D11/MAX($D$2:$D$26)+25*E11/MAX($E$2:$E$26)+10*K11/MAX($K$2:$K$26)+10*L11/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>38.5</v>
-      </c>
-      <c r="N11" s="7" t="n">
-        <f aca="false">RANK(M11,$M$2:$M$26)</f>
-        <v>15</v>
-      </c>
-      <c r="O11" s="20" t="n">
         <v>10</v>
       </c>
-      <c r="P11" s="7" t="n">
-        <f aca="false">O11-N11</f>
+      <c r="N11" s="17" t="n">
+        <f aca="false">M11-L11</f>
         <v>-5</v>
       </c>
-      <c r="Q11" s="7" t="n">
-        <f aca="false">IF(N11&lt;=7,1,IF(N11&lt;=12,2,IF(N11&lt;=19,3,4)))</f>
+      <c r="O11" s="17" t="n">
+        <f aca="false">IF(L11&lt;=7,1,IF(L11&lt;=12,2,IF(L11&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
-      <c r="R11" s="21" t="n">
-        <f aca="false">D11*28/SUM($D$2:$D$26)</f>
-        <v>1.01016028253192</v>
-      </c>
-      <c r="S11" s="21" t="n">
-        <f aca="false">R11-INT(R11)</f>
-        <v>0.0101602825319207</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="D12" s="8" t="n">
+      <c r="C12" s="17" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A12,'State Market Summary'!$B$4:$B$54)</f>
         <v>683</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A12,'State Market Summary'!$C$4:$C$54)</f>
         <v>220</v>
       </c>
-      <c r="F12" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D12/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="G12" s="8" t="n">
+      <c r="F12" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="18" t="n">
         <f aca="false">ROUND(D12/F12,0)</f>
-        <v>342</v>
-      </c>
-      <c r="H12" s="7" t="str">
-        <f aca="false">IF(G12&lt;275,"UNDER",IF(G12&gt;325,"OVER","IN BAND"))</f>
-        <v>OVER</v>
-      </c>
-      <c r="I12" s="7" t="n">
-        <f aca="false">INT(R12)+IF(RANK(S12,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J12" s="8" t="n">
-        <f aca="false">IF(I12=0,"n/a",ROUND(D12/I12,0))</f>
         <v>683</v>
       </c>
-      <c r="K12" s="17" t="n">
+      <c r="H12" s="20" t="n">
+        <f aca="false">ROUND(E12/F12,1)</f>
+        <v>220</v>
+      </c>
+      <c r="I12" s="21" t="n">
         <v>1070611</v>
       </c>
-      <c r="L12" s="18" t="n">
+      <c r="J12" s="22" t="n">
         <v>75694</v>
       </c>
+      <c r="K12" s="23" t="n">
+        <f aca="false">ROUND((40*D12/MAX($D$2:$D$26)+25*E12/MAX($E$2:$E$26)+10*I12/MAX($I$2:$I$26)+10*J12/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>41.2</v>
+      </c>
+      <c r="L12" s="17" t="n">
+        <f aca="false">RANK(K12,$K$2:$K$26)</f>
+        <v>13</v>
+      </c>
       <c r="M12" s="19" t="n">
-        <f aca="false">ROUND((40*D12/MAX($D$2:$D$26)+25*E12/MAX($E$2:$E$26)+10*K12/MAX($K$2:$K$26)+10*L12/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>41.2</v>
-      </c>
-      <c r="N12" s="7" t="n">
-        <f aca="false">RANK(M12,$M$2:$M$26)</f>
-        <v>13</v>
-      </c>
-      <c r="O12" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="P12" s="7" t="n">
-        <f aca="false">O12-N12</f>
+      <c r="N12" s="17" t="n">
+        <f aca="false">M12-L12</f>
         <v>-2</v>
       </c>
-      <c r="Q12" s="7" t="n">
-        <f aca="false">IF(N12&lt;=7,1,IF(N12&lt;=12,2,IF(N12&lt;=19,3,4)))</f>
+      <c r="O12" s="17" t="n">
+        <f aca="false">IF(L12&lt;=7,1,IF(L12&lt;=12,2,IF(L12&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
-      <c r="R12" s="21" t="n">
-        <f aca="false">D12*28/SUM($D$2:$D$26)</f>
-        <v>1.03906547133931</v>
-      </c>
-      <c r="S12" s="21" t="n">
-        <f aca="false">R12-INT(R12)</f>
-        <v>0.0390654713393099</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D13" s="8" t="n">
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>169</v>
+      </c>
+      <c r="C13" s="17" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A13,'State Market Summary'!$B$4:$B$54)</f>
         <v>734</v>
       </c>
-      <c r="E13" s="8" t="n">
+      <c r="E13" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A13,'State Market Summary'!$C$4:$C$54)</f>
         <v>225</v>
       </c>
-      <c r="F13" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D13/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="G13" s="8" t="n">
+      <c r="F13" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="18" t="n">
         <f aca="false">ROUND(D13/F13,0)</f>
-        <v>367</v>
-      </c>
-      <c r="H13" s="7" t="str">
-        <f aca="false">IF(G13&lt;275,"UNDER",IF(G13&gt;325,"OVER","IN BAND"))</f>
-        <v>OVER</v>
-      </c>
-      <c r="I13" s="7" t="n">
-        <f aca="false">INT(R13)+IF(RANK(S13,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J13" s="8" t="n">
-        <f aca="false">IF(I13=0,"n/a",ROUND(D13/I13,0))</f>
         <v>734</v>
       </c>
-      <c r="K13" s="17" t="n">
+      <c r="H13" s="20" t="n">
+        <f aca="false">ROUND(E13/F13,1)</f>
+        <v>225</v>
+      </c>
+      <c r="I13" s="21" t="n">
         <v>1119028</v>
       </c>
-      <c r="L13" s="18" t="n">
+      <c r="J13" s="22" t="n">
         <v>90198</v>
       </c>
+      <c r="K13" s="23" t="n">
+        <f aca="false">ROUND((40*D13/MAX($D$2:$D$26)+25*E13/MAX($E$2:$E$26)+10*I13/MAX($I$2:$I$26)+10*J13/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>44.7</v>
+      </c>
+      <c r="L13" s="17" t="n">
+        <f aca="false">RANK(K13,$K$2:$K$26)</f>
+        <v>7</v>
+      </c>
       <c r="M13" s="19" t="n">
-        <f aca="false">ROUND((40*D13/MAX($D$2:$D$26)+25*E13/MAX($E$2:$E$26)+10*K13/MAX($K$2:$K$26)+10*L13/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>44.7</v>
-      </c>
-      <c r="N13" s="7" t="n">
-        <f aca="false">RANK(M13,$M$2:$M$26)</f>
-        <v>7</v>
-      </c>
-      <c r="O13" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="P13" s="7" t="n">
-        <f aca="false">O13-N13</f>
+      <c r="N13" s="17" t="n">
+        <f aca="false">M13-L13</f>
         <v>5</v>
       </c>
-      <c r="Q13" s="7" t="n">
-        <f aca="false">IF(N13&lt;=7,1,IF(N13&lt;=12,2,IF(N13&lt;=19,3,4)))</f>
-        <v>1</v>
-      </c>
-      <c r="R13" s="21" t="n">
-        <f aca="false">D13*28/SUM($D$2:$D$26)</f>
-        <v>1.11665308340125</v>
-      </c>
-      <c r="S13" s="21" t="n">
-        <f aca="false">R13-INT(R13)</f>
-        <v>0.11665308340125</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="O13" s="17" t="n">
+        <f aca="false">IF(L13&lt;=7,1,IF(L13&lt;=12,2,IF(L13&lt;=19,3,4)))</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D14" s="8" t="n">
+      <c r="C14" s="17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D14" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A14,'State Market Summary'!$B$4:$B$54)</f>
         <v>779</v>
       </c>
-      <c r="E14" s="8" t="n">
+      <c r="E14" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A14,'State Market Summary'!$C$4:$C$54)</f>
         <v>181</v>
       </c>
-      <c r="F14" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D14/300,0))</f>
-        <v>3</v>
-      </c>
-      <c r="G14" s="8" t="n">
+      <c r="F14" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="18" t="n">
         <f aca="false">ROUND(D14/F14,0)</f>
-        <v>260</v>
-      </c>
-      <c r="H14" s="7" t="str">
-        <f aca="false">IF(G14&lt;275,"UNDER",IF(G14&gt;325,"OVER","IN BAND"))</f>
-        <v>UNDER</v>
-      </c>
-      <c r="I14" s="7" t="n">
-        <f aca="false">INT(R14)+IF(RANK(S14,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J14" s="8" t="n">
-        <f aca="false">IF(I14=0,"n/a",ROUND(D14/I14,0))</f>
         <v>779</v>
       </c>
-      <c r="K14" s="17" t="n">
+      <c r="H14" s="20" t="n">
+        <f aca="false">ROUND(E14/F14,1)</f>
+        <v>181</v>
+      </c>
+      <c r="I14" s="21" t="n">
         <v>975468</v>
       </c>
-      <c r="L14" s="18" t="n">
+      <c r="J14" s="22" t="n">
         <v>70436</v>
       </c>
+      <c r="K14" s="23" t="n">
+        <f aca="false">ROUND((40*D14/MAX($D$2:$D$26)+25*E14/MAX($E$2:$E$26)+10*I14/MAX($I$2:$I$26)+10*J14/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>41.3</v>
+      </c>
+      <c r="L14" s="17" t="n">
+        <f aca="false">RANK(K14,$K$2:$K$26)</f>
+        <v>12</v>
+      </c>
       <c r="M14" s="19" t="n">
-        <f aca="false">ROUND((40*D14/MAX($D$2:$D$26)+25*E14/MAX($E$2:$E$26)+10*K14/MAX($K$2:$K$26)+10*L14/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>41.3</v>
-      </c>
-      <c r="N14" s="7" t="n">
-        <f aca="false">RANK(M14,$M$2:$M$26)</f>
-        <v>12</v>
-      </c>
-      <c r="O14" s="20" t="n">
         <v>13</v>
       </c>
-      <c r="P14" s="7" t="n">
-        <f aca="false">O14-N14</f>
-        <v>1</v>
-      </c>
-      <c r="Q14" s="7" t="n">
-        <f aca="false">IF(N14&lt;=7,1,IF(N14&lt;=12,2,IF(N14&lt;=19,3,4)))</f>
+      <c r="N14" s="17" t="n">
+        <f aca="false">M14-L14</f>
+        <v>1</v>
+      </c>
+      <c r="O14" s="17" t="n">
+        <f aca="false">IF(L14&lt;=7,1,IF(L14&lt;=12,2,IF(L14&lt;=19,3,4)))</f>
         <v>2</v>
       </c>
-      <c r="R14" s="21" t="n">
-        <f aca="false">D14*28/SUM($D$2:$D$26)</f>
-        <v>1.18511274110296</v>
-      </c>
-      <c r="S14" s="21" t="n">
-        <f aca="false">R14-INT(R14)</f>
-        <v>0.185112741102961</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>175</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="D15" s="8" t="n">
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>172</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A15,'State Market Summary'!$B$4:$B$54)</f>
         <v>597</v>
       </c>
-      <c r="E15" s="8" t="n">
+      <c r="E15" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A15,'State Market Summary'!$C$4:$C$54)</f>
         <v>198</v>
       </c>
-      <c r="F15" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D15/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="G15" s="8" t="n">
+      <c r="F15" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="18" t="n">
         <f aca="false">ROUND(D15/F15,0)</f>
-        <v>299</v>
-      </c>
-      <c r="H15" s="7" t="str">
-        <f aca="false">IF(G15&lt;275,"UNDER",IF(G15&gt;325,"OVER","IN BAND"))</f>
-        <v>IN BAND</v>
-      </c>
-      <c r="I15" s="7" t="n">
-        <f aca="false">INT(R15)+IF(RANK(S15,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J15" s="8" t="n">
-        <f aca="false">IF(I15=0,"n/a",ROUND(D15/I15,0))</f>
         <v>597</v>
       </c>
-      <c r="K15" s="17" t="n">
+      <c r="H15" s="20" t="n">
+        <f aca="false">ROUND(E15/F15,1)</f>
+        <v>198</v>
+      </c>
+      <c r="I15" s="21" t="n">
         <v>1097099</v>
       </c>
-      <c r="L15" s="18" t="n">
+      <c r="J15" s="22" t="n">
         <v>68598</v>
       </c>
+      <c r="K15" s="23" t="n">
+        <f aca="false">ROUND((40*D15/MAX($D$2:$D$26)+25*E15/MAX($E$2:$E$26)+10*I15/MAX($I$2:$I$26)+10*J15/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>37</v>
+      </c>
+      <c r="L15" s="17" t="n">
+        <f aca="false">RANK(K15,$K$2:$K$26)</f>
+        <v>17</v>
+      </c>
       <c r="M15" s="19" t="n">
-        <f aca="false">ROUND((40*D15/MAX($D$2:$D$26)+25*E15/MAX($E$2:$E$26)+10*K15/MAX($K$2:$K$26)+10*L15/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>37</v>
-      </c>
-      <c r="N15" s="7" t="n">
-        <f aca="false">RANK(M15,$M$2:$M$26)</f>
-        <v>17</v>
-      </c>
-      <c r="O15" s="20" t="n">
         <v>14</v>
       </c>
-      <c r="P15" s="7" t="n">
-        <f aca="false">O15-N15</f>
+      <c r="N15" s="17" t="n">
+        <f aca="false">M15-L15</f>
         <v>-3</v>
       </c>
-      <c r="Q15" s="7" t="n">
-        <f aca="false">IF(N15&lt;=7,1,IF(N15&lt;=12,2,IF(N15&lt;=19,3,4)))</f>
+      <c r="O15" s="17" t="n">
+        <f aca="false">IF(L15&lt;=7,1,IF(L15&lt;=12,2,IF(L15&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
-      <c r="R15" s="21" t="n">
-        <f aca="false">D15*28/SUM($D$2:$D$26)</f>
-        <v>0.908231458842706</v>
-      </c>
-      <c r="S15" s="21" t="n">
-        <f aca="false">R15-INT(R15)</f>
-        <v>0.908231458842706</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>177</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D16" s="8" t="n">
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C16" s="17" t="s">
+        <v>175</v>
+      </c>
+      <c r="D16" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A16,'State Market Summary'!$B$4:$B$54)</f>
         <v>594</v>
       </c>
-      <c r="E16" s="8" t="n">
+      <c r="E16" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A16,'State Market Summary'!$C$4:$C$54)</f>
         <v>231</v>
       </c>
-      <c r="F16" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D16/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="G16" s="8" t="n">
+      <c r="F16" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="18" t="n">
         <f aca="false">ROUND(D16/F16,0)</f>
-        <v>297</v>
-      </c>
-      <c r="H16" s="7" t="str">
-        <f aca="false">IF(G16&lt;275,"UNDER",IF(G16&gt;325,"OVER","IN BAND"))</f>
-        <v>IN BAND</v>
-      </c>
-      <c r="I16" s="7" t="n">
-        <f aca="false">INT(R16)+IF(RANK(S16,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J16" s="8" t="n">
-        <f aca="false">IF(I16=0,"n/a",ROUND(D16/I16,0))</f>
         <v>594</v>
       </c>
-      <c r="K16" s="17" t="n">
+      <c r="H16" s="20" t="n">
+        <f aca="false">ROUND(E16/F16,1)</f>
+        <v>231</v>
+      </c>
+      <c r="I16" s="21" t="n">
         <v>1257732</v>
       </c>
-      <c r="L16" s="18" t="n">
+      <c r="J16" s="22" t="n">
         <v>75026</v>
       </c>
+      <c r="K16" s="23" t="n">
+        <f aca="false">ROUND((40*D16/MAX($D$2:$D$26)+25*E16/MAX($E$2:$E$26)+10*I16/MAX($I$2:$I$26)+10*J16/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>39.6</v>
+      </c>
+      <c r="L16" s="17" t="n">
+        <f aca="false">RANK(K16,$K$2:$K$26)</f>
+        <v>14</v>
+      </c>
       <c r="M16" s="19" t="n">
-        <f aca="false">ROUND((40*D16/MAX($D$2:$D$26)+25*E16/MAX($E$2:$E$26)+10*K16/MAX($K$2:$K$26)+10*L16/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>39.6</v>
-      </c>
-      <c r="N16" s="7" t="n">
-        <f aca="false">RANK(M16,$M$2:$M$26)</f>
-        <v>14</v>
-      </c>
-      <c r="O16" s="20" t="n">
         <v>15</v>
       </c>
-      <c r="P16" s="7" t="n">
-        <f aca="false">O16-N16</f>
-        <v>1</v>
-      </c>
-      <c r="Q16" s="7" t="n">
-        <f aca="false">IF(N16&lt;=7,1,IF(N16&lt;=12,2,IF(N16&lt;=19,3,4)))</f>
+      <c r="N16" s="17" t="n">
+        <f aca="false">M16-L16</f>
+        <v>1</v>
+      </c>
+      <c r="O16" s="17" t="n">
+        <f aca="false">IF(L16&lt;=7,1,IF(L16&lt;=12,2,IF(L16&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
-      <c r="R16" s="21" t="n">
-        <f aca="false">D16*28/SUM($D$2:$D$26)</f>
-        <v>0.903667481662592</v>
-      </c>
-      <c r="S16" s="21" t="n">
-        <f aca="false">R16-INT(R16)</f>
-        <v>0.903667481662592</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D17" s="8" t="n">
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>176</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="D17" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A17,'State Market Summary'!$B$4:$B$54)</f>
         <v>550</v>
       </c>
-      <c r="E17" s="8" t="n">
+      <c r="E17" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A17,'State Market Summary'!$C$4:$C$54)</f>
         <v>185</v>
       </c>
-      <c r="F17" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D17/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="G17" s="8" t="n">
+      <c r="F17" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="18" t="n">
         <f aca="false">ROUND(D17/F17,0)</f>
-        <v>275</v>
-      </c>
-      <c r="H17" s="7" t="str">
-        <f aca="false">IF(G17&lt;275,"UNDER",IF(G17&gt;325,"OVER","IN BAND"))</f>
-        <v>IN BAND</v>
-      </c>
-      <c r="I17" s="7" t="n">
-        <f aca="false">INT(R17)+IF(RANK(S17,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J17" s="8" t="n">
-        <f aca="false">IF(I17=0,"n/a",ROUND(D17/I17,0))</f>
         <v>550</v>
       </c>
-      <c r="K17" s="17" t="n">
+      <c r="H17" s="20" t="n">
+        <f aca="false">ROUND(E17/F17,1)</f>
+        <v>185</v>
+      </c>
+      <c r="I17" s="21" t="n">
         <v>915366</v>
       </c>
-      <c r="L17" s="18" t="n">
+      <c r="J17" s="22" t="n">
         <v>91862</v>
       </c>
+      <c r="K17" s="23" t="n">
+        <f aca="false">ROUND((40*D17/MAX($D$2:$D$26)+25*E17/MAX($E$2:$E$26)+10*I17/MAX($I$2:$I$26)+10*J17/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>37.4</v>
+      </c>
+      <c r="L17" s="17" t="n">
+        <f aca="false">RANK(K17,$K$2:$K$26)</f>
+        <v>16</v>
+      </c>
       <c r="M17" s="19" t="n">
-        <f aca="false">ROUND((40*D17/MAX($D$2:$D$26)+25*E17/MAX($E$2:$E$26)+10*K17/MAX($K$2:$K$26)+10*L17/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>37.4</v>
-      </c>
-      <c r="N17" s="7" t="n">
-        <f aca="false">RANK(M17,$M$2:$M$26)</f>
         <v>16</v>
       </c>
-      <c r="O17" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="P17" s="7" t="n">
-        <f aca="false">O17-N17</f>
+      <c r="N17" s="17" t="n">
+        <f aca="false">M17-L17</f>
         <v>0</v>
       </c>
-      <c r="Q17" s="7" t="n">
-        <f aca="false">IF(N17&lt;=7,1,IF(N17&lt;=12,2,IF(N17&lt;=19,3,4)))</f>
+      <c r="O17" s="17" t="n">
+        <f aca="false">IF(L17&lt;=7,1,IF(L17&lt;=12,2,IF(L17&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
-      <c r="R17" s="21" t="n">
-        <f aca="false">D17*28/SUM($D$2:$D$26)</f>
-        <v>0.836729149687585</v>
-      </c>
-      <c r="S17" s="21" t="n">
-        <f aca="false">R17-INT(R17)</f>
-        <v>0.836729149687585</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="B18" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D18" s="8" t="n">
+      <c r="C18" s="17" t="s">
+        <v>178</v>
+      </c>
+      <c r="D18" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A18,'State Market Summary'!$B$4:$B$54)</f>
         <v>718</v>
       </c>
-      <c r="E18" s="8" t="n">
+      <c r="E18" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A18,'State Market Summary'!$C$4:$C$54)</f>
         <v>241</v>
       </c>
-      <c r="F18" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D18/300,0))</f>
+      <c r="F18" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="18" t="n">
+        <f aca="false">ROUND(D18/F18,0)</f>
+        <v>718</v>
+      </c>
+      <c r="H18" s="20" t="n">
+        <f aca="false">ROUND(E18/F18,1)</f>
+        <v>241</v>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>1191812</v>
+      </c>
+      <c r="J18" s="22" t="n">
+        <v>84033</v>
+      </c>
+      <c r="K18" s="23" t="n">
+        <f aca="false">ROUND((40*D18/MAX($D$2:$D$26)+25*E18/MAX($E$2:$E$26)+10*I18/MAX($I$2:$I$26)+10*J18/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>44.4</v>
+      </c>
+      <c r="L18" s="17" t="n">
+        <f aca="false">RANK(K18,$K$2:$K$26)</f>
+        <v>8</v>
+      </c>
+      <c r="M18" s="19" t="n">
+        <v>17</v>
+      </c>
+      <c r="N18" s="17" t="n">
+        <f aca="false">M18-L18</f>
+        <v>9</v>
+      </c>
+      <c r="O18" s="17" t="n">
+        <f aca="false">IF(L18&lt;=7,1,IF(L18&lt;=12,2,IF(L18&lt;=19,3,4)))</f>
         <v>2</v>
       </c>
-      <c r="G18" s="8" t="n">
-        <f aca="false">ROUND(D18/F18,0)</f>
-        <v>359</v>
-      </c>
-      <c r="H18" s="7" t="str">
-        <f aca="false">IF(G18&lt;275,"UNDER",IF(G18&gt;325,"OVER","IN BAND"))</f>
-        <v>OVER</v>
-      </c>
-      <c r="I18" s="7" t="n">
-        <f aca="false">INT(R18)+IF(RANK(S18,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J18" s="8" t="n">
-        <f aca="false">IF(I18=0,"n/a",ROUND(D18/I18,0))</f>
-        <v>718</v>
-      </c>
-      <c r="K18" s="17" t="n">
-        <v>1191812</v>
-      </c>
-      <c r="L18" s="18" t="n">
-        <v>84033</v>
-      </c>
-      <c r="M18" s="19" t="n">
-        <f aca="false">ROUND((40*D18/MAX($D$2:$D$26)+25*E18/MAX($E$2:$E$26)+10*K18/MAX($K$2:$K$26)+10*L18/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>44.4</v>
-      </c>
-      <c r="N18" s="7" t="n">
-        <f aca="false">RANK(M18,$M$2:$M$26)</f>
-        <v>8</v>
-      </c>
-      <c r="O18" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="P18" s="7" t="n">
-        <f aca="false">O18-N18</f>
-        <v>9</v>
-      </c>
-      <c r="Q18" s="7" t="n">
-        <f aca="false">IF(N18&lt;=7,1,IF(N18&lt;=12,2,IF(N18&lt;=19,3,4)))</f>
-        <v>2</v>
-      </c>
-      <c r="R18" s="21" t="n">
-        <f aca="false">D18*28/SUM($D$2:$D$26)</f>
-        <v>1.09231187177397</v>
-      </c>
-      <c r="S18" s="21" t="n">
-        <f aca="false">R18-INT(R18)</f>
-        <v>0.0923118717739744</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="D19" s="8" t="n">
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="D19" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A19,'State Market Summary'!$B$4:$B$54)</f>
         <v>462</v>
       </c>
-      <c r="E19" s="8" t="n">
+      <c r="E19" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A19,'State Market Summary'!$C$4:$C$54)</f>
         <v>174</v>
       </c>
-      <c r="F19" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D19/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="G19" s="8" t="n">
+      <c r="F19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="18" t="n">
         <f aca="false">ROUND(D19/F19,0)</f>
-        <v>231</v>
-      </c>
-      <c r="H19" s="7" t="str">
-        <f aca="false">IF(G19&lt;275,"UNDER",IF(G19&gt;325,"OVER","IN BAND"))</f>
-        <v>UNDER</v>
-      </c>
-      <c r="I19" s="7" t="n">
-        <f aca="false">INT(R19)+IF(RANK(S19,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J19" s="8" t="n">
-        <f aca="false">IF(I19=0,"n/a",ROUND(D19/I19,0))</f>
         <v>462</v>
       </c>
-      <c r="K19" s="17" t="n">
+      <c r="H19" s="20" t="n">
+        <f aca="false">ROUND(E19/F19,1)</f>
+        <v>174</v>
+      </c>
+      <c r="I19" s="21" t="n">
         <v>772926</v>
       </c>
-      <c r="L19" s="18" t="n">
+      <c r="J19" s="22" t="n">
         <v>60048</v>
       </c>
+      <c r="K19" s="23" t="n">
+        <f aca="false">ROUND((40*D19/MAX($D$2:$D$26)+25*E19/MAX($E$2:$E$26)+10*I19/MAX($I$2:$I$26)+10*J19/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>30.1</v>
+      </c>
+      <c r="L19" s="17" t="n">
+        <f aca="false">RANK(K19,$K$2:$K$26)</f>
+        <v>21</v>
+      </c>
       <c r="M19" s="19" t="n">
-        <f aca="false">ROUND((40*D19/MAX($D$2:$D$26)+25*E19/MAX($E$2:$E$26)+10*K19/MAX($K$2:$K$26)+10*L19/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>30.1</v>
-      </c>
-      <c r="N19" s="7" t="n">
-        <f aca="false">RANK(M19,$M$2:$M$26)</f>
-        <v>21</v>
-      </c>
-      <c r="O19" s="20" t="n">
         <v>18</v>
       </c>
-      <c r="P19" s="7" t="n">
-        <f aca="false">O19-N19</f>
+      <c r="N19" s="17" t="n">
+        <f aca="false">M19-L19</f>
         <v>-3</v>
       </c>
-      <c r="Q19" s="7" t="n">
-        <f aca="false">IF(N19&lt;=7,1,IF(N19&lt;=12,2,IF(N19&lt;=19,3,4)))</f>
+      <c r="O19" s="17" t="n">
+        <f aca="false">IF(L19&lt;=7,1,IF(L19&lt;=12,2,IF(L19&lt;=19,3,4)))</f>
         <v>4</v>
       </c>
-      <c r="R19" s="21" t="n">
-        <f aca="false">D19*28/SUM($D$2:$D$26)</f>
-        <v>0.702852485737571</v>
-      </c>
-      <c r="S19" s="21" t="n">
-        <f aca="false">R19-INT(R19)</f>
-        <v>0.702852485737571</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D20" s="8" t="n">
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="D20" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A20,'State Market Summary'!$B$4:$B$54)</f>
         <v>477</v>
       </c>
-      <c r="E20" s="8" t="n">
+      <c r="E20" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A20,'State Market Summary'!$C$4:$C$54)</f>
         <v>176</v>
       </c>
-      <c r="F20" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D20/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="G20" s="8" t="n">
+      <c r="F20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G20" s="18" t="n">
         <f aca="false">ROUND(D20/F20,0)</f>
-        <v>239</v>
-      </c>
-      <c r="H20" s="7" t="str">
-        <f aca="false">IF(G20&lt;275,"UNDER",IF(G20&gt;325,"OVER","IN BAND"))</f>
-        <v>UNDER</v>
-      </c>
-      <c r="I20" s="7" t="n">
-        <f aca="false">INT(R20)+IF(RANK(S20,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J20" s="8" t="n">
-        <f aca="false">IF(I20=0,"n/a",ROUND(D20/I20,0))</f>
         <v>477</v>
       </c>
-      <c r="K20" s="17" t="n">
+      <c r="H20" s="20" t="n">
+        <f aca="false">ROUND(E20/F20,1)</f>
+        <v>176</v>
+      </c>
+      <c r="I20" s="21" t="n">
         <v>739152</v>
       </c>
-      <c r="L20" s="18" t="n">
+      <c r="J20" s="22" t="n">
         <v>59699</v>
       </c>
+      <c r="K20" s="23" t="n">
+        <f aca="false">ROUND((40*D20/MAX($D$2:$D$26)+25*E20/MAX($E$2:$E$26)+10*I20/MAX($I$2:$I$26)+10*J20/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>30.5</v>
+      </c>
+      <c r="L20" s="17" t="n">
+        <f aca="false">RANK(K20,$K$2:$K$26)</f>
+        <v>20</v>
+      </c>
       <c r="M20" s="19" t="n">
-        <f aca="false">ROUND((40*D20/MAX($D$2:$D$26)+25*E20/MAX($E$2:$E$26)+10*K20/MAX($K$2:$K$26)+10*L20/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>30.5</v>
-      </c>
-      <c r="N20" s="7" t="n">
-        <f aca="false">RANK(M20,$M$2:$M$26)</f>
-        <v>20</v>
-      </c>
-      <c r="O20" s="20" t="n">
         <v>19</v>
       </c>
-      <c r="P20" s="7" t="n">
-        <f aca="false">O20-N20</f>
+      <c r="N20" s="17" t="n">
+        <f aca="false">M20-L20</f>
         <v>-1</v>
       </c>
-      <c r="Q20" s="7" t="n">
-        <f aca="false">IF(N20&lt;=7,1,IF(N20&lt;=12,2,IF(N20&lt;=19,3,4)))</f>
+      <c r="O20" s="17" t="n">
+        <f aca="false">IF(L20&lt;=7,1,IF(L20&lt;=12,2,IF(L20&lt;=19,3,4)))</f>
         <v>4</v>
       </c>
-      <c r="R20" s="21" t="n">
-        <f aca="false">D20*28/SUM($D$2:$D$26)</f>
-        <v>0.725672371638142</v>
-      </c>
-      <c r="S20" s="21" t="n">
-        <f aca="false">R20-INT(R20)</f>
-        <v>0.725672371638142</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="7" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D21" s="8" t="n">
+      <c r="C21" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="D21" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A21,'State Market Summary'!$B$4:$B$54)</f>
         <v>442</v>
       </c>
-      <c r="E21" s="8" t="n">
+      <c r="E21" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A21,'State Market Summary'!$C$4:$C$54)</f>
         <v>111</v>
       </c>
-      <c r="F21" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D21/300,0))</f>
-        <v>1</v>
-      </c>
-      <c r="G21" s="8" t="n">
+      <c r="F21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="18" t="n">
         <f aca="false">ROUND(D21/F21,0)</f>
         <v>442</v>
       </c>
-      <c r="H21" s="7" t="str">
-        <f aca="false">IF(G21&lt;275,"UNDER",IF(G21&gt;325,"OVER","IN BAND"))</f>
-        <v>OVER</v>
-      </c>
-      <c r="I21" s="7" t="n">
-        <f aca="false">INT(R21)+IF(RANK(S21,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J21" s="8" t="n">
-        <f aca="false">IF(I21=0,"n/a",ROUND(D21/I21,0))</f>
-        <v>442</v>
-      </c>
-      <c r="K21" s="17" t="n">
+      <c r="H21" s="20" t="n">
+        <f aca="false">ROUND(E21/F21,1)</f>
+        <v>111</v>
+      </c>
+      <c r="I21" s="21" t="n">
         <v>663850</v>
       </c>
-      <c r="L21" s="18" t="n">
+      <c r="J21" s="22" t="n">
         <v>70489</v>
       </c>
+      <c r="K21" s="23" t="n">
+        <f aca="false">ROUND((40*D21/MAX($D$2:$D$26)+25*E21/MAX($E$2:$E$26)+10*I21/MAX($I$2:$I$26)+10*J21/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>27.8</v>
+      </c>
+      <c r="L21" s="17" t="n">
+        <f aca="false">RANK(K21,$K$2:$K$26)</f>
+        <v>22</v>
+      </c>
       <c r="M21" s="19" t="n">
-        <f aca="false">ROUND((40*D21/MAX($D$2:$D$26)+25*E21/MAX($E$2:$E$26)+10*K21/MAX($K$2:$K$26)+10*L21/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>27.8</v>
-      </c>
-      <c r="N21" s="7" t="n">
-        <f aca="false">RANK(M21,$M$2:$M$26)</f>
-        <v>22</v>
-      </c>
-      <c r="O21" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="P21" s="7" t="n">
-        <f aca="false">O21-N21</f>
+      <c r="N21" s="17" t="n">
+        <f aca="false">M21-L21</f>
         <v>-2</v>
       </c>
-      <c r="Q21" s="7" t="n">
-        <f aca="false">IF(N21&lt;=7,1,IF(N21&lt;=12,2,IF(N21&lt;=19,3,4)))</f>
+      <c r="O21" s="17" t="n">
+        <f aca="false">IF(L21&lt;=7,1,IF(L21&lt;=12,2,IF(L21&lt;=19,3,4)))</f>
         <v>4</v>
       </c>
-      <c r="R21" s="21" t="n">
-        <f aca="false">D21*28/SUM($D$2:$D$26)</f>
-        <v>0.672425971203477</v>
-      </c>
-      <c r="S21" s="21" t="n">
-        <f aca="false">R21-INT(R21)</f>
-        <v>0.672425971203477</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="17" t="s">
+        <v>135</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>134</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="D22" s="8" t="n">
+      <c r="C22" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A22,'State Market Summary'!$B$4:$B$54)</f>
         <v>478</v>
       </c>
-      <c r="E22" s="8" t="n">
+      <c r="E22" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A22,'State Market Summary'!$C$4:$C$54)</f>
         <v>137</v>
       </c>
-      <c r="F22" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D22/300,0))</f>
+      <c r="F22" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G22" s="18" t="n">
+        <f aca="false">ROUND(D22/F22,0)</f>
+        <v>478</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <f aca="false">ROUND(E22/F22,1)</f>
+        <v>137</v>
+      </c>
+      <c r="I22" s="21" t="n">
+        <v>794462</v>
+      </c>
+      <c r="J22" s="22" t="n">
+        <v>97828</v>
+      </c>
+      <c r="K22" s="23" t="n">
+        <f aca="false">ROUND((40*D22/MAX($D$2:$D$26)+25*E22/MAX($E$2:$E$26)+10*I22/MAX($I$2:$I$26)+10*J22/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>33.6</v>
+      </c>
+      <c r="L22" s="17" t="n">
+        <f aca="false">RANK(K22,$K$2:$K$26)</f>
+        <v>19</v>
+      </c>
+      <c r="M22" s="19" t="n">
+        <v>21</v>
+      </c>
+      <c r="N22" s="17" t="n">
+        <f aca="false">M22-L22</f>
         <v>2</v>
       </c>
-      <c r="G22" s="8" t="n">
-        <f aca="false">ROUND(D22/F22,0)</f>
-        <v>239</v>
-      </c>
-      <c r="H22" s="7" t="str">
-        <f aca="false">IF(G22&lt;275,"UNDER",IF(G22&gt;325,"OVER","IN BAND"))</f>
-        <v>UNDER</v>
-      </c>
-      <c r="I22" s="7" t="n">
-        <f aca="false">INT(R22)+IF(RANK(S22,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J22" s="8" t="n">
-        <f aca="false">IF(I22=0,"n/a",ROUND(D22/I22,0))</f>
-        <v>478</v>
-      </c>
-      <c r="K22" s="17" t="n">
-        <v>794462</v>
-      </c>
-      <c r="L22" s="18" t="n">
-        <v>97828</v>
-      </c>
-      <c r="M22" s="19" t="n">
-        <f aca="false">ROUND((40*D22/MAX($D$2:$D$26)+25*E22/MAX($E$2:$E$26)+10*K22/MAX($K$2:$K$26)+10*L22/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>33.6</v>
-      </c>
-      <c r="N22" s="7" t="n">
-        <f aca="false">RANK(M22,$M$2:$M$26)</f>
-        <v>19</v>
-      </c>
-      <c r="O22" s="20" t="n">
-        <v>21</v>
-      </c>
-      <c r="P22" s="7" t="n">
-        <f aca="false">O22-N22</f>
-        <v>2</v>
-      </c>
-      <c r="Q22" s="7" t="n">
-        <f aca="false">IF(N22&lt;=7,1,IF(N22&lt;=12,2,IF(N22&lt;=19,3,4)))</f>
+      <c r="O22" s="17" t="n">
+        <f aca="false">IF(L22&lt;=7,1,IF(L22&lt;=12,2,IF(L22&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
-      <c r="R22" s="21" t="n">
-        <f aca="false">D22*28/SUM($D$2:$D$26)</f>
-        <v>0.727193697364847</v>
-      </c>
-      <c r="S22" s="21" t="n">
-        <f aca="false">R22-INT(R22)</f>
-        <v>0.727193697364847</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="D23" s="8" t="n">
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="D23" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A23,'State Market Summary'!$B$4:$B$54)</f>
         <v>489</v>
       </c>
-      <c r="E23" s="8" t="n">
+      <c r="E23" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A23,'State Market Summary'!$C$4:$C$54)</f>
         <v>168</v>
       </c>
-      <c r="F23" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D23/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="G23" s="8" t="n">
+      <c r="F23" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" s="18" t="n">
         <f aca="false">ROUND(D23/F23,0)</f>
-        <v>245</v>
-      </c>
-      <c r="H23" s="7" t="str">
-        <f aca="false">IF(G23&lt;275,"UNDER",IF(G23&gt;325,"OVER","IN BAND"))</f>
-        <v>UNDER</v>
-      </c>
-      <c r="I23" s="7" t="n">
-        <f aca="false">INT(R23)+IF(RANK(S23,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J23" s="8" t="n">
-        <f aca="false">IF(I23=0,"n/a",ROUND(D23/I23,0))</f>
         <v>489</v>
       </c>
-      <c r="K23" s="17" t="n">
+      <c r="H23" s="20" t="n">
+        <f aca="false">ROUND(E23/F23,1)</f>
+        <v>168</v>
+      </c>
+      <c r="I23" s="21" t="n">
         <v>860620</v>
       </c>
-      <c r="L23" s="18" t="n">
+      <c r="J23" s="22" t="n">
         <v>94114</v>
       </c>
+      <c r="K23" s="23" t="n">
+        <f aca="false">ROUND((40*D23/MAX($D$2:$D$26)+25*E23/MAX($E$2:$E$26)+10*I23/MAX($I$2:$I$26)+10*J23/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>35</v>
+      </c>
+      <c r="L23" s="17" t="n">
+        <f aca="false">RANK(K23,$K$2:$K$26)</f>
+        <v>18</v>
+      </c>
       <c r="M23" s="19" t="n">
-        <f aca="false">ROUND((40*D23/MAX($D$2:$D$26)+25*E23/MAX($E$2:$E$26)+10*K23/MAX($K$2:$K$26)+10*L23/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>35</v>
-      </c>
-      <c r="N23" s="7" t="n">
-        <f aca="false">RANK(M23,$M$2:$M$26)</f>
-        <v>18</v>
-      </c>
-      <c r="O23" s="20" t="n">
         <v>22</v>
       </c>
-      <c r="P23" s="7" t="n">
-        <f aca="false">O23-N23</f>
+      <c r="N23" s="17" t="n">
+        <f aca="false">M23-L23</f>
         <v>4</v>
       </c>
-      <c r="Q23" s="7" t="n">
-        <f aca="false">IF(N23&lt;=7,1,IF(N23&lt;=12,2,IF(N23&lt;=19,3,4)))</f>
+      <c r="O23" s="17" t="n">
+        <f aca="false">IF(L23&lt;=7,1,IF(L23&lt;=12,2,IF(L23&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
-      <c r="R23" s="21" t="n">
-        <f aca="false">D23*28/SUM($D$2:$D$26)</f>
-        <v>0.743928280358598</v>
-      </c>
-      <c r="S23" s="21" t="n">
-        <f aca="false">R23-INT(R23)</f>
-        <v>0.743928280358598</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="B24" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" s="8" t="n">
+      <c r="C24" s="17" t="s">
+        <v>187</v>
+      </c>
+      <c r="D24" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A24,'State Market Summary'!$B$4:$B$54)</f>
         <v>401</v>
       </c>
-      <c r="E24" s="8" t="n">
+      <c r="E24" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A24,'State Market Summary'!$C$4:$C$54)</f>
         <v>124</v>
       </c>
-      <c r="F24" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D24/300,0))</f>
-        <v>1</v>
-      </c>
-      <c r="G24" s="8" t="n">
+      <c r="F24" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G24" s="18" t="n">
         <f aca="false">ROUND(D24/F24,0)</f>
         <v>401</v>
       </c>
-      <c r="H24" s="7" t="str">
-        <f aca="false">IF(G24&lt;275,"UNDER",IF(G24&gt;325,"OVER","IN BAND"))</f>
-        <v>OVER</v>
-      </c>
-      <c r="I24" s="7" t="n">
-        <f aca="false">INT(R24)+IF(RANK(S24,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
-        <v>1</v>
-      </c>
-      <c r="J24" s="8" t="n">
-        <f aca="false">IF(I24=0,"n/a",ROUND(D24/I24,0))</f>
-        <v>401</v>
-      </c>
-      <c r="K24" s="17" t="n">
+      <c r="H24" s="20" t="n">
+        <f aca="false">ROUND(E24/F24,1)</f>
+        <v>124</v>
+      </c>
+      <c r="I24" s="21" t="n">
         <v>634143</v>
       </c>
-      <c r="L24" s="18" t="n">
+      <c r="J24" s="22" t="n">
         <v>67976</v>
       </c>
+      <c r="K24" s="23" t="n">
+        <f aca="false">ROUND((40*D24/MAX($D$2:$D$26)+25*E24/MAX($E$2:$E$26)+10*I24/MAX($I$2:$I$26)+10*J24/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>26.8</v>
+      </c>
+      <c r="L24" s="17" t="n">
+        <f aca="false">RANK(K24,$K$2:$K$26)</f>
+        <v>23</v>
+      </c>
       <c r="M24" s="19" t="n">
-        <f aca="false">ROUND((40*D24/MAX($D$2:$D$26)+25*E24/MAX($E$2:$E$26)+10*K24/MAX($K$2:$K$26)+10*L24/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>26.8</v>
-      </c>
-      <c r="N24" s="7" t="n">
-        <f aca="false">RANK(M24,$M$2:$M$26)</f>
         <v>23</v>
       </c>
-      <c r="O24" s="20" t="n">
-        <v>23</v>
-      </c>
-      <c r="P24" s="7" t="n">
-        <f aca="false">O24-N24</f>
+      <c r="N24" s="17" t="n">
+        <f aca="false">M24-L24</f>
         <v>0</v>
       </c>
-      <c r="Q24" s="7" t="n">
-        <f aca="false">IF(N24&lt;=7,1,IF(N24&lt;=12,2,IF(N24&lt;=19,3,4)))</f>
+      <c r="O24" s="17" t="n">
+        <f aca="false">IF(L24&lt;=7,1,IF(L24&lt;=12,2,IF(L24&lt;=19,3,4)))</f>
         <v>4</v>
       </c>
-      <c r="R24" s="21" t="n">
-        <f aca="false">D24*28/SUM($D$2:$D$26)</f>
-        <v>0.610051616408585</v>
-      </c>
-      <c r="S24" s="21" t="n">
-        <f aca="false">R24-INT(R24)</f>
-        <v>0.610051616408585</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>191</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="D25" s="8" t="n">
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="D25" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A25,'State Market Summary'!$B$4:$B$54)</f>
         <v>345</v>
       </c>
-      <c r="E25" s="8" t="n">
+      <c r="E25" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A25,'State Market Summary'!$C$4:$C$54)</f>
         <v>111</v>
       </c>
-      <c r="F25" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D25/300,0))</f>
-        <v>1</v>
-      </c>
-      <c r="G25" s="8" t="n">
+      <c r="F25" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" s="18" t="n">
         <f aca="false">ROUND(D25/F25,0)</f>
         <v>345</v>
       </c>
-      <c r="H25" s="7" t="str">
-        <f aca="false">IF(G25&lt;275,"UNDER",IF(G25&gt;325,"OVER","IN BAND"))</f>
-        <v>OVER</v>
-      </c>
-      <c r="I25" s="7" t="n">
-        <f aca="false">INT(R25)+IF(RANK(S25,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
+      <c r="H25" s="20" t="n">
+        <f aca="false">ROUND(E25/F25,1)</f>
+        <v>111</v>
+      </c>
+      <c r="I25" s="21" t="n">
+        <v>528815</v>
+      </c>
+      <c r="J25" s="22" t="n">
+        <v>73245</v>
+      </c>
+      <c r="K25" s="23" t="n">
+        <f aca="false">ROUND((40*D25/MAX($D$2:$D$26)+25*E25/MAX($E$2:$E$26)+10*I25/MAX($I$2:$I$26)+10*J25/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>25</v>
+      </c>
+      <c r="L25" s="17" t="n">
+        <f aca="false">RANK(K25,$K$2:$K$26)</f>
+        <v>24</v>
+      </c>
+      <c r="M25" s="19" t="n">
+        <v>24</v>
+      </c>
+      <c r="N25" s="17" t="n">
+        <f aca="false">M25-L25</f>
         <v>0</v>
       </c>
-      <c r="J25" s="8" t="str">
-        <f aca="false">IF(I25=0,"n/a",ROUND(D25/I25,0))</f>
-        <v>n/a</v>
-      </c>
-      <c r="K25" s="17" t="n">
-        <v>528815</v>
-      </c>
-      <c r="L25" s="18" t="n">
-        <v>73245</v>
-      </c>
-      <c r="M25" s="19" t="n">
-        <f aca="false">ROUND((40*D25/MAX($D$2:$D$26)+25*E25/MAX($E$2:$E$26)+10*K25/MAX($K$2:$K$26)+10*L25/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>25</v>
-      </c>
-      <c r="N25" s="7" t="n">
-        <f aca="false">RANK(M25,$M$2:$M$26)</f>
-        <v>24</v>
-      </c>
-      <c r="O25" s="20" t="n">
-        <v>24</v>
-      </c>
-      <c r="P25" s="7" t="n">
-        <f aca="false">O25-N25</f>
-        <v>0</v>
-      </c>
-      <c r="Q25" s="7" t="n">
-        <f aca="false">IF(N25&lt;=7,1,IF(N25&lt;=12,2,IF(N25&lt;=19,3,4)))</f>
+      <c r="O25" s="17" t="n">
+        <f aca="false">IF(L25&lt;=7,1,IF(L25&lt;=12,2,IF(L25&lt;=19,3,4)))</f>
         <v>4</v>
       </c>
-      <c r="R25" s="21" t="n">
-        <f aca="false">D25*28/SUM($D$2:$D$26)</f>
-        <v>0.524857375713121</v>
-      </c>
-      <c r="S25" s="21" t="n">
-        <f aca="false">R25-INT(R25)</f>
-        <v>0.524857375713121</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="7" t="s">
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B26" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="D26" s="8" t="n">
+      <c r="C26" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="D26" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A26,'State Market Summary'!$B$4:$B$54)</f>
         <v>364</v>
       </c>
-      <c r="E26" s="8" t="n">
+      <c r="E26" s="18" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A26,'State Market Summary'!$C$4:$C$54)</f>
         <v>97</v>
       </c>
-      <c r="F26" s="7" t="n">
-        <f aca="false">MAX(1,ROUND(D26/300,0))</f>
-        <v>1</v>
-      </c>
-      <c r="G26" s="8" t="n">
+      <c r="F26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="18" t="n">
         <f aca="false">ROUND(D26/F26,0)</f>
         <v>364</v>
       </c>
-      <c r="H26" s="7" t="str">
-        <f aca="false">IF(G26&lt;275,"UNDER",IF(G26&gt;325,"OVER","IN BAND"))</f>
-        <v>OVER</v>
-      </c>
-      <c r="I26" s="7" t="n">
-        <f aca="false">INT(R26)+IF(RANK(S26,$S$2:$S$26)&lt;=28-SUMPRODUCT(INT($R$2:$R$26)),1,0)</f>
+      <c r="H26" s="20" t="n">
+        <f aca="false">ROUND(E26/F26,1)</f>
+        <v>97</v>
+      </c>
+      <c r="I26" s="21" t="n">
+        <v>473826</v>
+      </c>
+      <c r="J26" s="22" t="n">
+        <v>65973</v>
+      </c>
+      <c r="K26" s="23" t="n">
+        <f aca="false">ROUND((40*D26/MAX($D$2:$D$26)+25*E26/MAX($E$2:$E$26)+10*I26/MAX($I$2:$I$26)+10*J26/MAX($J$2:$J$26))/85*100,1)</f>
+        <v>23.8</v>
+      </c>
+      <c r="L26" s="17" t="n">
+        <f aca="false">RANK(K26,$K$2:$K$26)</f>
+        <v>25</v>
+      </c>
+      <c r="M26" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="N26" s="17" t="n">
+        <f aca="false">M26-L26</f>
         <v>0</v>
       </c>
-      <c r="J26" s="8" t="str">
-        <f aca="false">IF(I26=0,"n/a",ROUND(D26/I26,0))</f>
-        <v>n/a</v>
-      </c>
-      <c r="K26" s="17" t="n">
-        <v>473826</v>
-      </c>
-      <c r="L26" s="18" t="n">
-        <v>65973</v>
-      </c>
-      <c r="M26" s="19" t="n">
-        <f aca="false">ROUND((40*D26/MAX($D$2:$D$26)+25*E26/MAX($E$2:$E$26)+10*K26/MAX($K$2:$K$26)+10*L26/MAX($L$2:$L$26))/85*100,1)</f>
-        <v>23.8</v>
-      </c>
-      <c r="N26" s="7" t="n">
-        <f aca="false">RANK(M26,$M$2:$M$26)</f>
-        <v>25</v>
-      </c>
-      <c r="O26" s="20" t="n">
-        <v>25</v>
-      </c>
-      <c r="P26" s="7" t="n">
-        <f aca="false">O26-N26</f>
-        <v>0</v>
-      </c>
-      <c r="Q26" s="7" t="n">
-        <f aca="false">IF(N26&lt;=7,1,IF(N26&lt;=12,2,IF(N26&lt;=19,3,4)))</f>
+      <c r="O26" s="17" t="n">
+        <f aca="false">IF(L26&lt;=7,1,IF(L26&lt;=12,2,IF(L26&lt;=19,3,4)))</f>
         <v>4</v>
       </c>
-      <c r="R26" s="21" t="n">
-        <f aca="false">D26*28/SUM($D$2:$D$26)</f>
-        <v>0.553762564520511</v>
-      </c>
-      <c r="S26" s="21" t="n">
-        <f aca="false">R26-INT(R26)</f>
-        <v>0.553762564520511</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15" t="n">
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="24"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="25" t="n">
         <f aca="false">SUM(D2:D26)</f>
         <v>18405</v>
       </c>
-      <c r="E27" s="15" t="n">
+      <c r="E27" s="25" t="n">
         <f aca="false">SUM(E2:E26)</f>
         <v>5862</v>
       </c>
-      <c r="F27" s="15" t="n">
+      <c r="F27" s="25" t="n">
         <f aca="false">SUM(F2:F26)</f>
-        <v>61</v>
-      </c>
-      <c r="G27" s="15" t="n">
+        <v>28</v>
+      </c>
+      <c r="G27" s="25" t="n">
         <f aca="false">ROUND(D27/F27,0)</f>
-        <v>302</v>
-      </c>
-      <c r="H27" s="15"/>
-      <c r="I27" s="15" t="n">
+        <v>657</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <f aca="false">ROUND(E27/F27,1)</f>
+        <v>209.4</v>
+      </c>
+      <c r="I27" s="25" t="n">
         <f aca="false">SUM(I2:I26)</f>
-        <v>28</v>
-      </c>
-      <c r="J27" s="15"/>
-      <c r="K27" s="15" t="n">
-        <f aca="false">SUM(K2:K26)</f>
         <v>30870179</v>
       </c>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="15"/>
-      <c r="O27" s="15"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="15"/>
-      <c r="R27" s="15"/>
-      <c r="S27" s="15"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="24"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="24"/>
     </row>
     <row r="29" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -7043,12 +6596,10 @@
       <c r="M29" s="9"/>
       <c r="N29" s="9"/>
       <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A29:Q29"/>
+    <mergeCell ref="A29:O29"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7077,109 +6628,109 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>196</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="B2" s="22" t="s">
-        <v>201</v>
+        <v>197</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>198</v>
       </c>
       <c r="C2" s="8" t="n">
-        <f aca="false">SUMIF('Territory Plan'!$Q$2:$Q$26,1,'Territory Plan'!$F$2:$F$26)</f>
-        <v>26</v>
+        <f aca="false">SUMIF('Territory Plan'!$O$2:$O$26,1,'Territory Plan'!$F$2:$F$26)</f>
+        <v>10</v>
       </c>
       <c r="D2" s="8" t="n">
         <f aca="false">SUM($C$2:$C2)</f>
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="B3" s="22" t="s">
-        <v>204</v>
+        <v>200</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>201</v>
       </c>
       <c r="C3" s="8" t="n">
-        <f aca="false">SUMIF('Territory Plan'!$Q$2:$Q$26,2,'Territory Plan'!$F$2:$F$26)</f>
-        <v>13</v>
+        <f aca="false">SUMIF('Territory Plan'!$O$2:$O$26,2,'Territory Plan'!$F$2:$F$26)</f>
+        <v>5</v>
       </c>
       <c r="D3" s="8" t="n">
         <f aca="false">SUM($C$2:$C3)</f>
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B4" s="22" t="s">
-        <v>207</v>
+        <v>203</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>204</v>
       </c>
       <c r="C4" s="8" t="n">
-        <f aca="false">SUMIF('Territory Plan'!$Q$2:$Q$26,3,'Territory Plan'!$F$2:$F$26)</f>
-        <v>14</v>
+        <f aca="false">SUMIF('Territory Plan'!$O$2:$O$26,3,'Territory Plan'!$F$2:$F$26)</f>
+        <v>7</v>
       </c>
       <c r="D4" s="8" t="n">
         <f aca="false">SUM($C$2:$C4)</f>
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>210</v>
+        <v>206</v>
+      </c>
+      <c r="B5" s="27" t="s">
+        <v>207</v>
       </c>
       <c r="C5" s="8" t="n">
-        <f aca="false">SUMIF('Territory Plan'!$Q$2:$Q$26,4,'Territory Plan'!$F$2:$F$26)</f>
-        <v>8</v>
+        <f aca="false">SUMIF('Territory Plan'!$O$2:$O$26,4,'Territory Plan'!$F$2:$F$26)</f>
+        <v>6</v>
       </c>
       <c r="D5" s="8" t="n">
         <f aca="false">SUM($C$2:$C5)</f>
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
-        <v>212</v>
-      </c>
-      <c r="B7" s="23"/>
-      <c r="C7" s="23"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="A7" s="28" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -7209,1495 +6760,1470 @@
   <dimension ref="E1:R31"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="11" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="7"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E1" s="24" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E1" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
+      <c r="N1" s="10"/>
+      <c r="O1" s="10"/>
+      <c r="P1" s="10"/>
+      <c r="Q1" s="10"/>
+      <c r="R1" s="10"/>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="J2" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="K2" s="30" t="s">
+        <v>213</v>
+      </c>
+      <c r="L2" s="30" t="s">
         <v>214</v>
       </c>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
-      <c r="M1" s="24"/>
-      <c r="N1" s="24"/>
-      <c r="O1" s="24"/>
-      <c r="P1" s="24"/>
-      <c r="Q1" s="24"/>
-      <c r="R1" s="24"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J2" s="25" t="s">
+      <c r="N2" s="30" t="s">
         <v>215</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="O2" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="P2" s="30" t="s">
         <v>216</v>
       </c>
-      <c r="L2" s="26" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E3" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="N2" s="26" t="s">
+      <c r="I3" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="O2" s="26" t="s">
-        <v>218</v>
-      </c>
-      <c r="P2" s="26" t="s">
+      <c r="J3" s="16" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E3" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="H3" s="16" t="s">
+      <c r="K3" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="L3" s="16" t="s">
         <v>221</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="M3" s="16" t="s">
         <v>222</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="N3" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="L3" s="16" t="s">
+      <c r="O3" s="16" t="s">
         <v>224</v>
       </c>
-      <c r="M3" s="16" t="s">
+      <c r="P3" s="16" t="s">
         <v>225</v>
       </c>
-      <c r="N3" s="16" t="s">
+      <c r="Q3" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="O3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="P3" s="16" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E4" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="Q3" s="16" t="s">
-        <v>229</v>
-      </c>
-      <c r="R3" s="16" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E4" s="27" t="s">
-        <v>231</v>
-      </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T01",'State Market Summary'!$B$4:$B$54)</f>
         <v>1660</v>
       </c>
-      <c r="G4" s="28" t="n">
+      <c r="G4" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T01",'State Market Summary'!$C$4:$C$54)</f>
         <v>540</v>
       </c>
-      <c r="H4" s="28" t="n">
+      <c r="H4" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T01",'State Market Summary'!$N$4:$N$54)</f>
         <v>585</v>
       </c>
-      <c r="I4" s="28" t="n">
+      <c r="I4" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T01",'State Market Summary'!$O$4:$O$54)</f>
         <v>127</v>
       </c>
-      <c r="J4" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F4/300,0))</f>
-        <v>6</v>
-      </c>
-      <c r="K4" s="28" t="n">
+      <c r="J4" s="31" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" s="8" t="n">
         <f aca="false">ROUND(F4/J4,0)</f>
-        <v>277</v>
-      </c>
-      <c r="L4" s="30" t="n">
+        <v>553</v>
+      </c>
+      <c r="L4" s="32" t="n">
         <f aca="false">ROUND(G4/J4,1)</f>
-        <v>90</v>
-      </c>
-      <c r="M4" s="31" t="n">
+        <v>180</v>
+      </c>
+      <c r="M4" s="33" t="n">
         <f aca="false">H4/F4</f>
         <v>0.352409638554217</v>
       </c>
-      <c r="N4" s="32" t="n">
+      <c r="N4" s="34" t="n">
         <v>3090173</v>
       </c>
-      <c r="O4" s="33" t="n">
+      <c r="O4" s="35" t="n">
         <v>78473</v>
       </c>
-      <c r="P4" s="34" t="n">
+      <c r="P4" s="36" t="n">
         <v>31.7</v>
       </c>
-      <c r="Q4" s="35" t="n">
+      <c r="Q4" s="37" t="n">
         <f aca="false">ROUND((20*100*(K4-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L4-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N4-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O4-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>40.9</v>
-      </c>
-      <c r="R4" s="27" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="R4" s="7" t="n">
         <f aca="false">RANK(Q4,$Q$4:$Q$28)</f>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E5" s="27" t="s">
-        <v>232</v>
-      </c>
-      <c r="F5" s="28" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E5" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="F5" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T02",'State Market Summary'!$B$4:$B$54)</f>
         <v>1579</v>
       </c>
-      <c r="G5" s="28" t="n">
+      <c r="G5" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T02",'State Market Summary'!$C$4:$C$54)</f>
         <v>688</v>
       </c>
-      <c r="H5" s="28" t="n">
+      <c r="H5" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T02",'State Market Summary'!$N$4:$N$54)</f>
         <v>857</v>
       </c>
-      <c r="I5" s="28" t="n">
+      <c r="I5" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T02",'State Market Summary'!$O$4:$O$54)</f>
         <v>267</v>
       </c>
-      <c r="J5" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F5/300,0))</f>
-        <v>5</v>
-      </c>
-      <c r="K5" s="28" t="n">
+      <c r="J5" s="31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="8" t="n">
         <f aca="false">ROUND(F5/J5,0)</f>
-        <v>316</v>
-      </c>
-      <c r="L5" s="30" t="n">
+        <v>790</v>
+      </c>
+      <c r="L5" s="32" t="n">
         <f aca="false">ROUND(G5/J5,1)</f>
-        <v>137.6</v>
-      </c>
-      <c r="M5" s="31" t="n">
+        <v>344</v>
+      </c>
+      <c r="M5" s="33" t="n">
         <f aca="false">H5/F5</f>
         <v>0.542748575047498</v>
       </c>
-      <c r="N5" s="32" t="n">
+      <c r="N5" s="34" t="n">
         <v>3819366</v>
       </c>
-      <c r="O5" s="33" t="n">
+      <c r="O5" s="35" t="n">
         <v>97969</v>
       </c>
-      <c r="P5" s="34" t="n">
+      <c r="P5" s="36" t="n">
         <v>34.9</v>
       </c>
-      <c r="Q5" s="35" t="n">
+      <c r="Q5" s="37" t="n">
         <f aca="false">ROUND((20*100*(K5-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L5-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N5-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O5-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>88.1</v>
-      </c>
-      <c r="R5" s="27" t="n">
+        <v>80</v>
+      </c>
+      <c r="R5" s="7" t="n">
         <f aca="false">RANK(Q5,$Q$4:$Q$28)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E6" s="27" t="s">
-        <v>233</v>
-      </c>
-      <c r="F6" s="28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E6" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="F6" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T03",'State Market Summary'!$B$4:$B$54)</f>
         <v>1030</v>
       </c>
-      <c r="G6" s="28" t="n">
+      <c r="G6" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T03",'State Market Summary'!$C$4:$C$54)</f>
         <v>404</v>
       </c>
-      <c r="H6" s="28" t="n">
+      <c r="H6" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T03",'State Market Summary'!$N$4:$N$54)</f>
         <v>414</v>
       </c>
-      <c r="I6" s="28" t="n">
+      <c r="I6" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T03",'State Market Summary'!$O$4:$O$54)</f>
         <v>149</v>
       </c>
-      <c r="J6" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F6/300,0))</f>
-        <v>3</v>
-      </c>
-      <c r="K6" s="28" t="n">
+      <c r="J6" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="8" t="n">
         <f aca="false">ROUND(F6/J6,0)</f>
-        <v>343</v>
-      </c>
-      <c r="L6" s="30" t="n">
+        <v>1030</v>
+      </c>
+      <c r="L6" s="32" t="n">
         <f aca="false">ROUND(G6/J6,1)</f>
-        <v>134.7</v>
-      </c>
-      <c r="M6" s="31" t="n">
+        <v>404</v>
+      </c>
+      <c r="M6" s="33" t="n">
         <f aca="false">H6/F6</f>
         <v>0.401941747572816</v>
       </c>
-      <c r="N6" s="32" t="n">
+      <c r="N6" s="34" t="n">
         <v>1726412</v>
       </c>
-      <c r="O6" s="33" t="n">
+      <c r="O6" s="35" t="n">
         <v>89542</v>
       </c>
-      <c r="P6" s="34" t="n">
+      <c r="P6" s="36" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q6" s="35" t="n">
+      <c r="Q6" s="37" t="n">
         <f aca="false">ROUND((20*100*(K6-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L6-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N6-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O6-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>80</v>
-      </c>
-      <c r="R6" s="27" t="n">
+        <v>89.5</v>
+      </c>
+      <c r="R6" s="7" t="n">
         <f aca="false">RANK(Q6,$Q$4:$Q$28)</f>
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E7" s="27" t="s">
-        <v>234</v>
-      </c>
-      <c r="F7" s="28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E7" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="F7" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T04",'State Market Summary'!$B$4:$B$54)</f>
         <v>795</v>
       </c>
-      <c r="G7" s="28" t="n">
+      <c r="G7" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T04",'State Market Summary'!$C$4:$C$54)</f>
         <v>178</v>
       </c>
-      <c r="H7" s="28" t="n">
+      <c r="H7" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T04",'State Market Summary'!$N$4:$N$54)</f>
         <v>347</v>
       </c>
-      <c r="I7" s="28" t="n">
+      <c r="I7" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T04",'State Market Summary'!$O$4:$O$54)</f>
         <v>74</v>
       </c>
-      <c r="J7" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F7/300,0))</f>
-        <v>3</v>
-      </c>
-      <c r="K7" s="28" t="n">
+      <c r="J7" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="8" t="n">
         <f aca="false">ROUND(F7/J7,0)</f>
-        <v>265</v>
-      </c>
-      <c r="L7" s="30" t="n">
+        <v>795</v>
+      </c>
+      <c r="L7" s="32" t="n">
         <f aca="false">ROUND(G7/J7,1)</f>
-        <v>59.3</v>
-      </c>
-      <c r="M7" s="31" t="n">
+        <v>178</v>
+      </c>
+      <c r="M7" s="33" t="n">
         <f aca="false">H7/F7</f>
         <v>0.436477987421384</v>
       </c>
-      <c r="N7" s="32" t="n">
+      <c r="N7" s="34" t="n">
         <v>1089150</v>
       </c>
-      <c r="O7" s="33" t="n">
+      <c r="O7" s="35" t="n">
         <v>71229</v>
       </c>
-      <c r="P7" s="34" t="n">
+      <c r="P7" s="36" t="n">
         <v>30.4</v>
       </c>
-      <c r="Q7" s="35" t="n">
+      <c r="Q7" s="37" t="n">
         <f aca="false">ROUND((20*100*(K7-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L7-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N7-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O7-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>8.5</v>
-      </c>
-      <c r="R7" s="27" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="R7" s="7" t="n">
         <f aca="false">RANK(Q7,$Q$4:$Q$28)</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E8" s="27" t="s">
-        <v>235</v>
-      </c>
-      <c r="F8" s="28" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E8" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="F8" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T05",'State Market Summary'!$B$4:$B$54)</f>
         <v>1107</v>
       </c>
-      <c r="G8" s="28" t="n">
+      <c r="G8" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T05",'State Market Summary'!$C$4:$C$54)</f>
         <v>273</v>
       </c>
-      <c r="H8" s="28" t="n">
+      <c r="H8" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T05",'State Market Summary'!$N$4:$N$54)</f>
         <v>278</v>
       </c>
-      <c r="I8" s="28" t="n">
+      <c r="I8" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T05",'State Market Summary'!$O$4:$O$54)</f>
         <v>120</v>
       </c>
-      <c r="J8" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F8/300,0))</f>
-        <v>4</v>
-      </c>
-      <c r="K8" s="28" t="n">
+      <c r="J8" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="8" t="n">
         <f aca="false">ROUND(F8/J8,0)</f>
-        <v>277</v>
-      </c>
-      <c r="L8" s="30" t="n">
+        <v>1107</v>
+      </c>
+      <c r="L8" s="32" t="n">
         <f aca="false">ROUND(G8/J8,1)</f>
-        <v>68.3</v>
-      </c>
-      <c r="M8" s="31" t="n">
+        <v>273</v>
+      </c>
+      <c r="M8" s="33" t="n">
         <f aca="false">H8/F8</f>
         <v>0.251129177958446</v>
       </c>
-      <c r="N8" s="32" t="n">
+      <c r="N8" s="34" t="n">
         <v>1780020</v>
       </c>
-      <c r="O8" s="33" t="n">
+      <c r="O8" s="35" t="n">
         <v>71602</v>
       </c>
-      <c r="P8" s="34" t="n">
+      <c r="P8" s="36" t="n">
         <v>32.2</v>
       </c>
-      <c r="Q8" s="35" t="n">
+      <c r="Q8" s="37" t="n">
         <f aca="false">ROUND((20*100*(K8-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L8-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N8-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O8-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>18.7</v>
-      </c>
-      <c r="R8" s="27" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="R8" s="7" t="n">
         <f aca="false">RANK(Q8,$Q$4:$Q$28)</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E9" s="27" t="s">
-        <v>236</v>
-      </c>
-      <c r="F9" s="28" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E9" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F9" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T06",'State Market Summary'!$B$4:$B$54)</f>
         <v>1035</v>
       </c>
-      <c r="G9" s="28" t="n">
+      <c r="G9" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T06",'State Market Summary'!$C$4:$C$54)</f>
         <v>338</v>
       </c>
-      <c r="H9" s="28" t="n">
+      <c r="H9" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T06",'State Market Summary'!$N$4:$N$54)</f>
         <v>442</v>
       </c>
-      <c r="I9" s="28" t="n">
+      <c r="I9" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T06",'State Market Summary'!$O$4:$O$54)</f>
         <v>115</v>
       </c>
-      <c r="J9" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F9/300,0))</f>
-        <v>3</v>
-      </c>
-      <c r="K9" s="28" t="n">
+      <c r="J9" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="8" t="n">
         <f aca="false">ROUND(F9/J9,0)</f>
-        <v>345</v>
-      </c>
-      <c r="L9" s="30" t="n">
+        <v>1035</v>
+      </c>
+      <c r="L9" s="32" t="n">
         <f aca="false">ROUND(G9/J9,1)</f>
-        <v>112.7</v>
-      </c>
-      <c r="M9" s="31" t="n">
+        <v>338</v>
+      </c>
+      <c r="M9" s="33" t="n">
         <f aca="false">H9/F9</f>
         <v>0.427053140096618</v>
       </c>
-      <c r="N9" s="32" t="n">
+      <c r="N9" s="34" t="n">
         <v>1985432</v>
       </c>
-      <c r="O9" s="33" t="n">
+      <c r="O9" s="35" t="n">
         <v>89604</v>
       </c>
-      <c r="P9" s="34" t="n">
+      <c r="P9" s="36" t="n">
         <v>37.1</v>
       </c>
-      <c r="Q9" s="35" t="n">
+      <c r="Q9" s="37" t="n">
         <f aca="false">ROUND((20*100*(K9-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L9-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N9-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O9-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>64.2</v>
-      </c>
-      <c r="R9" s="27" t="n">
+        <v>77.5</v>
+      </c>
+      <c r="R9" s="7" t="n">
         <f aca="false">RANK(Q9,$Q$4:$Q$28)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E10" s="27" t="s">
-        <v>237</v>
-      </c>
-      <c r="F10" s="28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E10" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="F10" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T07",'State Market Summary'!$B$4:$B$54)</f>
         <v>746</v>
       </c>
-      <c r="G10" s="28" t="n">
+      <c r="G10" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T07",'State Market Summary'!$C$4:$C$54)</f>
         <v>207</v>
       </c>
-      <c r="H10" s="28" t="n">
+      <c r="H10" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T07",'State Market Summary'!$N$4:$N$54)</f>
         <v>441</v>
       </c>
-      <c r="I10" s="28" t="n">
+      <c r="I10" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T07",'State Market Summary'!$O$4:$O$54)</f>
         <v>96</v>
       </c>
-      <c r="J10" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F10/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="K10" s="28" t="n">
+      <c r="J10" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="8" t="n">
         <f aca="false">ROUND(F10/J10,0)</f>
-        <v>373</v>
-      </c>
-      <c r="L10" s="30" t="n">
+        <v>746</v>
+      </c>
+      <c r="L10" s="32" t="n">
         <f aca="false">ROUND(G10/J10,1)</f>
-        <v>103.5</v>
-      </c>
-      <c r="M10" s="31" t="n">
+        <v>207</v>
+      </c>
+      <c r="M10" s="33" t="n">
         <f aca="false">H10/F10</f>
         <v>0.591152815013405</v>
       </c>
-      <c r="N10" s="32" t="n">
+      <c r="N10" s="34" t="n">
         <v>910821</v>
       </c>
-      <c r="O10" s="33" t="n">
+      <c r="O10" s="35" t="n">
         <v>72965</v>
       </c>
-      <c r="P10" s="34" t="n">
+      <c r="P10" s="36" t="n">
         <v>31.3</v>
       </c>
-      <c r="Q10" s="35" t="n">
+      <c r="Q10" s="37" t="n">
         <f aca="false">ROUND((20*100*(K10-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L10-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N10-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O10-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>52.3</v>
-      </c>
-      <c r="R10" s="27" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="R10" s="7" t="n">
         <f aca="false">RANK(Q10,$Q$4:$Q$28)</f>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E11" s="27" t="s">
-        <v>238</v>
-      </c>
-      <c r="F11" s="28" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E11" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F11" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T08",'State Market Summary'!$B$4:$B$54)</f>
         <v>918</v>
       </c>
-      <c r="G11" s="28" t="n">
+      <c r="G11" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T08",'State Market Summary'!$C$4:$C$54)</f>
         <v>279</v>
       </c>
-      <c r="H11" s="28" t="n">
+      <c r="H11" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T08",'State Market Summary'!$N$4:$N$54)</f>
         <v>430</v>
       </c>
-      <c r="I11" s="28" t="n">
+      <c r="I11" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T08",'State Market Summary'!$O$4:$O$54)</f>
         <v>135</v>
       </c>
-      <c r="J11" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F11/300,0))</f>
-        <v>3</v>
-      </c>
-      <c r="K11" s="28" t="n">
+      <c r="J11" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="8" t="n">
         <f aca="false">ROUND(F11/J11,0)</f>
-        <v>306</v>
-      </c>
-      <c r="L11" s="30" t="n">
+        <v>918</v>
+      </c>
+      <c r="L11" s="32" t="n">
         <f aca="false">ROUND(G11/J11,1)</f>
-        <v>93</v>
-      </c>
-      <c r="M11" s="31" t="n">
+        <v>279</v>
+      </c>
+      <c r="M11" s="33" t="n">
         <f aca="false">H11/F11</f>
         <v>0.468409586056645</v>
       </c>
-      <c r="N11" s="32" t="n">
+      <c r="N11" s="34" t="n">
         <v>1294309</v>
       </c>
-      <c r="O11" s="33" t="n">
+      <c r="O11" s="35" t="n">
         <v>97019</v>
       </c>
-      <c r="P11" s="34" t="n">
+      <c r="P11" s="36" t="n">
         <v>42.3</v>
       </c>
-      <c r="Q11" s="35" t="n">
+      <c r="Q11" s="37" t="n">
         <f aca="false">ROUND((20*100*(K11-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L11-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N11-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O11-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>45.4</v>
-      </c>
-      <c r="R11" s="27" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="R11" s="7" t="n">
         <f aca="false">RANK(Q11,$Q$4:$Q$28)</f>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E12" s="27" t="s">
-        <v>239</v>
-      </c>
-      <c r="F12" s="28" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E12" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="F12" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T09",'State Market Summary'!$B$4:$B$54)</f>
         <v>758</v>
       </c>
-      <c r="G12" s="28" t="n">
+      <c r="G12" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T09",'State Market Summary'!$C$4:$C$54)</f>
         <v>176</v>
       </c>
-      <c r="H12" s="28" t="n">
+      <c r="H12" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T09",'State Market Summary'!$N$4:$N$54)</f>
         <v>373</v>
       </c>
-      <c r="I12" s="28" t="n">
+      <c r="I12" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T09",'State Market Summary'!$O$4:$O$54)</f>
         <v>87</v>
       </c>
-      <c r="J12" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F12/300,0))</f>
-        <v>3</v>
-      </c>
-      <c r="K12" s="28" t="n">
+      <c r="J12" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="8" t="n">
         <f aca="false">ROUND(F12/J12,0)</f>
-        <v>253</v>
-      </c>
-      <c r="L12" s="30" t="n">
+        <v>758</v>
+      </c>
+      <c r="L12" s="32" t="n">
         <f aca="false">ROUND(G12/J12,1)</f>
-        <v>58.7</v>
-      </c>
-      <c r="M12" s="31" t="n">
+        <v>176</v>
+      </c>
+      <c r="M12" s="33" t="n">
         <f aca="false">H12/F12</f>
         <v>0.492084432717678</v>
       </c>
-      <c r="N12" s="32" t="n">
+      <c r="N12" s="34" t="n">
         <v>1084210</v>
       </c>
-      <c r="O12" s="33" t="n">
+      <c r="O12" s="35" t="n">
         <v>81797</v>
       </c>
-      <c r="P12" s="34" t="n">
+      <c r="P12" s="36" t="n">
         <v>35.1</v>
       </c>
-      <c r="Q12" s="35" t="n">
+      <c r="Q12" s="37" t="n">
         <f aca="false">ROUND((20*100*(K12-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L12-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N12-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O12-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>9.7</v>
-      </c>
-      <c r="R12" s="27" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="R12" s="7" t="n">
         <f aca="false">RANK(Q12,$Q$4:$Q$28)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E13" s="27" t="s">
-        <v>240</v>
-      </c>
-      <c r="F13" s="28" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E13" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T10",'State Market Summary'!$B$4:$B$54)</f>
         <v>664</v>
       </c>
-      <c r="G13" s="28" t="n">
+      <c r="G13" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T10",'State Market Summary'!$C$4:$C$54)</f>
         <v>200</v>
       </c>
-      <c r="H13" s="28" t="n">
+      <c r="H13" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T10",'State Market Summary'!$N$4:$N$54)</f>
         <v>274</v>
       </c>
-      <c r="I13" s="28" t="n">
+      <c r="I13" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T10",'State Market Summary'!$O$4:$O$54)</f>
         <v>81</v>
       </c>
-      <c r="J13" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F13/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="K13" s="28" t="n">
+      <c r="J13" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="8" t="n">
         <f aca="false">ROUND(F13/J13,0)</f>
-        <v>332</v>
-      </c>
-      <c r="L13" s="30" t="n">
+        <v>664</v>
+      </c>
+      <c r="L13" s="32" t="n">
         <f aca="false">ROUND(G13/J13,1)</f>
-        <v>100</v>
-      </c>
-      <c r="M13" s="31" t="n">
+        <v>200</v>
+      </c>
+      <c r="M13" s="33" t="n">
         <f aca="false">H13/F13</f>
         <v>0.412650602409639</v>
       </c>
-      <c r="N13" s="32" t="n">
+      <c r="N13" s="34" t="n">
         <v>995376</v>
       </c>
-      <c r="O13" s="33" t="n">
+      <c r="O13" s="35" t="n">
         <v>67472</v>
       </c>
-      <c r="P13" s="34" t="n">
+      <c r="P13" s="36" t="n">
         <v>29.2</v>
       </c>
-      <c r="Q13" s="35" t="n">
+      <c r="Q13" s="37" t="n">
         <f aca="false">ROUND((20*100*(K13-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L13-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N13-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O13-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>44.6</v>
-      </c>
-      <c r="R13" s="27" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="R13" s="7" t="n">
         <f aca="false">RANK(Q13,$Q$4:$Q$28)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E14" s="27" t="s">
-        <v>241</v>
-      </c>
-      <c r="F14" s="28" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E14" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="F14" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T11",'State Market Summary'!$B$4:$B$54)</f>
         <v>683</v>
       </c>
-      <c r="G14" s="28" t="n">
+      <c r="G14" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T11",'State Market Summary'!$C$4:$C$54)</f>
         <v>220</v>
       </c>
-      <c r="H14" s="28" t="n">
+      <c r="H14" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T11",'State Market Summary'!$N$4:$N$54)</f>
         <v>122</v>
       </c>
-      <c r="I14" s="28" t="n">
+      <c r="I14" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T11",'State Market Summary'!$O$4:$O$54)</f>
         <v>49</v>
       </c>
-      <c r="J14" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F14/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="K14" s="28" t="n">
+      <c r="J14" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="8" t="n">
         <f aca="false">ROUND(F14/J14,0)</f>
-        <v>342</v>
-      </c>
-      <c r="L14" s="30" t="n">
+        <v>683</v>
+      </c>
+      <c r="L14" s="32" t="n">
         <f aca="false">ROUND(G14/J14,1)</f>
-        <v>110</v>
-      </c>
-      <c r="M14" s="31" t="n">
+        <v>220</v>
+      </c>
+      <c r="M14" s="33" t="n">
         <f aca="false">H14/F14</f>
         <v>0.178623718887262</v>
       </c>
-      <c r="N14" s="32" t="n">
+      <c r="N14" s="34" t="n">
         <v>1070611</v>
       </c>
-      <c r="O14" s="33" t="n">
+      <c r="O14" s="35" t="n">
         <v>75694</v>
       </c>
-      <c r="P14" s="34" t="n">
+      <c r="P14" s="36" t="n">
         <v>33.4</v>
       </c>
-      <c r="Q14" s="35" t="n">
+      <c r="Q14" s="37" t="n">
         <f aca="false">ROUND((20*100*(K14-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L14-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N14-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O14-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>55.5</v>
-      </c>
-      <c r="R14" s="27" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="R14" s="7" t="n">
         <f aca="false">RANK(Q14,$Q$4:$Q$28)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E15" s="27" t="s">
-        <v>242</v>
-      </c>
-      <c r="F15" s="28" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E15" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="F15" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T12",'State Market Summary'!$B$4:$B$54)</f>
         <v>734</v>
       </c>
-      <c r="G15" s="28" t="n">
+      <c r="G15" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T12",'State Market Summary'!$C$4:$C$54)</f>
         <v>225</v>
       </c>
-      <c r="H15" s="28" t="n">
+      <c r="H15" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T12",'State Market Summary'!$N$4:$N$54)</f>
         <v>383</v>
       </c>
-      <c r="I15" s="28" t="n">
+      <c r="I15" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T12",'State Market Summary'!$O$4:$O$54)</f>
         <v>112</v>
       </c>
-      <c r="J15" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F15/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="K15" s="28" t="n">
+      <c r="J15" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" s="8" t="n">
         <f aca="false">ROUND(F15/J15,0)</f>
-        <v>367</v>
-      </c>
-      <c r="L15" s="30" t="n">
+        <v>734</v>
+      </c>
+      <c r="L15" s="32" t="n">
         <f aca="false">ROUND(G15/J15,1)</f>
-        <v>112.5</v>
-      </c>
-      <c r="M15" s="31" t="n">
+        <v>225</v>
+      </c>
+      <c r="M15" s="33" t="n">
         <f aca="false">H15/F15</f>
         <v>0.521798365122616</v>
       </c>
-      <c r="N15" s="32" t="n">
+      <c r="N15" s="34" t="n">
         <v>1119028</v>
       </c>
-      <c r="O15" s="33" t="n">
+      <c r="O15" s="35" t="n">
         <v>90198</v>
       </c>
-      <c r="P15" s="34" t="n">
+      <c r="P15" s="36" t="n">
         <v>36.3</v>
       </c>
-      <c r="Q15" s="35" t="n">
+      <c r="Q15" s="37" t="n">
         <f aca="false">ROUND((20*100*(K15-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L15-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N15-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O15-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>63.7</v>
-      </c>
-      <c r="R15" s="27" t="n">
+        <v>45.1</v>
+      </c>
+      <c r="R15" s="7" t="n">
         <f aca="false">RANK(Q15,$Q$4:$Q$28)</f>
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E16" s="27" t="s">
-        <v>243</v>
-      </c>
-      <c r="F16" s="28" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E16" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="F16" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T13",'State Market Summary'!$B$4:$B$54)</f>
         <v>779</v>
       </c>
-      <c r="G16" s="28" t="n">
+      <c r="G16" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T13",'State Market Summary'!$C$4:$C$54)</f>
         <v>181</v>
       </c>
-      <c r="H16" s="28" t="n">
+      <c r="H16" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T13",'State Market Summary'!$N$4:$N$54)</f>
         <v>343</v>
       </c>
-      <c r="I16" s="28" t="n">
+      <c r="I16" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T13",'State Market Summary'!$O$4:$O$54)</f>
         <v>72</v>
       </c>
-      <c r="J16" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F16/300,0))</f>
-        <v>3</v>
-      </c>
-      <c r="K16" s="28" t="n">
+      <c r="J16" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="8" t="n">
         <f aca="false">ROUND(F16/J16,0)</f>
-        <v>260</v>
-      </c>
-      <c r="L16" s="30" t="n">
+        <v>779</v>
+      </c>
+      <c r="L16" s="32" t="n">
         <f aca="false">ROUND(G16/J16,1)</f>
-        <v>60.3</v>
-      </c>
-      <c r="M16" s="31" t="n">
+        <v>181</v>
+      </c>
+      <c r="M16" s="33" t="n">
         <f aca="false">H16/F16</f>
         <v>0.440308087291399</v>
       </c>
-      <c r="N16" s="32" t="n">
+      <c r="N16" s="34" t="n">
         <v>975468</v>
       </c>
-      <c r="O16" s="33" t="n">
+      <c r="O16" s="35" t="n">
         <v>70436</v>
       </c>
-      <c r="P16" s="34" t="n">
+      <c r="P16" s="36" t="n">
         <v>34</v>
       </c>
-      <c r="Q16" s="35" t="n">
+      <c r="Q16" s="37" t="n">
         <f aca="false">ROUND((20*100*(K16-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L16-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N16-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O16-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>8.3</v>
-      </c>
-      <c r="R16" s="27" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="R16" s="7" t="n">
         <f aca="false">RANK(Q16,$Q$4:$Q$28)</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E17" s="27" t="s">
-        <v>244</v>
-      </c>
-      <c r="F17" s="28" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E17" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="F17" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T14",'State Market Summary'!$B$4:$B$54)</f>
         <v>597</v>
       </c>
-      <c r="G17" s="28" t="n">
+      <c r="G17" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T14",'State Market Summary'!$C$4:$C$54)</f>
         <v>198</v>
       </c>
-      <c r="H17" s="28" t="n">
+      <c r="H17" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T14",'State Market Summary'!$N$4:$N$54)</f>
         <v>205</v>
       </c>
-      <c r="I17" s="28" t="n">
+      <c r="I17" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T14",'State Market Summary'!$O$4:$O$54)</f>
         <v>79</v>
       </c>
-      <c r="J17" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F17/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="K17" s="28" t="n">
+      <c r="J17" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="8" t="n">
         <f aca="false">ROUND(F17/J17,0)</f>
-        <v>299</v>
-      </c>
-      <c r="L17" s="30" t="n">
+        <v>597</v>
+      </c>
+      <c r="L17" s="32" t="n">
         <f aca="false">ROUND(G17/J17,1)</f>
-        <v>99</v>
-      </c>
-      <c r="M17" s="31" t="n">
+        <v>198</v>
+      </c>
+      <c r="M17" s="33" t="n">
         <f aca="false">H17/F17</f>
         <v>0.343383584589615</v>
       </c>
-      <c r="N17" s="32" t="n">
+      <c r="N17" s="34" t="n">
         <v>1097099</v>
       </c>
-      <c r="O17" s="33" t="n">
+      <c r="O17" s="35" t="n">
         <v>68598</v>
       </c>
-      <c r="P17" s="34" t="n">
+      <c r="P17" s="36" t="n">
         <v>30.5</v>
       </c>
-      <c r="Q17" s="35" t="n">
+      <c r="Q17" s="37" t="n">
         <f aca="false">ROUND((20*100*(K17-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L17-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N17-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O17-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>41.3</v>
-      </c>
-      <c r="R17" s="27" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="R17" s="7" t="n">
         <f aca="false">RANK(Q17,$Q$4:$Q$28)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E18" s="27" t="s">
-        <v>245</v>
-      </c>
-      <c r="F18" s="28" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E18" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="F18" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T15",'State Market Summary'!$B$4:$B$54)</f>
         <v>594</v>
       </c>
-      <c r="G18" s="28" t="n">
+      <c r="G18" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T15",'State Market Summary'!$C$4:$C$54)</f>
         <v>231</v>
       </c>
-      <c r="H18" s="28" t="n">
+      <c r="H18" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T15",'State Market Summary'!$N$4:$N$54)</f>
         <v>199</v>
       </c>
-      <c r="I18" s="28" t="n">
+      <c r="I18" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T15",'State Market Summary'!$O$4:$O$54)</f>
         <v>83</v>
       </c>
-      <c r="J18" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F18/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="K18" s="28" t="n">
+      <c r="J18" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="8" t="n">
         <f aca="false">ROUND(F18/J18,0)</f>
-        <v>297</v>
-      </c>
-      <c r="L18" s="30" t="n">
+        <v>594</v>
+      </c>
+      <c r="L18" s="32" t="n">
         <f aca="false">ROUND(G18/J18,1)</f>
-        <v>115.5</v>
-      </c>
-      <c r="M18" s="31" t="n">
+        <v>231</v>
+      </c>
+      <c r="M18" s="33" t="n">
         <f aca="false">H18/F18</f>
         <v>0.335016835016835</v>
       </c>
-      <c r="N18" s="32" t="n">
+      <c r="N18" s="34" t="n">
         <v>1257732</v>
       </c>
-      <c r="O18" s="33" t="n">
+      <c r="O18" s="35" t="n">
         <v>75026</v>
       </c>
-      <c r="P18" s="34" t="n">
+      <c r="P18" s="36" t="n">
         <v>30</v>
       </c>
-      <c r="Q18" s="35" t="n">
+      <c r="Q18" s="37" t="n">
         <f aca="false">ROUND((20*100*(K18-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L18-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N18-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O18-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>55.8</v>
-      </c>
-      <c r="R18" s="27" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="R18" s="7" t="n">
         <f aca="false">RANK(Q18,$Q$4:$Q$28)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E19" s="27" t="s">
-        <v>246</v>
-      </c>
-      <c r="F19" s="28" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E19" s="7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F19" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T16",'State Market Summary'!$B$4:$B$54)</f>
         <v>550</v>
       </c>
-      <c r="G19" s="28" t="n">
+      <c r="G19" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T16",'State Market Summary'!$C$4:$C$54)</f>
         <v>185</v>
       </c>
-      <c r="H19" s="28" t="n">
+      <c r="H19" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T16",'State Market Summary'!$N$4:$N$54)</f>
         <v>202</v>
       </c>
-      <c r="I19" s="28" t="n">
+      <c r="I19" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T16",'State Market Summary'!$O$4:$O$54)</f>
         <v>79</v>
       </c>
-      <c r="J19" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F19/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="K19" s="28" t="n">
+      <c r="J19" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" s="8" t="n">
         <f aca="false">ROUND(F19/J19,0)</f>
-        <v>275</v>
-      </c>
-      <c r="L19" s="30" t="n">
+        <v>550</v>
+      </c>
+      <c r="L19" s="32" t="n">
         <f aca="false">ROUND(G19/J19,1)</f>
-        <v>92.5</v>
-      </c>
-      <c r="M19" s="31" t="n">
+        <v>185</v>
+      </c>
+      <c r="M19" s="33" t="n">
         <f aca="false">H19/F19</f>
         <v>0.367272727272727</v>
       </c>
-      <c r="N19" s="32" t="n">
+      <c r="N19" s="34" t="n">
         <v>915366</v>
       </c>
-      <c r="O19" s="33" t="n">
+      <c r="O19" s="35" t="n">
         <v>91862</v>
       </c>
-      <c r="P19" s="34" t="n">
+      <c r="P19" s="36" t="n">
         <v>40.7</v>
       </c>
-      <c r="Q19" s="35" t="n">
+      <c r="Q19" s="37" t="n">
         <f aca="false">ROUND((20*100*(K19-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L19-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N19-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O19-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>39.6</v>
-      </c>
-      <c r="R19" s="27" t="n">
+        <v>32.3</v>
+      </c>
+      <c r="R19" s="7" t="n">
         <f aca="false">RANK(Q19,$Q$4:$Q$28)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E20" s="27" t="s">
-        <v>247</v>
-      </c>
-      <c r="F20" s="28" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E20" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="F20" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T17",'State Market Summary'!$B$4:$B$54)</f>
         <v>718</v>
       </c>
-      <c r="G20" s="28" t="n">
+      <c r="G20" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T17",'State Market Summary'!$C$4:$C$54)</f>
         <v>241</v>
       </c>
-      <c r="H20" s="28" t="n">
+      <c r="H20" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T17",'State Market Summary'!$N$4:$N$54)</f>
         <v>348</v>
       </c>
-      <c r="I20" s="28" t="n">
+      <c r="I20" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T17",'State Market Summary'!$O$4:$O$54)</f>
         <v>81</v>
       </c>
-      <c r="J20" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F20/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="K20" s="28" t="n">
+      <c r="J20" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" s="8" t="n">
         <f aca="false">ROUND(F20/J20,0)</f>
-        <v>359</v>
-      </c>
-      <c r="L20" s="30" t="n">
+        <v>718</v>
+      </c>
+      <c r="L20" s="32" t="n">
         <f aca="false">ROUND(G20/J20,1)</f>
-        <v>120.5</v>
-      </c>
-      <c r="M20" s="31" t="n">
+        <v>241</v>
+      </c>
+      <c r="M20" s="33" t="n">
         <f aca="false">H20/F20</f>
         <v>0.484679665738162</v>
       </c>
-      <c r="N20" s="32" t="n">
+      <c r="N20" s="34" t="n">
         <v>1191812</v>
       </c>
-      <c r="O20" s="33" t="n">
+      <c r="O20" s="35" t="n">
         <v>84033</v>
       </c>
-      <c r="P20" s="34" t="n">
+      <c r="P20" s="36" t="n">
         <v>36.3</v>
       </c>
-      <c r="Q20" s="35" t="n">
+      <c r="Q20" s="37" t="n">
         <f aca="false">ROUND((20*100*(K20-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L20-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N20-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O20-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>67.6</v>
-      </c>
-      <c r="R20" s="27" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="R20" s="7" t="n">
         <f aca="false">RANK(Q20,$Q$4:$Q$28)</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E21" s="27" t="s">
-        <v>248</v>
-      </c>
-      <c r="F21" s="28" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E21" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="F21" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T18",'State Market Summary'!$B$4:$B$54)</f>
         <v>462</v>
       </c>
-      <c r="G21" s="28" t="n">
+      <c r="G21" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T18",'State Market Summary'!$C$4:$C$54)</f>
         <v>174</v>
       </c>
-      <c r="H21" s="28" t="n">
+      <c r="H21" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T18",'State Market Summary'!$N$4:$N$54)</f>
         <v>89</v>
       </c>
-      <c r="I21" s="28" t="n">
+      <c r="I21" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T18",'State Market Summary'!$O$4:$O$54)</f>
         <v>37</v>
       </c>
-      <c r="J21" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F21/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="K21" s="28" t="n">
+      <c r="J21" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" s="8" t="n">
         <f aca="false">ROUND(F21/J21,0)</f>
-        <v>231</v>
-      </c>
-      <c r="L21" s="30" t="n">
+        <v>462</v>
+      </c>
+      <c r="L21" s="32" t="n">
         <f aca="false">ROUND(G21/J21,1)</f>
-        <v>87</v>
-      </c>
-      <c r="M21" s="31" t="n">
+        <v>174</v>
+      </c>
+      <c r="M21" s="33" t="n">
         <f aca="false">H21/F21</f>
         <v>0.192640692640693</v>
       </c>
-      <c r="N21" s="32" t="n">
+      <c r="N21" s="34" t="n">
         <v>772926</v>
       </c>
-      <c r="O21" s="33" t="n">
+      <c r="O21" s="35" t="n">
         <v>60048</v>
       </c>
-      <c r="P21" s="34" t="n">
+      <c r="P21" s="36" t="n">
         <v>26.1</v>
       </c>
-      <c r="Q21" s="35" t="n">
+      <c r="Q21" s="37" t="n">
         <f aca="false">ROUND((20*100*(K21-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L21-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N21-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O21-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>22.5</v>
-      </c>
-      <c r="R21" s="27" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="R21" s="7" t="n">
         <f aca="false">RANK(Q21,$Q$4:$Q$28)</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E22" s="27" t="s">
-        <v>249</v>
-      </c>
-      <c r="F22" s="28" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E22" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="F22" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T19",'State Market Summary'!$B$4:$B$54)</f>
         <v>477</v>
       </c>
-      <c r="G22" s="28" t="n">
+      <c r="G22" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T19",'State Market Summary'!$C$4:$C$54)</f>
         <v>176</v>
       </c>
-      <c r="H22" s="28" t="n">
+      <c r="H22" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T19",'State Market Summary'!$N$4:$N$54)</f>
         <v>201</v>
       </c>
-      <c r="I22" s="28" t="n">
+      <c r="I22" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T19",'State Market Summary'!$O$4:$O$54)</f>
         <v>69</v>
       </c>
-      <c r="J22" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F22/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="K22" s="28" t="n">
+      <c r="J22" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" s="8" t="n">
         <f aca="false">ROUND(F22/J22,0)</f>
-        <v>239</v>
-      </c>
-      <c r="L22" s="30" t="n">
+        <v>477</v>
+      </c>
+      <c r="L22" s="32" t="n">
         <f aca="false">ROUND(G22/J22,1)</f>
-        <v>88</v>
-      </c>
-      <c r="M22" s="31" t="n">
+        <v>176</v>
+      </c>
+      <c r="M22" s="33" t="n">
         <f aca="false">H22/F22</f>
         <v>0.421383647798742</v>
       </c>
-      <c r="N22" s="32" t="n">
+      <c r="N22" s="34" t="n">
         <v>739152</v>
       </c>
-      <c r="O22" s="33" t="n">
+      <c r="O22" s="35" t="n">
         <v>59699</v>
       </c>
-      <c r="P22" s="34" t="n">
+      <c r="P22" s="36" t="n">
         <v>25.6</v>
       </c>
-      <c r="Q22" s="35" t="n">
+      <c r="Q22" s="37" t="n">
         <f aca="false">ROUND((20*100*(K22-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L22-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N22-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O22-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>23.8</v>
-      </c>
-      <c r="R22" s="27" t="n">
+        <v>19.7</v>
+      </c>
+      <c r="R22" s="7" t="n">
         <f aca="false">RANK(Q22,$Q$4:$Q$28)</f>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E23" s="27" t="s">
-        <v>250</v>
-      </c>
-      <c r="F23" s="28" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E23" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="F23" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T20",'State Market Summary'!$B$4:$B$54)</f>
         <v>442</v>
       </c>
-      <c r="G23" s="28" t="n">
+      <c r="G23" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T20",'State Market Summary'!$C$4:$C$54)</f>
         <v>111</v>
       </c>
-      <c r="H23" s="28" t="n">
+      <c r="H23" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T20",'State Market Summary'!$N$4:$N$54)</f>
         <v>173</v>
       </c>
-      <c r="I23" s="28" t="n">
+      <c r="I23" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T20",'State Market Summary'!$O$4:$O$54)</f>
         <v>48</v>
       </c>
-      <c r="J23" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F23/300,0))</f>
-        <v>1</v>
-      </c>
-      <c r="K23" s="28" t="n">
+      <c r="J23" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" s="8" t="n">
         <f aca="false">ROUND(F23/J23,0)</f>
         <v>442</v>
       </c>
-      <c r="L23" s="30" t="n">
+      <c r="L23" s="32" t="n">
         <f aca="false">ROUND(G23/J23,1)</f>
         <v>111</v>
       </c>
-      <c r="M23" s="31" t="n">
+      <c r="M23" s="33" t="n">
         <f aca="false">H23/F23</f>
         <v>0.391402714932127</v>
       </c>
-      <c r="N23" s="32" t="n">
+      <c r="N23" s="34" t="n">
         <v>663850</v>
       </c>
-      <c r="O23" s="33" t="n">
+      <c r="O23" s="35" t="n">
         <v>70489</v>
       </c>
-      <c r="P23" s="34" t="n">
+      <c r="P23" s="36" t="n">
         <v>28.5</v>
       </c>
-      <c r="Q23" s="35" t="n">
+      <c r="Q23" s="37" t="n">
         <f aca="false">ROUND((20*100*(K23-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L23-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N23-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O23-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>63.2</v>
-      </c>
-      <c r="R23" s="27" t="n">
+        <v>8.7</v>
+      </c>
+      <c r="R23" s="7" t="n">
         <f aca="false">RANK(Q23,$Q$4:$Q$28)</f>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E24" s="27" t="s">
-        <v>251</v>
-      </c>
-      <c r="F24" s="28" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E24" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="F24" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T21",'State Market Summary'!$B$4:$B$54)</f>
         <v>478</v>
       </c>
-      <c r="G24" s="28" t="n">
+      <c r="G24" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T21",'State Market Summary'!$C$4:$C$54)</f>
         <v>137</v>
       </c>
-      <c r="H24" s="28" t="n">
+      <c r="H24" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T21",'State Market Summary'!$N$4:$N$54)</f>
         <v>241</v>
       </c>
-      <c r="I24" s="28" t="n">
+      <c r="I24" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T21",'State Market Summary'!$O$4:$O$54)</f>
         <v>49</v>
       </c>
-      <c r="J24" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F24/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="K24" s="28" t="n">
+      <c r="J24" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="8" t="n">
         <f aca="false">ROUND(F24/J24,0)</f>
-        <v>239</v>
-      </c>
-      <c r="L24" s="30" t="n">
+        <v>478</v>
+      </c>
+      <c r="L24" s="32" t="n">
         <f aca="false">ROUND(G24/J24,1)</f>
-        <v>68.5</v>
-      </c>
-      <c r="M24" s="31" t="n">
+        <v>137</v>
+      </c>
+      <c r="M24" s="33" t="n">
         <f aca="false">H24/F24</f>
         <v>0.50418410041841</v>
       </c>
-      <c r="N24" s="32" t="n">
+      <c r="N24" s="34" t="n">
         <v>794462</v>
       </c>
-      <c r="O24" s="33" t="n">
+      <c r="O24" s="35" t="n">
         <v>97828</v>
       </c>
-      <c r="P24" s="34" t="n">
+      <c r="P24" s="36" t="n">
         <v>41.2</v>
       </c>
-      <c r="Q24" s="35" t="n">
+      <c r="Q24" s="37" t="n">
         <f aca="false">ROUND((20*100*(K24-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L24-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N24-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O24-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>19.1</v>
-      </c>
-      <c r="R24" s="27" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="R24" s="7" t="n">
         <f aca="false">RANK(Q24,$Q$4:$Q$28)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E25" s="27" t="s">
-        <v>252</v>
-      </c>
-      <c r="F25" s="28" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E25" s="7" t="s">
+        <v>249</v>
+      </c>
+      <c r="F25" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T22",'State Market Summary'!$B$4:$B$54)</f>
         <v>489</v>
       </c>
-      <c r="G25" s="28" t="n">
+      <c r="G25" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T22",'State Market Summary'!$C$4:$C$54)</f>
         <v>168</v>
       </c>
-      <c r="H25" s="28" t="n">
+      <c r="H25" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T22",'State Market Summary'!$N$4:$N$54)</f>
         <v>199</v>
       </c>
-      <c r="I25" s="28" t="n">
+      <c r="I25" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T22",'State Market Summary'!$O$4:$O$54)</f>
         <v>78</v>
       </c>
-      <c r="J25" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F25/300,0))</f>
-        <v>2</v>
-      </c>
-      <c r="K25" s="28" t="n">
+      <c r="J25" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" s="8" t="n">
         <f aca="false">ROUND(F25/J25,0)</f>
-        <v>245</v>
-      </c>
-      <c r="L25" s="30" t="n">
+        <v>489</v>
+      </c>
+      <c r="L25" s="32" t="n">
         <f aca="false">ROUND(G25/J25,1)</f>
-        <v>84</v>
-      </c>
-      <c r="M25" s="31" t="n">
+        <v>168</v>
+      </c>
+      <c r="M25" s="33" t="n">
         <f aca="false">H25/F25</f>
         <v>0.406952965235174</v>
       </c>
-      <c r="N25" s="32" t="n">
+      <c r="N25" s="34" t="n">
         <v>860620</v>
       </c>
-      <c r="O25" s="33" t="n">
+      <c r="O25" s="35" t="n">
         <v>94114</v>
       </c>
-      <c r="P25" s="34" t="n">
+      <c r="P25" s="36" t="n">
         <v>39.1</v>
       </c>
-      <c r="Q25" s="35" t="n">
+      <c r="Q25" s="37" t="n">
         <f aca="false">ROUND((20*100*(K25-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L25-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N25-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O25-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>30.7</v>
-      </c>
-      <c r="R25" s="27" t="n">
+        <v>27.8</v>
+      </c>
+      <c r="R25" s="7" t="n">
         <f aca="false">RANK(Q25,$Q$4:$Q$28)</f>
         <v>18</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E26" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="F26" s="28" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E26" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="F26" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T23",'State Market Summary'!$B$4:$B$54)</f>
         <v>401</v>
       </c>
-      <c r="G26" s="28" t="n">
+      <c r="G26" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T23",'State Market Summary'!$C$4:$C$54)</f>
         <v>124</v>
       </c>
-      <c r="H26" s="28" t="n">
+      <c r="H26" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T23",'State Market Summary'!$N$4:$N$54)</f>
         <v>159</v>
       </c>
-      <c r="I26" s="28" t="n">
+      <c r="I26" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T23",'State Market Summary'!$O$4:$O$54)</f>
         <v>44</v>
       </c>
-      <c r="J26" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F26/300,0))</f>
-        <v>1</v>
-      </c>
-      <c r="K26" s="28" t="n">
+      <c r="J26" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" s="8" t="n">
         <f aca="false">ROUND(F26/J26,0)</f>
         <v>401</v>
       </c>
-      <c r="L26" s="30" t="n">
+      <c r="L26" s="32" t="n">
         <f aca="false">ROUND(G26/J26,1)</f>
         <v>124</v>
       </c>
-      <c r="M26" s="31" t="n">
+      <c r="M26" s="33" t="n">
         <f aca="false">H26/F26</f>
         <v>0.396508728179551</v>
       </c>
-      <c r="N26" s="32" t="n">
+      <c r="N26" s="34" t="n">
         <v>634143</v>
       </c>
-      <c r="O26" s="33" t="n">
+      <c r="O26" s="35" t="n">
         <v>67976</v>
       </c>
-      <c r="P26" s="34" t="n">
+      <c r="P26" s="36" t="n">
         <v>29.8</v>
       </c>
-      <c r="Q26" s="35" t="n">
+      <c r="Q26" s="37" t="n">
         <f aca="false">ROUND((20*100*(K26-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L26-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N26-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O26-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>68.4</v>
-      </c>
-      <c r="R26" s="27" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="R26" s="7" t="n">
         <f aca="false">RANK(Q26,$Q$4:$Q$28)</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E27" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="F27" s="28" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E27" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="F27" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T24",'State Market Summary'!$B$4:$B$54)</f>
         <v>345</v>
       </c>
-      <c r="G27" s="28" t="n">
+      <c r="G27" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T24",'State Market Summary'!$C$4:$C$54)</f>
         <v>111</v>
       </c>
-      <c r="H27" s="28" t="n">
+      <c r="H27" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T24",'State Market Summary'!$N$4:$N$54)</f>
         <v>168</v>
       </c>
-      <c r="I27" s="28" t="n">
+      <c r="I27" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T24",'State Market Summary'!$O$4:$O$54)</f>
         <v>55</v>
       </c>
-      <c r="J27" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F27/300,0))</f>
-        <v>1</v>
-      </c>
-      <c r="K27" s="28" t="n">
+      <c r="J27" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" s="8" t="n">
         <f aca="false">ROUND(F27/J27,0)</f>
         <v>345</v>
       </c>
-      <c r="L27" s="30" t="n">
+      <c r="L27" s="32" t="n">
         <f aca="false">ROUND(G27/J27,1)</f>
         <v>111</v>
       </c>
-      <c r="M27" s="31" t="n">
+      <c r="M27" s="33" t="n">
         <f aca="false">H27/F27</f>
         <v>0.48695652173913</v>
       </c>
-      <c r="N27" s="32" t="n">
+      <c r="N27" s="34" t="n">
         <v>528815</v>
       </c>
-      <c r="O27" s="33" t="n">
+      <c r="O27" s="35" t="n">
         <v>73245</v>
       </c>
-      <c r="P27" s="34" t="n">
+      <c r="P27" s="36" t="n">
         <v>30.7</v>
       </c>
-      <c r="Q27" s="35" t="n">
+      <c r="Q27" s="37" t="n">
         <f aca="false">ROUND((20*100*(K27-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L27-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N27-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O27-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>54.3</v>
-      </c>
-      <c r="R27" s="27" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="R27" s="7" t="n">
         <f aca="false">RANK(Q27,$Q$4:$Q$28)</f>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E28" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="F28" s="28" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E28" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="F28" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T25",'State Market Summary'!$B$4:$B$54)</f>
         <v>364</v>
       </c>
-      <c r="G28" s="28" t="n">
+      <c r="G28" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T25",'State Market Summary'!$C$4:$C$54)</f>
         <v>97</v>
       </c>
-      <c r="H28" s="28" t="n">
+      <c r="H28" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T25",'State Market Summary'!$N$4:$N$54)</f>
         <v>157</v>
       </c>
-      <c r="I28" s="28" t="n">
+      <c r="I28" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T25",'State Market Summary'!$O$4:$O$54)</f>
         <v>29</v>
       </c>
-      <c r="J28" s="29" t="n">
-        <f aca="false">MAX(1,ROUND(F28/300,0))</f>
-        <v>1</v>
-      </c>
-      <c r="K28" s="28" t="n">
+      <c r="J28" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" s="8" t="n">
         <f aca="false">ROUND(F28/J28,0)</f>
         <v>364</v>
       </c>
-      <c r="L28" s="30" t="n">
+      <c r="L28" s="32" t="n">
         <f aca="false">ROUND(G28/J28,1)</f>
         <v>97</v>
       </c>
-      <c r="M28" s="31" t="n">
+      <c r="M28" s="33" t="n">
         <f aca="false">H28/F28</f>
         <v>0.431318681318681</v>
       </c>
-      <c r="N28" s="32" t="n">
+      <c r="N28" s="34" t="n">
         <v>473826</v>
       </c>
-      <c r="O28" s="33" t="n">
+      <c r="O28" s="35" t="n">
         <v>65973</v>
       </c>
-      <c r="P28" s="34" t="n">
+      <c r="P28" s="36" t="n">
         <v>30.6</v>
       </c>
-      <c r="Q28" s="35" t="n">
+      <c r="Q28" s="37" t="n">
         <f aca="false">ROUND((20*100*(K28-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L28-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N28-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O28-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>43.4</v>
-      </c>
-      <c r="R28" s="27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R28" s="7" t="n">
         <f aca="false">RANK(Q28,$Q$4:$Q$28)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="E29" s="36" t="s">
-        <v>53</v>
-      </c>
-      <c r="F29" s="37" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E29" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" s="15" t="n">
         <f aca="false">SUM(F4:F28)</f>
         <v>18405</v>
       </c>
-      <c r="G29" s="37" t="n">
+      <c r="G29" s="15" t="n">
         <f aca="false">SUM(G4:G28)</f>
         <v>5862</v>
       </c>
-      <c r="H29" s="37" t="n">
+      <c r="H29" s="15" t="n">
         <f aca="false">SUM(H4:H28)</f>
         <v>7630</v>
       </c>
-      <c r="I29" s="37" t="n">
+      <c r="I29" s="15" t="n">
         <f aca="false">SUM(I4:I28)</f>
         <v>2215</v>
       </c>
-      <c r="J29" s="36" t="n">
+      <c r="J29" s="38" t="n">
         <f aca="false">SUM(J4:J28)</f>
-        <v>61</v>
-      </c>
-      <c r="K29" s="37" t="n">
+        <v>28</v>
+      </c>
+      <c r="K29" s="15" t="n">
         <f aca="false">ROUND(F29/J29,0)</f>
-        <v>302</v>
-      </c>
-      <c r="L29" s="38" t="n">
+        <v>657</v>
+      </c>
+      <c r="L29" s="39" t="n">
         <f aca="false">ROUND(G29/J29,1)</f>
-        <v>96.1</v>
-      </c>
-      <c r="M29" s="39" t="n">
+        <v>209.4</v>
+      </c>
+      <c r="M29" s="40" t="n">
         <f aca="false">H29/F29</f>
         <v>0.414561260527031</v>
       </c>
-      <c r="N29" s="36"/>
-      <c r="O29" s="36"/>
-      <c r="P29" s="36"/>
-      <c r="Q29" s="36"/>
-      <c r="R29" s="36"/>
+      <c r="N29" s="38"/>
+      <c r="O29" s="38"/>
+      <c r="P29" s="38"/>
+      <c r="Q29" s="38"/>
+      <c r="R29" s="38"/>
     </row>
     <row r="31" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E31" s="9" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>

--- a/docs/deliverables/Femasys_Territory_Plan_v4.xlsx
+++ b/docs/deliverables/Femasys_Territory_Plan_v4.xlsx
@@ -25,120 +25,99 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="254">
-  <si>
-    <t xml:space="preserve">FemaSeed U.S. Territory Plan — v1 (Workload-Based Model)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THE HEADLINE: 28 reps is the right size — the data confirms it.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target universe = prescribers with ovulation-induction volume &gt;=5 (demonstrated repeat fertility behavior): 8,757 HCPs. At 28 reps that is 313 target HCPs per rep — inside the 275-325 workload band — and ~78 priority (&gt;=10) clinics per rep, inside the 65-80 band. Two independent workload axes both land in band at exactly 28. The workload-based method and the 28-territory ask agree.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TIERS: T1 = vol &gt;=20 (1,476 HCPs) | T2 = 10-19 (2,925) | T3 = 5-9 (4,356). Field plan built on T1-T3.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DECISIONS LOCKED IN THIS VERSION (all adjustable):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Universe: &gt;=5 volume. Scenario tab shows implied org size at other cuts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Building block: STATE. Multi-rep states (TX 3, CA 2) carry the split internally; drawing metro boundaries inside a state requires clinic addresses (see Phase 2). No geography invented.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Classification: locked v3 (clinic/physicians/associates removed; UWH routed academic). Every number reconciles to the approved Data Request waterfall: ALL 18,406 | &gt;=10 4,401 | Private &gt;=10 2,883 — exact matches. Puerto Rico excluded (matches Data Request universe).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4. Scoring weights (from the methodology thread): Target HCPs 40% / Clinics 25% / Fertility volume 15% / Women 25-39 10% / Income 5% / Education 5%. The three demographic components (20%) require the national ZIP census files, which are not yet appended — weights renormalized to HCPs 50% / Clinics 31.25% / Volume 18.75% for v1. Demographic slot is built; append shifts scores, not structure.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VALIDATION vs the prior analysis (six pilot states, patients/HCPs):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FL 6,638/1,107 (theirs 6,623/1,106) | NC 5,649/779 (5,651/781) | GA 5,391/683 (5,366/682) | TN 3,269/401 (3,278/402) | SC 2,825/364 (2,874/378) | AL 2,501/294 (2,508/297) — matches within ~1%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Their 18,652 rows vs our 18,522: minor filter delta in source versions; six-state agreement confirms same underlying data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HOW TO USE: On 'Territory Plan', the Reps column (blue) is adjustable. Per-rep loads and band flags recalculate live. Four single-state territories (OH, MI, FL, NY) run over-band and are the first candidates for a split or added rep once addresses enable intra-state boundaries.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOURCE-FILE RECONCILIATION (verified against Megan's July file directly):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18,652 total rows = 130 records with no practice identity (cannot be assigned to a clinic or classified; excluded) + 116 Puerto Rico rows (outside the Data Request universe) + 18,406 workable records. All 18,522 non-null NPIs carry identical volumes in both file versions (0 discrepancies).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WORKLOAD-BAND VERIFICATION AT 28 REPS (targets from the methodology thread):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target HCPs 313/rep (band 275-325: IN) | Priority clinics 78.1/rep (65-80: IN) | Tier 2 104.5/rep (100-130: IN) | Tier 1 52.7/rep (35-45: ABOVE band).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Tier 1 overage means the market holds more top-tier prescribers than the workload template assumed - evidence that 28 reps is a floor, not a ceiling.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V2 — NATIONAL CENSUS APPENDED (this version):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">All 52 state ZIP-census files applied (33,765 ZCTAs). Full scoring weights restored: Target HCPs 40% / Clinics 25% / Volume 15% / Women 25-39 10% / Income 5% / Education 5%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Income is population-weighted across ZCTAs with 3,144 missing-value sentinels excluded (census uses -666666666 for suppressed ZIPs; including them corrupts averages).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17 of 25 territory rankings shifted; hiring waves updated.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data-quality notes: the extract's women-25-39 total runs ~20% below published national figures (relative rankings unaffected; do not quote absolute counts as census fact), and the 15-19 age band column is unreliable in spots — it is not used anywhere in this model.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STRATEGIC CAVEAT — MANDATE STATES: the demographic weights promote Northeast territories (PA-NJ into Wave 1; New England to rank 8). Several of those are insurance-mandate states, which FemaSeed's go-to-market deliberately deprioritizes. The pure-opportunity ranking and the mandate-aware GTM disagree in the early waves. Resolve via the mandate overlay (Phase 2) using a verified CURRENT mandate list before committing hire sequencing — statuses have changed recently.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V3 — SCORING REVISIONS (this version, per Megan's direction):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Women's demographic window widened from 25-39 to 25-44 (adds the 40-44 census band). The lower bound stays at 25; the 15-19 band remains excluded (unreliable in the extract).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2. Education weight set to 0% (column retained for reference, not scored).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3. Income weight raised from 5% to 10%. Final v3 weights: Target HCPs 40% / Clinics 25% / Fertility volume 15% / Women 25-44 10% / Income 10% / Education 0%. (Sums to 100 with no renormalization.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effect: only 2 of 25 rankings changed; top 8 identical; hiring waves materially unchanged. The mandate-state caveat on Hiring Waves stands. Women 25-44 extract total (30.9M ex-PR) runs ~20-25% below published figures — valid for relative ranking, not for absolute quotation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V4 — UNIVERSE CHANGE (2026-07-21, per Megan/CEO direction):</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Universe changed from &gt;=5 volume to ALL MDs (18,405 per Waterfall A rev1, canonical). This reverses the v1 universe lock. The 28-rep workload rationale does not hold at this universe; reps are now sized per territory to the 275-325 HCPs/rep band.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOURCE DELTA (18,405 vs 18,406): v3's Read Me reconciles to 18,406; Waterfall A rev1 (canonical for v4) totals 18,405. A state-level diff isolates the difference to a single state: MICHIGAN (v3: 747 All MDs; Waterfall A rev1: 746). All other 50 state rows match exactly.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V4 SCORING (volume unavailable at this universe): no source provides per-state total volume across ALL MDs — row-level volume exists only for the &gt;=10 subset (4,424 physician rows, min volume 10). Reusing the &gt;=5-only volume column for an ALL-MD universe would misstate coverage, so the 15% volume weight is redistributed proportionally. Final v4 weights: All MDs 47.06% / All Clinics 29.41% / Women 25-44 11.76% / Income 11.76% (exactly 40/25/10/10 renormalized over 85). Each component is scored as share-of-territory-maximum, weighted, and rescaled to a 0-100 max. Clinics component now uses ALL clinics (consistent with the ALL-MD universe), not &gt;=10 priority clinics. Census columns (Women 25-44, Income) carried from v3 Territory Plan unchanged; v3's census data-quality caveats still apply.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V4 SOURCE-DATA FLAGS (Waterfall A rev1): (1) NV Private ALL MDs is written as 304 in the source, inconsistent with NV Total (150) and NV Academic (35), and with the source's own Private TOTAL (10,775), which only reconciles at NV Private = 115. v4 uses 115 = Total - Academic; flagged, not silently corrected at the TOTAL. (2) The waterfall's own row-level tabs contain 4,424 MDs at &gt;=10 vs 4,401 in the Waterfall A TOTAL row — a 23-MD source-internal discrepancy, unexplained in the file. Waterfall A TOTALs remain canonical.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V4 STRUCTURE NOTES: territory state groupings are v3's 25 territories, unchanged (no geography redrawn). 'Reps Required' = ROUND(All MDs / 300), minimum 1 — the headline staffing ('right reps for right areas'); it implies a 61-rep national org. A 28-rep constrained allocation (largest-remainder apportionment by All MDs) is shown alongside for comparison; under it, T24 (IA-SD-ND-WY) and T25 (SC) receive 0 reps — the 28-cap cannot cover the ALL-MD universe within band (657 HCPs/rep nationally). Hiring waves re-ranked by v4 score, keeping v3's wave sizes (7/5/7/6 territories); 18 of 25 rankings changed vs v3. The mandate-state caveat carries forward verbatim on Hiring Waves.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Note: v3's Read Me text above is carried forward from the v3 file; minor punctuation artifacts from text extraction were cleaned without changing wording or numbers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V4 ADDENDUM — 'Kathy - ALL Universe' tab: per-territory view in Kathy's layout (columns E-P), ALL-MD universe. Counts sum Waterfall A rev1 labeled columns only. Reps is a live formula (ROUND(All MDs/300), min 1) that Kathy can overwrite; per-rep loads, Academic Share, Score, and Rank recalculate. Score uses Kathy's weights — All MDs/Rep 20% / All Clinics/Rep 60% / Women 25-44 10% / Median Income 10% / Education 0% — each component min-max normalized 0-100 across the 25 territories.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">V4.1 — REP CAP CORRECTION (2026-07-22, per Rajiv): 28 reps is a HARD CAP; per-territory rep sizing (ROUND(All MDs/300)) and the largest-remainder 28-cap apportionment were removed as irrelevant. The Reps column on Territory Plan and the Kathy - ALL Universe tab now carry the original (v3) Territory Plan allocation — TX 3, CA-HI 2, all other territories 1 — totaling exactly 28, entered as adjustable inputs. At the ALL-MD universe this is ~657 MDs/rep on average; the plan functions as a prioritization model using the &gt;=10 (4,401) and &gt;=20 (1,476) tiers. Scoring, rankings, and hiring waves are unchanged by this correction (score does not depend on reps on the Territory Plan tab; the Kathy tab score, which weights per-rep loads, now reflects the 28-cap allocation).</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="247">
+  <si>
+    <t xml:space="preserve">FemaSeed U.S. Territory Plan — v4 (ALL-MD Universe, 28-Rep Hard Cap)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22 | Universe re-based per Megan/CEO direction. Supersedes v3; v1-v3 methodology history lives in the v3 file.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOURCES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Waterfall A rev1 (NATIONAL-Femasys_DataRequest_Waterfall-06222026-rev1_ME_FINAL NUMBERS.xlsx) — CANONICAL for all MD/clinic counts. Labeled columns only; stray unlabeled scratch columns excluded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Femasys_Territory_Plan_v3.xlsx — territory-to-state groupings (unchanged, no geography redrawn) and census columns (Women 25-44, Income, Education), carried unchanged.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puerto Rico excluded (matches Data Request universe).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UNIVERSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALL MDs = 18,405 (Waterfall A rev1 TOTAL). Full waterfall: ALL Clinics 5,862 | &gt;=10 MDs 4,401 | &gt;=20 MDs 1,476 | Private ALL 10,775 | Academic/Group ALL 7,630. State Market Summary reproduces the full state table; its TOTAL row ties to Waterfall A exactly.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source delta vs v3: v3 reconciled to 18,406. The 1-MD difference is Michigan (v3: 747; Waterfall A rev1: 746). All other states match exactly. Rev1 is the number of record.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier definition (per source): Volume = Femara + Clomid + Letrozole + Clomiphene prescribing; &gt;=10 and &gt;=20 are inclusive thresholds.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REP ALLOCATION — HARD CAP 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 reps is a hard cap; no rep-sizing math is used. Allocation (Territory Plan and Kathy tabs, blue adjustable inputs, total must stay 28):</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - 2 reps (10 total): T01 TX, T02 CA-HI, T03 NY, T05 FL, T06 PA-NJ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - 1 rep (18 total): all other territories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  - 0 reps: T24 IA-SD-ND-WY, T25 SC — unstaffed at the cap (~709 MDs, 3.9% of universe)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At 18,405 MDs, 28 reps average ~657 MDs each. The plan operates as a PRIORITIZATION model: reps work their territory top-down via the &gt;=20 tier (1,476 MDs) then the &gt;=10 tier (4,401), using the tiers on State Market Summary.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCORING (Territory Plan tab — rep-independent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No source provides volume for the full ALL-MD universe (row-level volume exists only for the &gt;=10 subset), so v3's 15% volume weight is redistributed proportionally rather than reusing partial-coverage volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Weights: All MDs 47.06% / All Clinics 29.41% / Women 25-44 11.76% / Income 11.76% (= 40/25/10/10 renormalized over 85). Each component scored as share of territory maximum, weighted, rescaled to 0-100 max. Education retained for reference at 0%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Result vs v3: 18 of 25 rankings changed. Top 8: CA-HI, TX, NY, PA-NJ, FL, New England, WA-OR-AK, IL.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KATHY - ALL UNIVERSE TAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kathy's layout (columns E-P). Counts sum Waterfall A rev1 labeled columns only. Score uses Kathy's weights — All MDs/Rep 20% / All Clinics/Rep 60% / Women 25-44 10% / Median Income 10% / Education 0% — min-max normalized 0-100. Note: these weights score PER-REP loads, so scores shift when Reps is edited; unstaffed territories carry no score.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIRING WAVES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Territories ranked by v4 score, wave sizes 7/5/7/6. Cumulative reps 12 / 17 / 24 / 28. Wave 4 includes the two unstaffed territories at 0 reps.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STRATEGIC CAVEAT — MANDATE STATES (carried from v3, still open): rankings are pure opportunity, not mandate-adjusted. Northeast (incl. mandate states) remains in early waves. Verify the current mandate list and re-sequence before committing hires — statuses have changed recently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATA FLAGS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. NV Private ALL MDs reads 304 in Waterfall A, inconsistent with NV Total (150), NV Academic (35), and the source's own Private TOTAL (10,775, which reconciles only at 115). v4 uses 115 = Total - Academic (highlighted on State Market Summary).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. The waterfall's row-level tabs contain 4,424 MDs at &gt;=10 vs 4,401 in the Waterfall A TOTAL row — a 23-MD source-internal gap, unexplained in the file. Waterfall A TOTALs remain canonical.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Census columns (from v3): Women 25-44 totals run ~20-25% below published census figures — valid for relative ranking, never for absolute quotation. Income is population-weighted with census suppression sentinels excluded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HOW TO USE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Blue cells are inputs. Reps columns (Territory Plan F, Kathy J) are adjustable — keep each column's total at 28; per-rep loads, Kathy score/rank, and wave rep counts recalculate. To re-shape a territory, move its states on State Market Summary (column T) and every dependent number recalculates.</t>
   </si>
   <si>
     <t xml:space="preserve">Target Universe Definition</t>
@@ -183,7 +162,7 @@
     <t xml:space="preserve">Volume &gt;=20</t>
   </si>
   <si>
-    <t xml:space="preserve">v3 note (retained): 'The &gt;=5 universe is the only definition where 28 reps lands inside the industry workload band.' v4 selects ALL prescribers per Megan/CEO direction. Rep count is a HARD CAP of 28 (~657 MDs/rep at this universe); the 'Reps @300/rep' column is scenario context only, not a staffing proposal. The 28 are allocated per the original Territory Plan (see Territory Plan tab).</t>
+    <t xml:space="preserve">Universe: ALL prescribers (18,405, Waterfall A rev1) per Megan/CEO direction. Rep count is a HARD CAP of 28 (~657 MDs/rep at this universe); the 'Reps @300/rep' column is scenario context only, not a staffing proposal. Allocation of the 28 is on the Territory Plan tab; T24 IA-SD-ND-WY and T25 SC are unstaffed at the cap.</t>
   </si>
   <si>
     <t xml:space="preserve">Source: Waterfall A rev1 (canonical). MDs = All MDs headline. NV Private All MDs derived as Total - Academic (source shows 304, inconsistent with its own totals; see Read Me).</t>
@@ -600,7 +579,7 @@
     <t xml:space="preserve">Greenville, Florence, Spartanburg</t>
   </si>
   <si>
-    <t xml:space="preserve">HARD CAP: 28 reps. The Reps column (blue) carries v3's original Territory Plan allocation (TX 3, CA-HI 2, all others 1 = 28) and is adjustable — per-rep loads, Score, Rank, and Hiring Wave figures recalculate; keep the column total at 28. Per-rep loads against the ALL-MD universe (18,405) average ~657 MDs/rep — use with the &gt;=10 / &gt;=20 tiers on State Market Summary as a prioritization model. Women 25-44 and Wtd Income carried from v3 unchanged (blue = input). Score v4 weights: All MDs 47.06% / All Clinics 29.41% / Women 25-44 11.76% / Income 11.76% (see Read Me).</t>
+    <t xml:space="preserve">HARD CAP: 28 reps. Allocation (blue, adjustable — keep the column total at 28): 2 reps each for TX, CA-HI, NY, FL, PA-NJ; 1 rep for 18 territories; 0 reps for T24 IA-SD-ND-WY and T25 SC (unstaffed at the cap). Per-rep loads, Score, Rank, and Hiring Wave figures recalculate. Against the ALL-MD universe (18,405) the 28 reps average ~657 MDs each — use with the &gt;=10 / &gt;=20 tiers on State Market Summary as a prioritization model. Women 25-44 and Wtd Income carried from v3 unchanged (blue = input). Score v4 weights: All MDs 47.06% / All Clinics 29.41% / Women 25-44 11.76% / Income 11.76% (see Read Me). Score does not depend on Reps.</t>
   </si>
   <si>
     <t xml:space="preserve">Wave</t>
@@ -657,10 +636,10 @@
     <t xml:space="preserve">CAVEAT: rankings are pure opportunity, not mandate-adjusted. Northeast (incl. mandate states) remains in early waves under v3 weights. Verify the current mandate list (Phase 2) and re-sequence before committing hires.</t>
   </si>
   <si>
-    <t xml:space="preserve">v4 notes: waves re-ranked by v4 score (18 of 25 rankings changed vs v3); wave sizes kept at v3's 7/5/7/6 territories. Rep counts use the hard 28-cap allocation from the original (v3) Territory Plan — TX 3, CA-HI 2, all others 1. Cumulative total = 28.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kathy - ALL Universe: all counts sum Waterfall A rev1 labeled columns only (via State Market Summary). Reps (J, blue) = the original Territory Plan 28-rep allocation (TX 3, CA-HI 2, others 1; hard cap 28) — overwrite freely, keep total 28; per-rep loads, Academic Share, Score, and Rank recalculate.</t>
+    <t xml:space="preserve">v4 notes: waves ranked by v4 score, wave sizes 7/5/7/6 territories. Rep counts use the hard 28-cap allocation (2 each: TX, CA-HI, NY, FL, PA-NJ; 1 each: 18 territories). Wave 4 lists T24 IA-SD-ND-WY and T25 SC at 0 reps — unstaffed at the cap. Cumulative total = 28.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kathy - ALL Universe: all counts sum Waterfall A rev1 labeled columns only (via State Market Summary). Reps (J, blue) = the 28-rep hard-cap allocation (2 each: TX, CA-HI, NY, FL, PA-NJ; 1 each: 18 territories; 0: IA-SD-ND-WY, SC) — overwrite freely, keep total 28; per-rep loads, Academic Share, Score, and Rank recalculate. Unstaffed territories show no per-rep figures or score.</t>
   </si>
   <si>
     <t xml:space="preserve">Weights:</t>
@@ -786,21 +765,20 @@
     <t xml:space="preserve">T25 SC</t>
   </si>
   <si>
-    <t xml:space="preserve">Score = min-max normalization (0-100 across territories) of All MDs/Rep (20%), All Clinics/Rep (60%), Women 25-44 (10%), Median Income (10%); Education 0% (displayed, not scored). Blue cells are inputs: Reps carries the original Territory Plan 28-rep allocation (hard cap); Women 25-44 / Median Income / Education carried from v3 Territory Plan unchanged (v3 census data-quality caveats apply). All MD/clinic counts (F-I) are sums of member states from Waterfall A rev1 labeled columns only; stray unlabeled scratch columns in the source were excluded.</t>
+    <t xml:space="preserve">Score = min-max normalization (0-100 across staffed territories) of All MDs/Rep (20%), All Clinics/Rep (60%), Women 25-44 (10%), Median Income (10%); Education 0% (displayed, not scored). Blue cells are inputs: Reps carries the 28-rep hard-cap allocation; Women 25-44 / Median Income / Education carried from v3 Territory Plan unchanged (v3 census data-quality caveats apply). All MD/clinic counts (F-I) are sums of member states from Waterfall A rev1 labeled columns only; stray unlabeled scratch columns in the source were excluded.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="\$#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="170" formatCode="\$#,##0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -944,7 +922,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1013,43 +991,31 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1069,39 +1035,11 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="169" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1373,191 +1311,177 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+    <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="3" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+    <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="3" t="s">
-        <v>12</v>
-      </c>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
-        <v>15</v>
+      <c r="A16" s="3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="3" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="3" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="3"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="2" t="s">
+    <row r="31" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="3"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3" t="s">
+    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="3" t="s">
+    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="3"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3" t="s">
         <v>30</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1589,27 +1513,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B2" s="6" t="n">
         <v>18405</v>
@@ -1623,15 +1547,15 @@
         <v>657</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B3" s="8" t="n">
         <v>8757</v>
@@ -1645,15 +1569,15 @@
         <v>313</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>4401</v>
@@ -1667,13 +1591,13 @@
         <v>157</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>1476</v>
@@ -1687,13 +1611,13 @@
         <v>53</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F5" s="7"/>
     </row>
     <row r="7" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -1730,7 +1654,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -1754,7 +1678,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="11" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="11"/>
@@ -1762,7 +1686,7 @@
       <c r="F2" s="11"/>
       <c r="G2" s="11"/>
       <c r="H2" s="11" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="11"/>
@@ -1770,7 +1694,7 @@
       <c r="L2" s="11"/>
       <c r="M2" s="11"/>
       <c r="N2" s="11" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="O2" s="11"/>
       <c r="P2" s="11"/>
@@ -1780,69 +1704,69 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="R3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="S3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="T3" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B4" s="8" t="n">
         <v>50</v>
@@ -1899,12 +1823,12 @@
         <v>0</v>
       </c>
       <c r="T4" s="12" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="B5" s="8" t="n">
         <v>294</v>
@@ -1961,12 +1885,12 @@
         <v>4</v>
       </c>
       <c r="T5" s="12" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B6" s="8" t="n">
         <v>180</v>
@@ -2023,12 +1947,12 @@
         <v>6</v>
       </c>
       <c r="T6" s="12" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="12" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>273</v>
@@ -2085,12 +2009,12 @@
         <v>4</v>
       </c>
       <c r="T7" s="12" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B8" s="8" t="n">
         <v>1499</v>
@@ -2147,12 +2071,12 @@
         <v>44</v>
       </c>
       <c r="T8" s="12" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B9" s="8" t="n">
         <v>352</v>
@@ -2209,12 +2133,12 @@
         <v>3</v>
       </c>
       <c r="T9" s="12" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B10" s="8" t="n">
         <v>254</v>
@@ -2271,12 +2195,12 @@
         <v>2</v>
       </c>
       <c r="T10" s="12" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B11" s="8" t="n">
         <v>34</v>
@@ -2333,12 +2257,12 @@
         <v>0</v>
       </c>
       <c r="T11" s="12" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="12" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B12" s="8" t="n">
         <v>28</v>
@@ -2395,12 +2319,12 @@
         <v>0</v>
       </c>
       <c r="T12" s="12" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="12" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="B13" s="8" t="n">
         <v>1107</v>
@@ -2457,12 +2381,12 @@
         <v>11</v>
       </c>
       <c r="T13" s="12" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="B14" s="8" t="n">
         <v>683</v>
@@ -2519,12 +2443,12 @@
         <v>3</v>
       </c>
       <c r="T14" s="12" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="12" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="B15" s="8" t="n">
         <v>80</v>
@@ -2581,12 +2505,12 @@
         <v>3</v>
       </c>
       <c r="T15" s="12" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="12" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="B16" s="8" t="n">
         <v>179</v>
@@ -2643,12 +2567,12 @@
         <v>4</v>
       </c>
       <c r="T16" s="12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="12" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="B17" s="8" t="n">
         <v>102</v>
@@ -2705,12 +2629,12 @@
         <v>3</v>
       </c>
       <c r="T17" s="12" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="12" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="B18" s="8" t="n">
         <v>718</v>
@@ -2767,12 +2691,12 @@
         <v>9</v>
       </c>
       <c r="T18" s="12" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B19" s="8" t="n">
         <v>442</v>
@@ -2829,12 +2753,12 @@
         <v>13</v>
       </c>
       <c r="T19" s="12" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="B20" s="8" t="n">
         <v>176</v>
@@ -2891,12 +2815,12 @@
         <v>3</v>
       </c>
       <c r="T20" s="12" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="12" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B21" s="8" t="n">
         <v>277</v>
@@ -2953,12 +2877,12 @@
         <v>8</v>
       </c>
       <c r="T21" s="12" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B22" s="8" t="n">
         <v>297</v>
@@ -3015,12 +2939,12 @@
         <v>7</v>
       </c>
       <c r="T22" s="12" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="12" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="B23" s="8" t="n">
         <v>353</v>
@@ -3077,12 +3001,12 @@
         <v>3</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="12" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B24" s="8" t="n">
         <v>320</v>
@@ -3139,12 +3063,12 @@
         <v>6</v>
       </c>
       <c r="T24" s="12" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="12" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="B25" s="8" t="n">
         <v>110</v>
@@ -3201,12 +3125,12 @@
         <v>1</v>
       </c>
       <c r="T25" s="12" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="12" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="B26" s="8" t="n">
         <v>746</v>
@@ -3263,12 +3187,12 @@
         <v>18</v>
       </c>
       <c r="T26" s="12" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="12" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="B27" s="8" t="n">
         <v>395</v>
@@ -3325,12 +3249,12 @@
         <v>3</v>
       </c>
       <c r="T27" s="12" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="12" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="B28" s="8" t="n">
         <v>387</v>
@@ -3387,12 +3311,12 @@
         <v>12</v>
       </c>
       <c r="T28" s="12" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="12" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="B29" s="8" t="n">
         <v>168</v>
@@ -3449,12 +3373,12 @@
         <v>2</v>
       </c>
       <c r="T29" s="12" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="B30" s="8" t="n">
         <v>69</v>
@@ -3511,12 +3435,12 @@
         <v>1</v>
       </c>
       <c r="T30" s="12" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="12" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B31" s="8" t="n">
         <v>779</v>
@@ -3573,12 +3497,12 @@
         <v>13</v>
       </c>
       <c r="T31" s="12" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B32" s="8" t="n">
         <v>53</v>
@@ -3635,12 +3559,12 @@
         <v>2</v>
       </c>
       <c r="T32" s="12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="12" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="B33" s="8" t="n">
         <v>142</v>
@@ -3697,12 +3621,12 @@
         <v>2</v>
       </c>
       <c r="T33" s="12" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="B34" s="8" t="n">
         <v>92</v>
@@ -3759,12 +3683,12 @@
         <v>1</v>
       </c>
       <c r="T34" s="12" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="12" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="B35" s="8" t="n">
         <v>428</v>
@@ -3821,12 +3745,12 @@
         <v>6</v>
       </c>
       <c r="T35" s="12" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="12" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="B36" s="8" t="n">
         <v>86</v>
@@ -3883,12 +3807,12 @@
         <v>0</v>
       </c>
       <c r="T36" s="12" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="12" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B37" s="8" t="n">
         <v>150</v>
@@ -3945,12 +3869,12 @@
         <v>1</v>
       </c>
       <c r="T37" s="12" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="12" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="B38" s="8" t="n">
         <v>1030</v>
@@ -4007,12 +3931,12 @@
         <v>24</v>
       </c>
       <c r="T38" s="12" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="12" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="B39" s="8" t="n">
         <v>795</v>
@@ -4069,12 +3993,12 @@
         <v>23</v>
       </c>
       <c r="T39" s="12" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="12" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="B40" s="8" t="n">
         <v>193</v>
@@ -4131,12 +4055,12 @@
         <v>4</v>
       </c>
       <c r="T40" s="12" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="12" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="B41" s="8" t="n">
         <v>304</v>
@@ -4193,12 +4117,12 @@
         <v>3</v>
       </c>
       <c r="T41" s="12" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="12" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B42" s="8" t="n">
         <v>607</v>
@@ -4255,12 +4179,12 @@
         <v>6</v>
       </c>
       <c r="T42" s="12" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="12" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B43" s="8" t="n">
         <v>77</v>
@@ -4317,12 +4241,12 @@
         <v>3</v>
       </c>
       <c r="T43" s="12" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="12" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B44" s="8" t="n">
         <v>364</v>
@@ -4379,12 +4303,12 @@
         <v>5</v>
       </c>
       <c r="T44" s="12" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="12" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="B45" s="8" t="n">
         <v>74</v>
@@ -4441,12 +4365,12 @@
         <v>4</v>
       </c>
       <c r="T45" s="12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="12" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="B46" s="8" t="n">
         <v>401</v>
@@ -4503,12 +4427,12 @@
         <v>6</v>
       </c>
       <c r="T46" s="12" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="12" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="B47" s="8" t="n">
         <v>1660</v>
@@ -4565,12 +4489,12 @@
         <v>24</v>
       </c>
       <c r="T47" s="12" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="12" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="B48" s="8" t="n">
         <v>198</v>
@@ -4627,12 +4551,12 @@
         <v>4</v>
       </c>
       <c r="T48" s="12" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="12" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="B49" s="8" t="n">
         <v>478</v>
@@ -4689,12 +4613,12 @@
         <v>8</v>
       </c>
       <c r="T49" s="12" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="12" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="B50" s="8" t="n">
         <v>32</v>
@@ -4751,12 +4675,12 @@
         <v>3</v>
       </c>
       <c r="T50" s="12" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="12" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="B51" s="8" t="n">
         <v>380</v>
@@ -4813,12 +4737,12 @@
         <v>7</v>
       </c>
       <c r="T51" s="12" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="12" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="B52" s="8" t="n">
         <v>363</v>
@@ -4875,12 +4799,12 @@
         <v>9</v>
       </c>
       <c r="T52" s="12" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="12" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B53" s="8" t="n">
         <v>107</v>
@@ -4937,12 +4861,12 @@
         <v>2</v>
       </c>
       <c r="T53" s="12" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="12" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="B54" s="8" t="n">
         <v>39</v>
@@ -4999,12 +4923,12 @@
         <v>0</v>
       </c>
       <c r="T54" s="12" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="14" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B55" s="15" t="n">
         <f aca="false">SUM(B4:B54)</f>
@@ -5104,1483 +5028,1483 @@
   <dimension ref="A1:O29"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="9"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="B1" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="G1" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="H1" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="I1" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="J1" s="16" t="s">
+        <v>140</v>
+      </c>
+      <c r="K1" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="L1" s="16" t="s">
         <v>142</v>
       </c>
-      <c r="D1" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="E1" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="F1" s="16" t="s">
+      <c r="M1" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="N1" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="H1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>145</v>
       </c>
-      <c r="I1" s="16" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="J1" s="16" t="s">
-        <v>147</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>148</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="M1" s="16" t="s">
-        <v>150</v>
-      </c>
-      <c r="N1" s="16" t="s">
-        <v>151</v>
-      </c>
-      <c r="O1" s="16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>131</v>
-      </c>
-      <c r="C2" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A2,'State Market Summary'!$B$4:$B$54)</f>
         <v>1660</v>
       </c>
-      <c r="E2" s="18" t="n">
+      <c r="E2" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A2,'State Market Summary'!$C$4:$C$54)</f>
         <v>540</v>
       </c>
-      <c r="F2" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" s="18" t="n">
-        <f aca="false">ROUND(D2/F2,0)</f>
-        <v>553</v>
-      </c>
-      <c r="H2" s="20" t="n">
-        <f aca="false">ROUND(E2/F2,1)</f>
-        <v>180</v>
-      </c>
-      <c r="I2" s="21" t="n">
+      <c r="F2" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <f aca="false">IF(F2=0,"unstaffed",ROUND(D2/F2,0))</f>
+        <v>830</v>
+      </c>
+      <c r="H2" s="18" t="n">
+        <f aca="false">IF(F2=0,"unstaffed",ROUND(E2/F2,1))</f>
+        <v>270</v>
+      </c>
+      <c r="I2" s="19" t="n">
         <v>3090173</v>
       </c>
-      <c r="J2" s="22" t="n">
+      <c r="J2" s="20" t="n">
         <v>78473</v>
       </c>
-      <c r="K2" s="23" t="n">
+      <c r="K2" s="21" t="n">
         <f aca="false">ROUND((40*D2/MAX($D$2:$D$26)+25*E2/MAX($E$2:$E$26)+10*I2/MAX($I$2:$I$26)+10*J2/MAX($J$2:$J$26))/85*100,1)</f>
         <v>89.1</v>
       </c>
-      <c r="L2" s="17" t="n">
+      <c r="L2" s="7" t="n">
         <f aca="false">RANK(K2,$K$2:$K$26)</f>
         <v>2</v>
       </c>
-      <c r="M2" s="19" t="n">
+      <c r="M2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="N2" s="17" t="n">
+      <c r="N2" s="7" t="n">
         <f aca="false">M2-L2</f>
         <v>-1</v>
       </c>
-      <c r="O2" s="17" t="n">
+      <c r="O2" s="7" t="n">
         <f aca="false">IF(L2&lt;=7,1,IF(L2&lt;=12,2,IF(L2&lt;=19,3,4)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>155</v>
-      </c>
-      <c r="D3" s="18" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D3" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A3,'State Market Summary'!$B$4:$B$54)</f>
         <v>1579</v>
       </c>
-      <c r="E3" s="18" t="n">
+      <c r="E3" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A3,'State Market Summary'!$C$4:$C$54)</f>
         <v>688</v>
       </c>
-      <c r="F3" s="19" t="n">
+      <c r="F3" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="G3" s="18" t="n">
-        <f aca="false">ROUND(D3/F3,0)</f>
+      <c r="G3" s="8" t="n">
+        <f aca="false">IF(F3=0,"unstaffed",ROUND(D3/F3,0))</f>
         <v>790</v>
       </c>
-      <c r="H3" s="20" t="n">
-        <f aca="false">ROUND(E3/F3,1)</f>
+      <c r="H3" s="18" t="n">
+        <f aca="false">IF(F3=0,"unstaffed",ROUND(E3/F3,1))</f>
         <v>344</v>
       </c>
-      <c r="I3" s="21" t="n">
+      <c r="I3" s="19" t="n">
         <v>3819366</v>
       </c>
-      <c r="J3" s="22" t="n">
+      <c r="J3" s="20" t="n">
         <v>97969</v>
       </c>
-      <c r="K3" s="23" t="n">
+      <c r="K3" s="21" t="n">
         <f aca="false">ROUND((40*D3/MAX($D$2:$D$26)+25*E3/MAX($E$2:$E$26)+10*I3/MAX($I$2:$I$26)+10*J3/MAX($J$2:$J$26))/85*100,1)</f>
         <v>97.7</v>
       </c>
-      <c r="L3" s="17" t="n">
+      <c r="L3" s="7" t="n">
         <f aca="false">RANK(K3,$K$2:$K$26)</f>
         <v>1</v>
       </c>
-      <c r="M3" s="19" t="n">
+      <c r="M3" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="N3" s="17" t="n">
+      <c r="N3" s="7" t="n">
         <f aca="false">M3-L3</f>
         <v>1</v>
       </c>
-      <c r="O3" s="17" t="n">
+      <c r="O3" s="7" t="n">
         <f aca="false">IF(L3&lt;=7,1,IF(L3&lt;=12,2,IF(L3&lt;=19,3,4)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="D4" s="18" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D4" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A4,'State Market Summary'!$B$4:$B$54)</f>
         <v>1030</v>
       </c>
-      <c r="E4" s="18" t="n">
+      <c r="E4" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A4,'State Market Summary'!$C$4:$C$54)</f>
         <v>404</v>
       </c>
-      <c r="F4" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" s="18" t="n">
-        <f aca="false">ROUND(D4/F4,0)</f>
-        <v>1030</v>
-      </c>
-      <c r="H4" s="20" t="n">
-        <f aca="false">ROUND(E4/F4,1)</f>
-        <v>404</v>
-      </c>
-      <c r="I4" s="21" t="n">
+      <c r="F4" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G4" s="8" t="n">
+        <f aca="false">IF(F4=0,"unstaffed",ROUND(D4/F4,0))</f>
+        <v>515</v>
+      </c>
+      <c r="H4" s="18" t="n">
+        <f aca="false">IF(F4=0,"unstaffed",ROUND(E4/F4,1))</f>
+        <v>202</v>
+      </c>
+      <c r="I4" s="19" t="n">
         <v>1726412</v>
       </c>
-      <c r="J4" s="22" t="n">
+      <c r="J4" s="20" t="n">
         <v>89542</v>
       </c>
-      <c r="K4" s="23" t="n">
+      <c r="K4" s="21" t="n">
         <f aca="false">ROUND((40*D4/MAX($D$2:$D$26)+25*E4/MAX($E$2:$E$26)+10*I4/MAX($I$2:$I$26)+10*J4/MAX($J$2:$J$26))/85*100,1)</f>
         <v>62.5</v>
       </c>
-      <c r="L4" s="17" t="n">
+      <c r="L4" s="7" t="n">
         <f aca="false">RANK(K4,$K$2:$K$26)</f>
         <v>3</v>
       </c>
-      <c r="M4" s="19" t="n">
+      <c r="M4" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="N4" s="17" t="n">
+      <c r="N4" s="7" t="n">
         <f aca="false">M4-L4</f>
         <v>0</v>
       </c>
-      <c r="O4" s="17" t="n">
+      <c r="O4" s="7" t="n">
         <f aca="false">IF(L4&lt;=7,1,IF(L4&lt;=12,2,IF(L4&lt;=19,3,4)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>157</v>
-      </c>
-      <c r="D5" s="18" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A5,'State Market Summary'!$B$4:$B$54)</f>
         <v>795</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A5,'State Market Summary'!$C$4:$C$54)</f>
         <v>178</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G5" s="18" t="n">
-        <f aca="false">ROUND(D5/F5,0)</f>
+      <c r="G5" s="8" t="n">
+        <f aca="false">IF(F5=0,"unstaffed",ROUND(D5/F5,0))</f>
         <v>795</v>
       </c>
-      <c r="H5" s="20" t="n">
-        <f aca="false">ROUND(E5/F5,1)</f>
+      <c r="H5" s="18" t="n">
+        <f aca="false">IF(F5=0,"unstaffed",ROUND(E5/F5,1))</f>
         <v>178</v>
       </c>
-      <c r="I5" s="21" t="n">
+      <c r="I5" s="19" t="n">
         <v>1089150</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="20" t="n">
         <v>71229</v>
       </c>
-      <c r="K5" s="23" t="n">
+      <c r="K5" s="21" t="n">
         <f aca="false">ROUND((40*D5/MAX($D$2:$D$26)+25*E5/MAX($E$2:$E$26)+10*I5/MAX($I$2:$I$26)+10*J5/MAX($J$2:$J$26))/85*100,1)</f>
         <v>42.1</v>
       </c>
-      <c r="L5" s="17" t="n">
+      <c r="L5" s="7" t="n">
         <f aca="false">RANK(K5,$K$2:$K$26)</f>
         <v>10</v>
       </c>
-      <c r="M5" s="19" t="n">
+      <c r="M5" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="N5" s="17" t="n">
+      <c r="N5" s="7" t="n">
         <f aca="false">M5-L5</f>
         <v>-6</v>
       </c>
-      <c r="O5" s="17" t="n">
+      <c r="O5" s="7" t="n">
         <f aca="false">IF(L5&lt;=7,1,IF(L5&lt;=12,2,IF(L5&lt;=19,3,4)))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D6" s="18" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A6,'State Market Summary'!$B$4:$B$54)</f>
         <v>1107</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A6,'State Market Summary'!$C$4:$C$54)</f>
         <v>273</v>
       </c>
-      <c r="F6" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <f aca="false">ROUND(D6/F6,0)</f>
-        <v>1107</v>
-      </c>
-      <c r="H6" s="20" t="n">
-        <f aca="false">ROUND(E6/F6,1)</f>
-        <v>273</v>
-      </c>
-      <c r="I6" s="21" t="n">
+      <c r="F6" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <f aca="false">IF(F6=0,"unstaffed",ROUND(D6/F6,0))</f>
+        <v>554</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <f aca="false">IF(F6=0,"unstaffed",ROUND(E6/F6,1))</f>
+        <v>136.5</v>
+      </c>
+      <c r="I6" s="19" t="n">
         <v>1780020</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="20" t="n">
         <v>71602</v>
       </c>
-      <c r="K6" s="23" t="n">
+      <c r="K6" s="21" t="n">
         <f aca="false">ROUND((40*D6/MAX($D$2:$D$26)+25*E6/MAX($E$2:$E$26)+10*I6/MAX($I$2:$I$26)+10*J6/MAX($J$2:$J$26))/85*100,1)</f>
         <v>57.1</v>
       </c>
-      <c r="L6" s="17" t="n">
+      <c r="L6" s="7" t="n">
         <f aca="false">RANK(K6,$K$2:$K$26)</f>
         <v>5</v>
       </c>
-      <c r="M6" s="19" t="n">
+      <c r="M6" s="17" t="n">
         <v>5</v>
       </c>
-      <c r="N6" s="17" t="n">
+      <c r="N6" s="7" t="n">
         <f aca="false">M6-L6</f>
         <v>0</v>
       </c>
-      <c r="O6" s="17" t="n">
+      <c r="O6" s="7" t="n">
         <f aca="false">IF(L6&lt;=7,1,IF(L6&lt;=12,2,IF(L6&lt;=19,3,4)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>160</v>
-      </c>
-      <c r="D7" s="18" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="D7" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A7,'State Market Summary'!$B$4:$B$54)</f>
         <v>1035</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A7,'State Market Summary'!$C$4:$C$54)</f>
         <v>338</v>
       </c>
-      <c r="F7" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <f aca="false">ROUND(D7/F7,0)</f>
-        <v>1035</v>
-      </c>
-      <c r="H7" s="20" t="n">
-        <f aca="false">ROUND(E7/F7,1)</f>
-        <v>338</v>
-      </c>
-      <c r="I7" s="21" t="n">
+      <c r="F7" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <f aca="false">IF(F7=0,"unstaffed",ROUND(D7/F7,0))</f>
+        <v>518</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <f aca="false">IF(F7=0,"unstaffed",ROUND(E7/F7,1))</f>
+        <v>169</v>
+      </c>
+      <c r="I7" s="19" t="n">
         <v>1985432</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="20" t="n">
         <v>89604</v>
       </c>
-      <c r="K7" s="23" t="n">
+      <c r="K7" s="21" t="n">
         <f aca="false">ROUND((40*D7/MAX($D$2:$D$26)+25*E7/MAX($E$2:$E$26)+10*I7/MAX($I$2:$I$26)+10*J7/MAX($J$2:$J$26))/85*100,1)</f>
         <v>60.7</v>
       </c>
-      <c r="L7" s="17" t="n">
+      <c r="L7" s="7" t="n">
         <f aca="false">RANK(K7,$K$2:$K$26)</f>
         <v>4</v>
       </c>
-      <c r="M7" s="19" t="n">
+      <c r="M7" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="N7" s="17" t="n">
+      <c r="N7" s="7" t="n">
         <f aca="false">M7-L7</f>
         <v>2</v>
       </c>
-      <c r="O7" s="17" t="n">
+      <c r="O7" s="7" t="n">
         <f aca="false">IF(L7&lt;=7,1,IF(L7&lt;=12,2,IF(L7&lt;=19,3,4)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>161</v>
-      </c>
-      <c r="D8" s="18" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A8,'State Market Summary'!$B$4:$B$54)</f>
         <v>746</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A8,'State Market Summary'!$C$4:$C$54)</f>
         <v>207</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G8" s="18" t="n">
-        <f aca="false">ROUND(D8/F8,0)</f>
+      <c r="G8" s="8" t="n">
+        <f aca="false">IF(F8=0,"unstaffed",ROUND(D8/F8,0))</f>
         <v>746</v>
       </c>
-      <c r="H8" s="20" t="n">
-        <f aca="false">ROUND(E8/F8,1)</f>
+      <c r="H8" s="18" t="n">
+        <f aca="false">IF(F8=0,"unstaffed",ROUND(E8/F8,1))</f>
         <v>207</v>
       </c>
-      <c r="I8" s="21" t="n">
+      <c r="I8" s="19" t="n">
         <v>910821</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="20" t="n">
         <v>72965</v>
       </c>
-      <c r="K8" s="23" t="n">
+      <c r="K8" s="21" t="n">
         <f aca="false">ROUND((40*D8/MAX($D$2:$D$26)+25*E8/MAX($E$2:$E$26)+10*I8/MAX($I$2:$I$26)+10*J8/MAX($J$2:$J$26))/85*100,1)</f>
         <v>41.6</v>
       </c>
-      <c r="L8" s="17" t="n">
+      <c r="L8" s="7" t="n">
         <f aca="false">RANK(K8,$K$2:$K$26)</f>
         <v>11</v>
       </c>
-      <c r="M8" s="19" t="n">
+      <c r="M8" s="17" t="n">
         <v>7</v>
       </c>
-      <c r="N8" s="17" t="n">
+      <c r="N8" s="7" t="n">
         <f aca="false">M8-L8</f>
         <v>-4</v>
       </c>
-      <c r="O8" s="17" t="n">
+      <c r="O8" s="7" t="n">
         <f aca="false">IF(L8&lt;=7,1,IF(L8&lt;=12,2,IF(L8&lt;=19,3,4)))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>162</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>163</v>
-      </c>
-      <c r="D9" s="18" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="D9" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A9,'State Market Summary'!$B$4:$B$54)</f>
         <v>918</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A9,'State Market Summary'!$C$4:$C$54)</f>
         <v>279</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G9" s="18" t="n">
-        <f aca="false">ROUND(D9/F9,0)</f>
+      <c r="G9" s="8" t="n">
+        <f aca="false">IF(F9=0,"unstaffed",ROUND(D9/F9,0))</f>
         <v>918</v>
       </c>
-      <c r="H9" s="20" t="n">
-        <f aca="false">ROUND(E9/F9,1)</f>
+      <c r="H9" s="18" t="n">
+        <f aca="false">IF(F9=0,"unstaffed",ROUND(E9/F9,1))</f>
         <v>279</v>
       </c>
-      <c r="I9" s="21" t="n">
+      <c r="I9" s="19" t="n">
         <v>1294309</v>
       </c>
-      <c r="J9" s="22" t="n">
+      <c r="J9" s="20" t="n">
         <v>97019</v>
       </c>
-      <c r="K9" s="23" t="n">
+      <c r="K9" s="21" t="n">
         <f aca="false">ROUND((40*D9/MAX($D$2:$D$26)+25*E9/MAX($E$2:$E$26)+10*I9/MAX($I$2:$I$26)+10*J9/MAX($J$2:$J$26))/85*100,1)</f>
         <v>53.6</v>
       </c>
-      <c r="L9" s="17" t="n">
+      <c r="L9" s="7" t="n">
         <f aca="false">RANK(K9,$K$2:$K$26)</f>
         <v>6</v>
       </c>
-      <c r="M9" s="19" t="n">
+      <c r="M9" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="N9" s="17" t="n">
+      <c r="N9" s="7" t="n">
         <f aca="false">M9-L9</f>
         <v>2</v>
       </c>
-      <c r="O9" s="17" t="n">
+      <c r="O9" s="7" t="n">
         <f aca="false">IF(L9&lt;=7,1,IF(L9&lt;=12,2,IF(L9&lt;=19,3,4)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>105</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>165</v>
-      </c>
-      <c r="D10" s="18" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A10,'State Market Summary'!$B$4:$B$54)</f>
         <v>758</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A10,'State Market Summary'!$C$4:$C$54)</f>
         <v>176</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G10" s="18" t="n">
-        <f aca="false">ROUND(D10/F10,0)</f>
+      <c r="G10" s="8" t="n">
+        <f aca="false">IF(F10=0,"unstaffed",ROUND(D10/F10,0))</f>
         <v>758</v>
       </c>
-      <c r="H10" s="20" t="n">
-        <f aca="false">ROUND(E10/F10,1)</f>
+      <c r="H10" s="18" t="n">
+        <f aca="false">IF(F10=0,"unstaffed",ROUND(E10/F10,1))</f>
         <v>176</v>
       </c>
-      <c r="I10" s="21" t="n">
+      <c r="I10" s="19" t="n">
         <v>1084210</v>
       </c>
-      <c r="J10" s="22" t="n">
+      <c r="J10" s="20" t="n">
         <v>81797</v>
       </c>
-      <c r="K10" s="23" t="n">
+      <c r="K10" s="21" t="n">
         <f aca="false">ROUND((40*D10/MAX($D$2:$D$26)+25*E10/MAX($E$2:$E$26)+10*I10/MAX($I$2:$I$26)+10*J10/MAX($J$2:$J$26))/85*100,1)</f>
         <v>42.2</v>
       </c>
-      <c r="L10" s="17" t="n">
+      <c r="L10" s="7" t="n">
         <f aca="false">RANK(K10,$K$2:$K$26)</f>
         <v>9</v>
       </c>
-      <c r="M10" s="19" t="n">
+      <c r="M10" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="N10" s="17" t="n">
+      <c r="N10" s="7" t="n">
         <f aca="false">M10-L10</f>
         <v>0</v>
       </c>
-      <c r="O10" s="17" t="n">
+      <c r="O10" s="7" t="n">
         <f aca="false">IF(L10&lt;=7,1,IF(L10&lt;=12,2,IF(L10&lt;=19,3,4)))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" s="18" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A11,'State Market Summary'!$B$4:$B$54)</f>
         <v>664</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A11,'State Market Summary'!$C$4:$C$54)</f>
         <v>200</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G11" s="18" t="n">
-        <f aca="false">ROUND(D11/F11,0)</f>
+      <c r="G11" s="8" t="n">
+        <f aca="false">IF(F11=0,"unstaffed",ROUND(D11/F11,0))</f>
         <v>664</v>
       </c>
-      <c r="H11" s="20" t="n">
-        <f aca="false">ROUND(E11/F11,1)</f>
+      <c r="H11" s="18" t="n">
+        <f aca="false">IF(F11=0,"unstaffed",ROUND(E11/F11,1))</f>
         <v>200</v>
       </c>
-      <c r="I11" s="21" t="n">
+      <c r="I11" s="19" t="n">
         <v>995376</v>
       </c>
-      <c r="J11" s="22" t="n">
+      <c r="J11" s="20" t="n">
         <v>67472</v>
       </c>
-      <c r="K11" s="23" t="n">
+      <c r="K11" s="21" t="n">
         <f aca="false">ROUND((40*D11/MAX($D$2:$D$26)+25*E11/MAX($E$2:$E$26)+10*I11/MAX($I$2:$I$26)+10*J11/MAX($J$2:$J$26))/85*100,1)</f>
         <v>38.5</v>
       </c>
-      <c r="L11" s="17" t="n">
+      <c r="L11" s="7" t="n">
         <f aca="false">RANK(K11,$K$2:$K$26)</f>
         <v>15</v>
       </c>
-      <c r="M11" s="19" t="n">
+      <c r="M11" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="N11" s="17" t="n">
+      <c r="N11" s="7" t="n">
         <f aca="false">M11-L11</f>
         <v>-5</v>
       </c>
-      <c r="O11" s="17" t="n">
+      <c r="O11" s="7" t="n">
         <f aca="false">IF(L11&lt;=7,1,IF(L11&lt;=12,2,IF(L11&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>168</v>
-      </c>
-      <c r="D12" s="18" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D12" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A12,'State Market Summary'!$B$4:$B$54)</f>
         <v>683</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A12,'State Market Summary'!$C$4:$C$54)</f>
         <v>220</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G12" s="18" t="n">
-        <f aca="false">ROUND(D12/F12,0)</f>
+      <c r="G12" s="8" t="n">
+        <f aca="false">IF(F12=0,"unstaffed",ROUND(D12/F12,0))</f>
         <v>683</v>
       </c>
-      <c r="H12" s="20" t="n">
-        <f aca="false">ROUND(E12/F12,1)</f>
+      <c r="H12" s="18" t="n">
+        <f aca="false">IF(F12=0,"unstaffed",ROUND(E12/F12,1))</f>
         <v>220</v>
       </c>
-      <c r="I12" s="21" t="n">
+      <c r="I12" s="19" t="n">
         <v>1070611</v>
       </c>
-      <c r="J12" s="22" t="n">
+      <c r="J12" s="20" t="n">
         <v>75694</v>
       </c>
-      <c r="K12" s="23" t="n">
+      <c r="K12" s="21" t="n">
         <f aca="false">ROUND((40*D12/MAX($D$2:$D$26)+25*E12/MAX($E$2:$E$26)+10*I12/MAX($I$2:$I$26)+10*J12/MAX($J$2:$J$26))/85*100,1)</f>
         <v>41.2</v>
       </c>
-      <c r="L12" s="17" t="n">
+      <c r="L12" s="7" t="n">
         <f aca="false">RANK(K12,$K$2:$K$26)</f>
         <v>13</v>
       </c>
-      <c r="M12" s="19" t="n">
+      <c r="M12" s="17" t="n">
         <v>11</v>
       </c>
-      <c r="N12" s="17" t="n">
+      <c r="N12" s="7" t="n">
         <f aca="false">M12-L12</f>
         <v>-2</v>
       </c>
-      <c r="O12" s="17" t="n">
+      <c r="O12" s="7" t="n">
         <f aca="false">IF(L12&lt;=7,1,IF(L12&lt;=12,2,IF(L12&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="D13" s="18" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D13" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A13,'State Market Summary'!$B$4:$B$54)</f>
         <v>734</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A13,'State Market Summary'!$C$4:$C$54)</f>
         <v>225</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="18" t="n">
-        <f aca="false">ROUND(D13/F13,0)</f>
+      <c r="G13" s="8" t="n">
+        <f aca="false">IF(F13=0,"unstaffed",ROUND(D13/F13,0))</f>
         <v>734</v>
       </c>
-      <c r="H13" s="20" t="n">
-        <f aca="false">ROUND(E13/F13,1)</f>
+      <c r="H13" s="18" t="n">
+        <f aca="false">IF(F13=0,"unstaffed",ROUND(E13/F13,1))</f>
         <v>225</v>
       </c>
-      <c r="I13" s="21" t="n">
+      <c r="I13" s="19" t="n">
         <v>1119028</v>
       </c>
-      <c r="J13" s="22" t="n">
+      <c r="J13" s="20" t="n">
         <v>90198</v>
       </c>
-      <c r="K13" s="23" t="n">
+      <c r="K13" s="21" t="n">
         <f aca="false">ROUND((40*D13/MAX($D$2:$D$26)+25*E13/MAX($E$2:$E$26)+10*I13/MAX($I$2:$I$26)+10*J13/MAX($J$2:$J$26))/85*100,1)</f>
         <v>44.7</v>
       </c>
-      <c r="L13" s="17" t="n">
+      <c r="L13" s="7" t="n">
         <f aca="false">RANK(K13,$K$2:$K$26)</f>
         <v>7</v>
       </c>
-      <c r="M13" s="19" t="n">
+      <c r="M13" s="17" t="n">
         <v>12</v>
       </c>
-      <c r="N13" s="17" t="n">
+      <c r="N13" s="7" t="n">
         <f aca="false">M13-L13</f>
         <v>5</v>
       </c>
-      <c r="O13" s="17" t="n">
+      <c r="O13" s="7" t="n">
         <f aca="false">IF(L13&lt;=7,1,IF(L13&lt;=12,2,IF(L13&lt;=19,3,4)))</f>
         <v>1</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17" t="s">
-        <v>110</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>109</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="D14" s="18" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D14" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A14,'State Market Summary'!$B$4:$B$54)</f>
         <v>779</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A14,'State Market Summary'!$C$4:$C$54)</f>
         <v>181</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="18" t="n">
-        <f aca="false">ROUND(D14/F14,0)</f>
+      <c r="G14" s="8" t="n">
+        <f aca="false">IF(F14=0,"unstaffed",ROUND(D14/F14,0))</f>
         <v>779</v>
       </c>
-      <c r="H14" s="20" t="n">
-        <f aca="false">ROUND(E14/F14,1)</f>
+      <c r="H14" s="18" t="n">
+        <f aca="false">IF(F14=0,"unstaffed",ROUND(E14/F14,1))</f>
         <v>181</v>
       </c>
-      <c r="I14" s="21" t="n">
+      <c r="I14" s="19" t="n">
         <v>975468</v>
       </c>
-      <c r="J14" s="22" t="n">
+      <c r="J14" s="20" t="n">
         <v>70436</v>
       </c>
-      <c r="K14" s="23" t="n">
+      <c r="K14" s="21" t="n">
         <f aca="false">ROUND((40*D14/MAX($D$2:$D$26)+25*E14/MAX($E$2:$E$26)+10*I14/MAX($I$2:$I$26)+10*J14/MAX($J$2:$J$26))/85*100,1)</f>
         <v>41.3</v>
       </c>
-      <c r="L14" s="17" t="n">
+      <c r="L14" s="7" t="n">
         <f aca="false">RANK(K14,$K$2:$K$26)</f>
         <v>12</v>
       </c>
-      <c r="M14" s="19" t="n">
+      <c r="M14" s="17" t="n">
         <v>13</v>
       </c>
-      <c r="N14" s="17" t="n">
+      <c r="N14" s="7" t="n">
         <f aca="false">M14-L14</f>
         <v>1</v>
       </c>
-      <c r="O14" s="17" t="n">
+      <c r="O14" s="7" t="n">
         <f aca="false">IF(L14&lt;=7,1,IF(L14&lt;=12,2,IF(L14&lt;=19,3,4)))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>172</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>173</v>
-      </c>
-      <c r="D15" s="18" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D15" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A15,'State Market Summary'!$B$4:$B$54)</f>
         <v>597</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A15,'State Market Summary'!$C$4:$C$54)</f>
         <v>198</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G15" s="18" t="n">
-        <f aca="false">ROUND(D15/F15,0)</f>
+      <c r="G15" s="8" t="n">
+        <f aca="false">IF(F15=0,"unstaffed",ROUND(D15/F15,0))</f>
         <v>597</v>
       </c>
-      <c r="H15" s="20" t="n">
-        <f aca="false">ROUND(E15/F15,1)</f>
+      <c r="H15" s="18" t="n">
+        <f aca="false">IF(F15=0,"unstaffed",ROUND(E15/F15,1))</f>
         <v>198</v>
       </c>
-      <c r="I15" s="21" t="n">
+      <c r="I15" s="19" t="n">
         <v>1097099</v>
       </c>
-      <c r="J15" s="22" t="n">
+      <c r="J15" s="20" t="n">
         <v>68598</v>
       </c>
-      <c r="K15" s="23" t="n">
+      <c r="K15" s="21" t="n">
         <f aca="false">ROUND((40*D15/MAX($D$2:$D$26)+25*E15/MAX($E$2:$E$26)+10*I15/MAX($I$2:$I$26)+10*J15/MAX($J$2:$J$26))/85*100,1)</f>
         <v>37</v>
       </c>
-      <c r="L15" s="17" t="n">
+      <c r="L15" s="7" t="n">
         <f aca="false">RANK(K15,$K$2:$K$26)</f>
         <v>17</v>
       </c>
-      <c r="M15" s="19" t="n">
+      <c r="M15" s="17" t="n">
         <v>14</v>
       </c>
-      <c r="N15" s="17" t="n">
+      <c r="N15" s="7" t="n">
         <f aca="false">M15-L15</f>
         <v>-3</v>
       </c>
-      <c r="O15" s="17" t="n">
+      <c r="O15" s="7" t="n">
         <f aca="false">IF(L15&lt;=7,1,IF(L15&lt;=12,2,IF(L15&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>174</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="D16" s="18" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D16" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A16,'State Market Summary'!$B$4:$B$54)</f>
         <v>594</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A16,'State Market Summary'!$C$4:$C$54)</f>
         <v>231</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G16" s="18" t="n">
-        <f aca="false">ROUND(D16/F16,0)</f>
+      <c r="G16" s="8" t="n">
+        <f aca="false">IF(F16=0,"unstaffed",ROUND(D16/F16,0))</f>
         <v>594</v>
       </c>
-      <c r="H16" s="20" t="n">
-        <f aca="false">ROUND(E16/F16,1)</f>
+      <c r="H16" s="18" t="n">
+        <f aca="false">IF(F16=0,"unstaffed",ROUND(E16/F16,1))</f>
         <v>231</v>
       </c>
-      <c r="I16" s="21" t="n">
+      <c r="I16" s="19" t="n">
         <v>1257732</v>
       </c>
-      <c r="J16" s="22" t="n">
+      <c r="J16" s="20" t="n">
         <v>75026</v>
       </c>
-      <c r="K16" s="23" t="n">
+      <c r="K16" s="21" t="n">
         <f aca="false">ROUND((40*D16/MAX($D$2:$D$26)+25*E16/MAX($E$2:$E$26)+10*I16/MAX($I$2:$I$26)+10*J16/MAX($J$2:$J$26))/85*100,1)</f>
         <v>39.6</v>
       </c>
-      <c r="L16" s="17" t="n">
+      <c r="L16" s="7" t="n">
         <f aca="false">RANK(K16,$K$2:$K$26)</f>
         <v>14</v>
       </c>
-      <c r="M16" s="19" t="n">
+      <c r="M16" s="17" t="n">
         <v>15</v>
       </c>
-      <c r="N16" s="17" t="n">
+      <c r="N16" s="7" t="n">
         <f aca="false">M16-L16</f>
         <v>1</v>
       </c>
-      <c r="O16" s="17" t="n">
+      <c r="O16" s="7" t="n">
         <f aca="false">IF(L16&lt;=7,1,IF(L16&lt;=12,2,IF(L16&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="D17" s="18" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A17,'State Market Summary'!$B$4:$B$54)</f>
         <v>550</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A17,'State Market Summary'!$C$4:$C$54)</f>
         <v>185</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G17" s="18" t="n">
-        <f aca="false">ROUND(D17/F17,0)</f>
+      <c r="G17" s="8" t="n">
+        <f aca="false">IF(F17=0,"unstaffed",ROUND(D17/F17,0))</f>
         <v>550</v>
       </c>
-      <c r="H17" s="20" t="n">
-        <f aca="false">ROUND(E17/F17,1)</f>
+      <c r="H17" s="18" t="n">
+        <f aca="false">IF(F17=0,"unstaffed",ROUND(E17/F17,1))</f>
         <v>185</v>
       </c>
-      <c r="I17" s="21" t="n">
+      <c r="I17" s="19" t="n">
         <v>915366</v>
       </c>
-      <c r="J17" s="22" t="n">
+      <c r="J17" s="20" t="n">
         <v>91862</v>
       </c>
-      <c r="K17" s="23" t="n">
+      <c r="K17" s="21" t="n">
         <f aca="false">ROUND((40*D17/MAX($D$2:$D$26)+25*E17/MAX($E$2:$E$26)+10*I17/MAX($I$2:$I$26)+10*J17/MAX($J$2:$J$26))/85*100,1)</f>
         <v>37.4</v>
       </c>
-      <c r="L17" s="17" t="n">
+      <c r="L17" s="7" t="n">
         <f aca="false">RANK(K17,$K$2:$K$26)</f>
         <v>16</v>
       </c>
-      <c r="M17" s="19" t="n">
+      <c r="M17" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="N17" s="17" t="n">
+      <c r="N17" s="7" t="n">
         <f aca="false">M17-L17</f>
         <v>0</v>
       </c>
-      <c r="O17" s="17" t="n">
+      <c r="O17" s="7" t="n">
         <f aca="false">IF(L17&lt;=7,1,IF(L17&lt;=12,2,IF(L17&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>178</v>
-      </c>
-      <c r="D18" s="18" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A18,'State Market Summary'!$B$4:$B$54)</f>
         <v>718</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A18,'State Market Summary'!$C$4:$C$54)</f>
         <v>241</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G18" s="18" t="n">
-        <f aca="false">ROUND(D18/F18,0)</f>
+      <c r="G18" s="8" t="n">
+        <f aca="false">IF(F18=0,"unstaffed",ROUND(D18/F18,0))</f>
         <v>718</v>
       </c>
-      <c r="H18" s="20" t="n">
-        <f aca="false">ROUND(E18/F18,1)</f>
+      <c r="H18" s="18" t="n">
+        <f aca="false">IF(F18=0,"unstaffed",ROUND(E18/F18,1))</f>
         <v>241</v>
       </c>
-      <c r="I18" s="21" t="n">
+      <c r="I18" s="19" t="n">
         <v>1191812</v>
       </c>
-      <c r="J18" s="22" t="n">
+      <c r="J18" s="20" t="n">
         <v>84033</v>
       </c>
-      <c r="K18" s="23" t="n">
+      <c r="K18" s="21" t="n">
         <f aca="false">ROUND((40*D18/MAX($D$2:$D$26)+25*E18/MAX($E$2:$E$26)+10*I18/MAX($I$2:$I$26)+10*J18/MAX($J$2:$J$26))/85*100,1)</f>
         <v>44.4</v>
       </c>
-      <c r="L18" s="17" t="n">
+      <c r="L18" s="7" t="n">
         <f aca="false">RANK(K18,$K$2:$K$26)</f>
         <v>8</v>
       </c>
-      <c r="M18" s="19" t="n">
+      <c r="M18" s="17" t="n">
         <v>17</v>
       </c>
-      <c r="N18" s="17" t="n">
+      <c r="N18" s="7" t="n">
         <f aca="false">M18-L18</f>
         <v>9</v>
       </c>
-      <c r="O18" s="17" t="n">
+      <c r="O18" s="7" t="n">
         <f aca="false">IF(L18&lt;=7,1,IF(L18&lt;=12,2,IF(L18&lt;=19,3,4)))</f>
         <v>2</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="D19" s="18" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A19,'State Market Summary'!$B$4:$B$54)</f>
         <v>462</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A19,'State Market Summary'!$C$4:$C$54)</f>
         <v>174</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G19" s="18" t="n">
-        <f aca="false">ROUND(D19/F19,0)</f>
+      <c r="G19" s="8" t="n">
+        <f aca="false">IF(F19=0,"unstaffed",ROUND(D19/F19,0))</f>
         <v>462</v>
       </c>
-      <c r="H19" s="20" t="n">
-        <f aca="false">ROUND(E19/F19,1)</f>
+      <c r="H19" s="18" t="n">
+        <f aca="false">IF(F19=0,"unstaffed",ROUND(E19/F19,1))</f>
         <v>174</v>
       </c>
-      <c r="I19" s="21" t="n">
+      <c r="I19" s="19" t="n">
         <v>772926</v>
       </c>
-      <c r="J19" s="22" t="n">
+      <c r="J19" s="20" t="n">
         <v>60048</v>
       </c>
-      <c r="K19" s="23" t="n">
+      <c r="K19" s="21" t="n">
         <f aca="false">ROUND((40*D19/MAX($D$2:$D$26)+25*E19/MAX($E$2:$E$26)+10*I19/MAX($I$2:$I$26)+10*J19/MAX($J$2:$J$26))/85*100,1)</f>
         <v>30.1</v>
       </c>
-      <c r="L19" s="17" t="n">
+      <c r="L19" s="7" t="n">
         <f aca="false">RANK(K19,$K$2:$K$26)</f>
         <v>21</v>
       </c>
-      <c r="M19" s="19" t="n">
+      <c r="M19" s="17" t="n">
         <v>18</v>
       </c>
-      <c r="N19" s="17" t="n">
+      <c r="N19" s="7" t="n">
         <f aca="false">M19-L19</f>
         <v>-3</v>
       </c>
-      <c r="O19" s="17" t="n">
+      <c r="O19" s="7" t="n">
         <f aca="false">IF(L19&lt;=7,1,IF(L19&lt;=12,2,IF(L19&lt;=19,3,4)))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>182</v>
-      </c>
-      <c r="D20" s="18" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A20,'State Market Summary'!$B$4:$B$54)</f>
         <v>477</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A20,'State Market Summary'!$C$4:$C$54)</f>
         <v>176</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G20" s="18" t="n">
-        <f aca="false">ROUND(D20/F20,0)</f>
+      <c r="G20" s="8" t="n">
+        <f aca="false">IF(F20=0,"unstaffed",ROUND(D20/F20,0))</f>
         <v>477</v>
       </c>
-      <c r="H20" s="20" t="n">
-        <f aca="false">ROUND(E20/F20,1)</f>
+      <c r="H20" s="18" t="n">
+        <f aca="false">IF(F20=0,"unstaffed",ROUND(E20/F20,1))</f>
         <v>176</v>
       </c>
-      <c r="I20" s="21" t="n">
+      <c r="I20" s="19" t="n">
         <v>739152</v>
       </c>
-      <c r="J20" s="22" t="n">
+      <c r="J20" s="20" t="n">
         <v>59699</v>
       </c>
-      <c r="K20" s="23" t="n">
+      <c r="K20" s="21" t="n">
         <f aca="false">ROUND((40*D20/MAX($D$2:$D$26)+25*E20/MAX($E$2:$E$26)+10*I20/MAX($I$2:$I$26)+10*J20/MAX($J$2:$J$26))/85*100,1)</f>
         <v>30.5</v>
       </c>
-      <c r="L20" s="17" t="n">
+      <c r="L20" s="7" t="n">
         <f aca="false">RANK(K20,$K$2:$K$26)</f>
         <v>20</v>
       </c>
-      <c r="M20" s="19" t="n">
+      <c r="M20" s="17" t="n">
         <v>19</v>
       </c>
-      <c r="N20" s="17" t="n">
+      <c r="N20" s="7" t="n">
         <f aca="false">M20-L20</f>
         <v>-1</v>
       </c>
-      <c r="O20" s="17" t="n">
+      <c r="O20" s="7" t="n">
         <f aca="false">IF(L20&lt;=7,1,IF(L20&lt;=12,2,IF(L20&lt;=19,3,4)))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>183</v>
-      </c>
-      <c r="D21" s="18" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A21,'State Market Summary'!$B$4:$B$54)</f>
         <v>442</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A21,'State Market Summary'!$C$4:$C$54)</f>
         <v>111</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G21" s="18" t="n">
-        <f aca="false">ROUND(D21/F21,0)</f>
+      <c r="G21" s="8" t="n">
+        <f aca="false">IF(F21=0,"unstaffed",ROUND(D21/F21,0))</f>
         <v>442</v>
       </c>
-      <c r="H21" s="20" t="n">
-        <f aca="false">ROUND(E21/F21,1)</f>
+      <c r="H21" s="18" t="n">
+        <f aca="false">IF(F21=0,"unstaffed",ROUND(E21/F21,1))</f>
         <v>111</v>
       </c>
-      <c r="I21" s="21" t="n">
+      <c r="I21" s="19" t="n">
         <v>663850</v>
       </c>
-      <c r="J21" s="22" t="n">
+      <c r="J21" s="20" t="n">
         <v>70489</v>
       </c>
-      <c r="K21" s="23" t="n">
+      <c r="K21" s="21" t="n">
         <f aca="false">ROUND((40*D21/MAX($D$2:$D$26)+25*E21/MAX($E$2:$E$26)+10*I21/MAX($I$2:$I$26)+10*J21/MAX($J$2:$J$26))/85*100,1)</f>
         <v>27.8</v>
       </c>
-      <c r="L21" s="17" t="n">
+      <c r="L21" s="7" t="n">
         <f aca="false">RANK(K21,$K$2:$K$26)</f>
         <v>22</v>
       </c>
-      <c r="M21" s="19" t="n">
+      <c r="M21" s="17" t="n">
         <v>20</v>
       </c>
-      <c r="N21" s="17" t="n">
+      <c r="N21" s="7" t="n">
         <f aca="false">M21-L21</f>
         <v>-2</v>
       </c>
-      <c r="O21" s="17" t="n">
+      <c r="O21" s="7" t="n">
         <f aca="false">IF(L21&lt;=7,1,IF(L21&lt;=12,2,IF(L21&lt;=19,3,4)))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="D22" s="18" t="n">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A22,'State Market Summary'!$B$4:$B$54)</f>
         <v>478</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A22,'State Market Summary'!$C$4:$C$54)</f>
         <v>137</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="18" t="n">
-        <f aca="false">ROUND(D22/F22,0)</f>
+      <c r="G22" s="8" t="n">
+        <f aca="false">IF(F22=0,"unstaffed",ROUND(D22/F22,0))</f>
         <v>478</v>
       </c>
-      <c r="H22" s="20" t="n">
-        <f aca="false">ROUND(E22/F22,1)</f>
+      <c r="H22" s="18" t="n">
+        <f aca="false">IF(F22=0,"unstaffed",ROUND(E22/F22,1))</f>
         <v>137</v>
       </c>
-      <c r="I22" s="21" t="n">
+      <c r="I22" s="19" t="n">
         <v>794462</v>
       </c>
-      <c r="J22" s="22" t="n">
+      <c r="J22" s="20" t="n">
         <v>97828</v>
       </c>
-      <c r="K22" s="23" t="n">
+      <c r="K22" s="21" t="n">
         <f aca="false">ROUND((40*D22/MAX($D$2:$D$26)+25*E22/MAX($E$2:$E$26)+10*I22/MAX($I$2:$I$26)+10*J22/MAX($J$2:$J$26))/85*100,1)</f>
         <v>33.6</v>
       </c>
-      <c r="L22" s="17" t="n">
+      <c r="L22" s="7" t="n">
         <f aca="false">RANK(K22,$K$2:$K$26)</f>
         <v>19</v>
       </c>
-      <c r="M22" s="19" t="n">
+      <c r="M22" s="17" t="n">
         <v>21</v>
       </c>
-      <c r="N22" s="17" t="n">
+      <c r="N22" s="7" t="n">
         <f aca="false">M22-L22</f>
         <v>2</v>
       </c>
-      <c r="O22" s="17" t="n">
+      <c r="O22" s="7" t="n">
         <f aca="false">IF(L22&lt;=7,1,IF(L22&lt;=12,2,IF(L22&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="D23" s="18" t="n">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D23" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A23,'State Market Summary'!$B$4:$B$54)</f>
         <v>489</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A23,'State Market Summary'!$C$4:$C$54)</f>
         <v>168</v>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="18" t="n">
-        <f aca="false">ROUND(D23/F23,0)</f>
+      <c r="G23" s="8" t="n">
+        <f aca="false">IF(F23=0,"unstaffed",ROUND(D23/F23,0))</f>
         <v>489</v>
       </c>
-      <c r="H23" s="20" t="n">
-        <f aca="false">ROUND(E23/F23,1)</f>
+      <c r="H23" s="18" t="n">
+        <f aca="false">IF(F23=0,"unstaffed",ROUND(E23/F23,1))</f>
         <v>168</v>
       </c>
-      <c r="I23" s="21" t="n">
+      <c r="I23" s="19" t="n">
         <v>860620</v>
       </c>
-      <c r="J23" s="22" t="n">
+      <c r="J23" s="20" t="n">
         <v>94114</v>
       </c>
-      <c r="K23" s="23" t="n">
+      <c r="K23" s="21" t="n">
         <f aca="false">ROUND((40*D23/MAX($D$2:$D$26)+25*E23/MAX($E$2:$E$26)+10*I23/MAX($I$2:$I$26)+10*J23/MAX($J$2:$J$26))/85*100,1)</f>
         <v>35</v>
       </c>
-      <c r="L23" s="17" t="n">
+      <c r="L23" s="7" t="n">
         <f aca="false">RANK(K23,$K$2:$K$26)</f>
         <v>18</v>
       </c>
-      <c r="M23" s="19" t="n">
+      <c r="M23" s="17" t="n">
         <v>22</v>
       </c>
-      <c r="N23" s="17" t="n">
+      <c r="N23" s="7" t="n">
         <f aca="false">M23-L23</f>
         <v>4</v>
       </c>
-      <c r="O23" s="17" t="n">
+      <c r="O23" s="7" t="n">
         <f aca="false">IF(L23&lt;=7,1,IF(L23&lt;=12,2,IF(L23&lt;=19,3,4)))</f>
         <v>3</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17" t="s">
-        <v>130</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="D24" s="18" t="n">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="D24" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A24,'State Market Summary'!$B$4:$B$54)</f>
         <v>401</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A24,'State Market Summary'!$C$4:$C$54)</f>
         <v>124</v>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="18" t="n">
-        <f aca="false">ROUND(D24/F24,0)</f>
+      <c r="G24" s="8" t="n">
+        <f aca="false">IF(F24=0,"unstaffed",ROUND(D24/F24,0))</f>
         <v>401</v>
       </c>
-      <c r="H24" s="20" t="n">
-        <f aca="false">ROUND(E24/F24,1)</f>
+      <c r="H24" s="18" t="n">
+        <f aca="false">IF(F24=0,"unstaffed",ROUND(E24/F24,1))</f>
         <v>124</v>
       </c>
-      <c r="I24" s="21" t="n">
+      <c r="I24" s="19" t="n">
         <v>634143</v>
       </c>
-      <c r="J24" s="22" t="n">
+      <c r="J24" s="20" t="n">
         <v>67976</v>
       </c>
-      <c r="K24" s="23" t="n">
+      <c r="K24" s="21" t="n">
         <f aca="false">ROUND((40*D24/MAX($D$2:$D$26)+25*E24/MAX($E$2:$E$26)+10*I24/MAX($I$2:$I$26)+10*J24/MAX($J$2:$J$26))/85*100,1)</f>
         <v>26.8</v>
       </c>
-      <c r="L24" s="17" t="n">
+      <c r="L24" s="7" t="n">
         <f aca="false">RANK(K24,$K$2:$K$26)</f>
         <v>23</v>
       </c>
-      <c r="M24" s="19" t="n">
+      <c r="M24" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="N24" s="17" t="n">
+      <c r="N24" s="7" t="n">
         <f aca="false">M24-L24</f>
         <v>0</v>
       </c>
-      <c r="O24" s="17" t="n">
+      <c r="O24" s="7" t="n">
         <f aca="false">IF(L24&lt;=7,1,IF(L24&lt;=12,2,IF(L24&lt;=19,3,4)))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>188</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="D25" s="18" t="n">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>181</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="D25" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A25,'State Market Summary'!$B$4:$B$54)</f>
         <v>345</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A25,'State Market Summary'!$C$4:$C$54)</f>
         <v>111</v>
       </c>
-      <c r="F25" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" s="18" t="n">
-        <f aca="false">ROUND(D25/F25,0)</f>
-        <v>345</v>
-      </c>
-      <c r="H25" s="20" t="n">
-        <f aca="false">ROUND(E25/F25,1)</f>
-        <v>111</v>
-      </c>
-      <c r="I25" s="21" t="n">
+      <c r="F25" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="8" t="str">
+        <f aca="false">IF(F25=0,"unstaffed",ROUND(D25/F25,0))</f>
+        <v>unstaffed</v>
+      </c>
+      <c r="H25" s="18" t="str">
+        <f aca="false">IF(F25=0,"unstaffed",ROUND(E25/F25,1))</f>
+        <v>unstaffed</v>
+      </c>
+      <c r="I25" s="19" t="n">
         <v>528815</v>
       </c>
-      <c r="J25" s="22" t="n">
+      <c r="J25" s="20" t="n">
         <v>73245</v>
       </c>
-      <c r="K25" s="23" t="n">
+      <c r="K25" s="21" t="n">
         <f aca="false">ROUND((40*D25/MAX($D$2:$D$26)+25*E25/MAX($E$2:$E$26)+10*I25/MAX($I$2:$I$26)+10*J25/MAX($J$2:$J$26))/85*100,1)</f>
         <v>25</v>
       </c>
-      <c r="L25" s="17" t="n">
+      <c r="L25" s="7" t="n">
         <f aca="false">RANK(K25,$K$2:$K$26)</f>
         <v>24</v>
       </c>
-      <c r="M25" s="19" t="n">
+      <c r="M25" s="17" t="n">
         <v>24</v>
       </c>
-      <c r="N25" s="17" t="n">
+      <c r="N25" s="7" t="n">
         <f aca="false">M25-L25</f>
         <v>0</v>
       </c>
-      <c r="O25" s="17" t="n">
+      <c r="O25" s="7" t="n">
         <f aca="false">IF(L25&lt;=7,1,IF(L25&lt;=12,2,IF(L25&lt;=19,3,4)))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>190</v>
-      </c>
-      <c r="D26" s="18" t="n">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="D26" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A26,'State Market Summary'!$B$4:$B$54)</f>
         <v>364</v>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,$A26,'State Market Summary'!$C$4:$C$54)</f>
         <v>97</v>
       </c>
-      <c r="F26" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" s="18" t="n">
-        <f aca="false">ROUND(D26/F26,0)</f>
-        <v>364</v>
-      </c>
-      <c r="H26" s="20" t="n">
-        <f aca="false">ROUND(E26/F26,1)</f>
-        <v>97</v>
-      </c>
-      <c r="I26" s="21" t="n">
+      <c r="F26" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="8" t="str">
+        <f aca="false">IF(F26=0,"unstaffed",ROUND(D26/F26,0))</f>
+        <v>unstaffed</v>
+      </c>
+      <c r="H26" s="18" t="str">
+        <f aca="false">IF(F26=0,"unstaffed",ROUND(E26/F26,1))</f>
+        <v>unstaffed</v>
+      </c>
+      <c r="I26" s="19" t="n">
         <v>473826</v>
       </c>
-      <c r="J26" s="22" t="n">
+      <c r="J26" s="20" t="n">
         <v>65973</v>
       </c>
-      <c r="K26" s="23" t="n">
+      <c r="K26" s="21" t="n">
         <f aca="false">ROUND((40*D26/MAX($D$2:$D$26)+25*E26/MAX($E$2:$E$26)+10*I26/MAX($I$2:$I$26)+10*J26/MAX($J$2:$J$26))/85*100,1)</f>
         <v>23.8</v>
       </c>
-      <c r="L26" s="17" t="n">
+      <c r="L26" s="7" t="n">
         <f aca="false">RANK(K26,$K$2:$K$26)</f>
         <v>25</v>
       </c>
-      <c r="M26" s="19" t="n">
+      <c r="M26" s="17" t="n">
         <v>25</v>
       </c>
-      <c r="N26" s="17" t="n">
+      <c r="N26" s="7" t="n">
         <f aca="false">M26-L26</f>
         <v>0</v>
       </c>
-      <c r="O26" s="17" t="n">
+      <c r="O26" s="7" t="n">
         <f aca="false">IF(L26&lt;=7,1,IF(L26&lt;=12,2,IF(L26&lt;=19,3,4)))</f>
         <v>4</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="B27" s="24"/>
-      <c r="C27" s="24"/>
-      <c r="D27" s="25" t="n">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="15" t="n">
         <f aca="false">SUM(D2:D26)</f>
         <v>18405</v>
       </c>
-      <c r="E27" s="25" t="n">
+      <c r="E27" s="15" t="n">
         <f aca="false">SUM(E2:E26)</f>
         <v>5862</v>
       </c>
-      <c r="F27" s="25" t="n">
+      <c r="F27" s="15" t="n">
         <f aca="false">SUM(F2:F26)</f>
         <v>28</v>
       </c>
-      <c r="G27" s="25" t="n">
+      <c r="G27" s="15" t="n">
         <f aca="false">ROUND(D27/F27,0)</f>
         <v>657</v>
       </c>
-      <c r="H27" s="26" t="n">
+      <c r="H27" s="23" t="n">
         <f aca="false">ROUND(E27/F27,1)</f>
         <v>209.4</v>
       </c>
-      <c r="I27" s="25" t="n">
+      <c r="I27" s="15" t="n">
         <f aca="false">SUM(I2:I26)</f>
         <v>30870179</v>
       </c>
-      <c r="J27" s="24"/>
-      <c r="K27" s="24"/>
-      <c r="L27" s="24"/>
-      <c r="M27" s="24"/>
-      <c r="N27" s="24"/>
-      <c r="O27" s="24"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
     </row>
     <row r="29" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -6628,46 +6552,46 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="B2" s="27" t="s">
-        <v>198</v>
+        <v>190</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>191</v>
       </c>
       <c r="C2" s="8" t="n">
         <f aca="false">SUMIF('Territory Plan'!$O$2:$O$26,1,'Territory Plan'!$F$2:$F$26)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D2" s="8" t="n">
         <f aca="false">SUM($C$2:$C2)</f>
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
-        <v>200</v>
-      </c>
-      <c r="B3" s="27" t="s">
-        <v>201</v>
+        <v>193</v>
+      </c>
+      <c r="B3" s="24" t="s">
+        <v>194</v>
       </c>
       <c r="C3" s="8" t="n">
         <f aca="false">SUMIF('Territory Plan'!$O$2:$O$26,2,'Territory Plan'!$F$2:$F$26)</f>
@@ -6675,18 +6599,18 @@
       </c>
       <c r="D3" s="8" t="n">
         <f aca="false">SUM($C$2:$C3)</f>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>204</v>
+        <v>196</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>197</v>
       </c>
       <c r="C4" s="8" t="n">
         <f aca="false">SUMIF('Territory Plan'!$O$2:$O$26,3,'Territory Plan'!$F$2:$F$26)</f>
@@ -6694,43 +6618,43 @@
       </c>
       <c r="D4" s="8" t="n">
         <f aca="false">SUM($C$2:$C4)</f>
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B5" s="27" t="s">
-        <v>207</v>
+        <v>199</v>
+      </c>
+      <c r="B5" s="24" t="s">
+        <v>200</v>
       </c>
       <c r="C5" s="8" t="n">
         <f aca="false">SUMIF('Territory Plan'!$O$2:$O$26,4,'Territory Plan'!$F$2:$F$26)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D5" s="8" t="n">
         <f aca="false">SUM($C$2:$C5)</f>
         <v>28</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
-        <v>209</v>
-      </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
+      <c r="A7" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="25"/>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
@@ -6774,7 +6698,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E1" s="10" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F1" s="10"/>
       <c r="G1" s="10"/>
@@ -6791,72 +6715,72 @@
       <c r="R1" s="10"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="J2" s="29" t="s">
-        <v>212</v>
-      </c>
-      <c r="K2" s="30" t="s">
-        <v>213</v>
-      </c>
-      <c r="L2" s="30" t="s">
-        <v>214</v>
-      </c>
-      <c r="N2" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="O2" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="P2" s="30" t="s">
-        <v>216</v>
+      <c r="J2" s="26" t="s">
+        <v>205</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>206</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="O2" s="27" t="s">
+        <v>208</v>
+      </c>
+      <c r="P2" s="27" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E3" s="16" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="H3" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>211</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>213</v>
+      </c>
+      <c r="L3" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="M3" s="16" t="s">
+        <v>215</v>
+      </c>
+      <c r="N3" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="O3" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="I3" s="16" t="s">
+      <c r="P3" s="16" t="s">
         <v>218</v>
       </c>
-      <c r="J3" s="16" t="s">
+      <c r="Q3" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="K3" s="16" t="s">
+      <c r="R3" s="16" t="s">
         <v>220</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>221</v>
-      </c>
-      <c r="M3" s="16" t="s">
-        <v>222</v>
-      </c>
-      <c r="N3" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="O3" s="16" t="s">
-        <v>224</v>
-      </c>
-      <c r="P3" s="16" t="s">
-        <v>225</v>
-      </c>
-      <c r="Q3" s="16" t="s">
-        <v>226</v>
-      </c>
-      <c r="R3" s="16" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E4" s="7" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="F4" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T01",'State Market Summary'!$B$4:$B$54)</f>
@@ -6874,42 +6798,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T01",'State Market Summary'!$O$4:$O$54)</f>
         <v>127</v>
       </c>
-      <c r="J4" s="31" t="n">
-        <v>3</v>
+      <c r="J4" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="K4" s="8" t="n">
-        <f aca="false">ROUND(F4/J4,0)</f>
-        <v>553</v>
-      </c>
-      <c r="L4" s="32" t="n">
-        <f aca="false">ROUND(G4/J4,1)</f>
-        <v>180</v>
-      </c>
-      <c r="M4" s="33" t="n">
+        <f aca="false">IF(J4=0,"unstaffed",ROUND(F4/J4,0))</f>
+        <v>830</v>
+      </c>
+      <c r="L4" s="18" t="n">
+        <f aca="false">IF(J4=0,"unstaffed",ROUND(G4/J4,1))</f>
+        <v>270</v>
+      </c>
+      <c r="M4" s="28" t="n">
         <f aca="false">H4/F4</f>
         <v>0.352409638554217</v>
       </c>
-      <c r="N4" s="34" t="n">
+      <c r="N4" s="19" t="n">
         <v>3090173</v>
       </c>
-      <c r="O4" s="35" t="n">
+      <c r="O4" s="20" t="n">
         <v>78473</v>
       </c>
-      <c r="P4" s="36" t="n">
+      <c r="P4" s="29" t="n">
         <v>31.7</v>
       </c>
-      <c r="Q4" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K4-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L4-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N4-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O4-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>34.4</v>
+      <c r="Q4" s="21" t="n">
+        <f aca="false">IF(J4=0,"unstaffed",ROUND((20*100*(K4-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L4-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N4-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O4-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>70.3</v>
       </c>
       <c r="R4" s="7" t="n">
-        <f aca="false">RANK(Q4,$Q$4:$Q$28)</f>
-        <v>11</v>
+        <f aca="false">IF(J4=0,"n/a",RANK(Q4,$Q$4:$Q$28))</f>
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E5" s="7" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="F5" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T02",'State Market Summary'!$B$4:$B$54)</f>
@@ -6927,42 +6851,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T02",'State Market Summary'!$O$4:$O$54)</f>
         <v>267</v>
       </c>
-      <c r="J5" s="31" t="n">
+      <c r="J5" s="17" t="n">
         <v>2</v>
       </c>
       <c r="K5" s="8" t="n">
-        <f aca="false">ROUND(F5/J5,0)</f>
+        <f aca="false">IF(J5=0,"unstaffed",ROUND(F5/J5,0))</f>
         <v>790</v>
       </c>
-      <c r="L5" s="32" t="n">
-        <f aca="false">ROUND(G5/J5,1)</f>
+      <c r="L5" s="18" t="n">
+        <f aca="false">IF(J5=0,"unstaffed",ROUND(G5/J5,1))</f>
         <v>344</v>
       </c>
-      <c r="M5" s="33" t="n">
+      <c r="M5" s="28" t="n">
         <f aca="false">H5/F5</f>
         <v>0.542748575047498</v>
       </c>
-      <c r="N5" s="34" t="n">
+      <c r="N5" s="19" t="n">
         <v>3819366</v>
       </c>
-      <c r="O5" s="35" t="n">
+      <c r="O5" s="20" t="n">
         <v>97969</v>
       </c>
-      <c r="P5" s="36" t="n">
+      <c r="P5" s="29" t="n">
         <v>34.9</v>
       </c>
-      <c r="Q5" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K5-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L5-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N5-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O5-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>80</v>
+      <c r="Q5" s="21" t="n">
+        <f aca="false">IF(J5=0,"unstaffed",ROUND((20*100*(K5-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L5-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N5-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O5-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>95</v>
       </c>
       <c r="R5" s="7" t="n">
-        <f aca="false">RANK(Q5,$Q$4:$Q$28)</f>
-        <v>2</v>
+        <f aca="false">IF(J5=0,"n/a",RANK(Q5,$Q$4:$Q$28))</f>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E6" s="7" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="F6" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T03",'State Market Summary'!$B$4:$B$54)</f>
@@ -6980,42 +6904,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T03",'State Market Summary'!$O$4:$O$54)</f>
         <v>149</v>
       </c>
-      <c r="J6" s="31" t="n">
-        <v>1</v>
+      <c r="J6" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="K6" s="8" t="n">
-        <f aca="false">ROUND(F6/J6,0)</f>
-        <v>1030</v>
-      </c>
-      <c r="L6" s="32" t="n">
-        <f aca="false">ROUND(G6/J6,1)</f>
-        <v>404</v>
-      </c>
-      <c r="M6" s="33" t="n">
+        <f aca="false">IF(J6=0,"unstaffed",ROUND(F6/J6,0))</f>
+        <v>515</v>
+      </c>
+      <c r="L6" s="18" t="n">
+        <f aca="false">IF(J6=0,"unstaffed",ROUND(G6/J6,1))</f>
+        <v>202</v>
+      </c>
+      <c r="M6" s="28" t="n">
         <f aca="false">H6/F6</f>
         <v>0.401941747572816</v>
       </c>
-      <c r="N6" s="34" t="n">
+      <c r="N6" s="19" t="n">
         <v>1726412</v>
       </c>
-      <c r="O6" s="35" t="n">
+      <c r="O6" s="20" t="n">
         <v>89542</v>
       </c>
-      <c r="P6" s="36" t="n">
+      <c r="P6" s="29" t="n">
         <v>38.3</v>
       </c>
-      <c r="Q6" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K6-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L6-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N6-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O6-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>89.5</v>
+      <c r="Q6" s="21" t="n">
+        <f aca="false">IF(J6=0,"unstaffed",ROUND((20*100*(K6-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L6-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N6-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O6-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>39.4</v>
       </c>
       <c r="R6" s="7" t="n">
-        <f aca="false">RANK(Q6,$Q$4:$Q$28)</f>
-        <v>1</v>
+        <f aca="false">IF(J6=0,"n/a",RANK(Q6,$Q$4:$Q$28))</f>
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E7" s="7" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="F7" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T04",'State Market Summary'!$B$4:$B$54)</f>
@@ -7033,42 +6957,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T04",'State Market Summary'!$O$4:$O$54)</f>
         <v>74</v>
       </c>
-      <c r="J7" s="31" t="n">
+      <c r="J7" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K7" s="8" t="n">
-        <f aca="false">ROUND(F7/J7,0)</f>
+        <f aca="false">IF(J7=0,"unstaffed",ROUND(F7/J7,0))</f>
         <v>795</v>
       </c>
-      <c r="L7" s="32" t="n">
-        <f aca="false">ROUND(G7/J7,1)</f>
+      <c r="L7" s="18" t="n">
+        <f aca="false">IF(J7=0,"unstaffed",ROUND(G7/J7,1))</f>
         <v>178</v>
       </c>
-      <c r="M7" s="33" t="n">
+      <c r="M7" s="28" t="n">
         <f aca="false">H7/F7</f>
         <v>0.436477987421384</v>
       </c>
-      <c r="N7" s="34" t="n">
+      <c r="N7" s="19" t="n">
         <v>1089150</v>
       </c>
-      <c r="O7" s="35" t="n">
+      <c r="O7" s="20" t="n">
         <v>71229</v>
       </c>
-      <c r="P7" s="36" t="n">
+      <c r="P7" s="29" t="n">
         <v>30.4</v>
       </c>
-      <c r="Q7" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K7-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L7-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N7-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O7-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>32.5</v>
+      <c r="Q7" s="21" t="n">
+        <f aca="false">IF(J7=0,"unstaffed",ROUND((20*100*(K7-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L7-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N7-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O7-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>37.3</v>
       </c>
       <c r="R7" s="7" t="n">
-        <f aca="false">RANK(Q7,$Q$4:$Q$28)</f>
-        <v>13</v>
+        <f aca="false">IF(J7=0,"n/a",RANK(Q7,$Q$4:$Q$28))</f>
+        <v>11</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E8" s="7" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="F8" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T05",'State Market Summary'!$B$4:$B$54)</f>
@@ -7086,42 +7010,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T05",'State Market Summary'!$O$4:$O$54)</f>
         <v>120</v>
       </c>
-      <c r="J8" s="31" t="n">
-        <v>1</v>
+      <c r="J8" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="K8" s="8" t="n">
-        <f aca="false">ROUND(F8/J8,0)</f>
-        <v>1107</v>
-      </c>
-      <c r="L8" s="32" t="n">
-        <f aca="false">ROUND(G8/J8,1)</f>
-        <v>273</v>
-      </c>
-      <c r="M8" s="33" t="n">
+        <f aca="false">IF(J8=0,"unstaffed",ROUND(F8/J8,0))</f>
+        <v>554</v>
+      </c>
+      <c r="L8" s="18" t="n">
+        <f aca="false">IF(J8=0,"unstaffed",ROUND(G8/J8,1))</f>
+        <v>136.5</v>
+      </c>
+      <c r="M8" s="28" t="n">
         <f aca="false">H8/F8</f>
         <v>0.251129177958446</v>
       </c>
-      <c r="N8" s="34" t="n">
+      <c r="N8" s="19" t="n">
         <v>1780020</v>
       </c>
-      <c r="O8" s="35" t="n">
+      <c r="O8" s="20" t="n">
         <v>71602</v>
       </c>
-      <c r="P8" s="36" t="n">
+      <c r="P8" s="29" t="n">
         <v>32.2</v>
       </c>
-      <c r="Q8" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K8-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L8-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N8-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O8-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>61.4</v>
+      <c r="Q8" s="21" t="n">
+        <f aca="false">IF(J8=0,"unstaffed",ROUND((20*100*(K8-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L8-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N8-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O8-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>19.5</v>
       </c>
       <c r="R8" s="7" t="n">
-        <f aca="false">RANK(Q8,$Q$4:$Q$28)</f>
-        <v>5</v>
+        <f aca="false">IF(J8=0,"n/a",RANK(Q8,$Q$4:$Q$28))</f>
+        <v>21</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E9" s="7" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F9" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T06",'State Market Summary'!$B$4:$B$54)</f>
@@ -7139,42 +7063,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T06",'State Market Summary'!$O$4:$O$54)</f>
         <v>115</v>
       </c>
-      <c r="J9" s="31" t="n">
-        <v>1</v>
+      <c r="J9" s="17" t="n">
+        <v>2</v>
       </c>
       <c r="K9" s="8" t="n">
-        <f aca="false">ROUND(F9/J9,0)</f>
-        <v>1035</v>
-      </c>
-      <c r="L9" s="32" t="n">
-        <f aca="false">ROUND(G9/J9,1)</f>
-        <v>338</v>
-      </c>
-      <c r="M9" s="33" t="n">
+        <f aca="false">IF(J9=0,"unstaffed",ROUND(F9/J9,0))</f>
+        <v>518</v>
+      </c>
+      <c r="L9" s="18" t="n">
+        <f aca="false">IF(J9=0,"unstaffed",ROUND(G9/J9,1))</f>
+        <v>169</v>
+      </c>
+      <c r="M9" s="28" t="n">
         <f aca="false">H9/F9</f>
         <v>0.427053140096618</v>
       </c>
-      <c r="N9" s="34" t="n">
+      <c r="N9" s="19" t="n">
         <v>1985432</v>
       </c>
-      <c r="O9" s="35" t="n">
+      <c r="O9" s="20" t="n">
         <v>89604</v>
       </c>
-      <c r="P9" s="36" t="n">
+      <c r="P9" s="29" t="n">
         <v>37.1</v>
       </c>
-      <c r="Q9" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K9-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L9-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N9-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O9-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>77.5</v>
+      <c r="Q9" s="21" t="n">
+        <f aca="false">IF(J9=0,"unstaffed",ROUND((20*100*(K9-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L9-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N9-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O9-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>31.8</v>
       </c>
       <c r="R9" s="7" t="n">
-        <f aca="false">RANK(Q9,$Q$4:$Q$28)</f>
-        <v>3</v>
+        <f aca="false">IF(J9=0,"n/a",RANK(Q9,$Q$4:$Q$28))</f>
+        <v>16</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E10" s="7" t="s">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="F10" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T07",'State Market Summary'!$B$4:$B$54)</f>
@@ -7192,42 +7116,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T07",'State Market Summary'!$O$4:$O$54)</f>
         <v>96</v>
       </c>
-      <c r="J10" s="31" t="n">
+      <c r="J10" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K10" s="8" t="n">
-        <f aca="false">ROUND(F10/J10,0)</f>
+        <f aca="false">IF(J10=0,"unstaffed",ROUND(F10/J10,0))</f>
         <v>746</v>
       </c>
-      <c r="L10" s="32" t="n">
-        <f aca="false">ROUND(G10/J10,1)</f>
+      <c r="L10" s="18" t="n">
+        <f aca="false">IF(J10=0,"unstaffed",ROUND(G10/J10,1))</f>
         <v>207</v>
       </c>
-      <c r="M10" s="33" t="n">
+      <c r="M10" s="28" t="n">
         <f aca="false">H10/F10</f>
         <v>0.591152815013405</v>
       </c>
-      <c r="N10" s="34" t="n">
+      <c r="N10" s="19" t="n">
         <v>910821</v>
       </c>
-      <c r="O10" s="35" t="n">
+      <c r="O10" s="20" t="n">
         <v>72965</v>
       </c>
-      <c r="P10" s="36" t="n">
+      <c r="P10" s="29" t="n">
         <v>31.3</v>
       </c>
-      <c r="Q10" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K10-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L10-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N10-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O10-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>36.8</v>
+      <c r="Q10" s="21" t="n">
+        <f aca="false">IF(J10=0,"unstaffed",ROUND((20*100*(K10-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L10-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N10-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O10-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>42.8</v>
       </c>
       <c r="R10" s="7" t="n">
-        <f aca="false">RANK(Q10,$Q$4:$Q$28)</f>
-        <v>10</v>
+        <f aca="false">IF(J10=0,"n/a",RANK(Q10,$Q$4:$Q$28))</f>
+        <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E11" s="7" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="F11" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T08",'State Market Summary'!$B$4:$B$54)</f>
@@ -7245,42 +7169,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T08",'State Market Summary'!$O$4:$O$54)</f>
         <v>135</v>
       </c>
-      <c r="J11" s="31" t="n">
+      <c r="J11" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K11" s="8" t="n">
-        <f aca="false">ROUND(F11/J11,0)</f>
+        <f aca="false">IF(J11=0,"unstaffed",ROUND(F11/J11,0))</f>
         <v>918</v>
       </c>
-      <c r="L11" s="32" t="n">
-        <f aca="false">ROUND(G11/J11,1)</f>
+      <c r="L11" s="18" t="n">
+        <f aca="false">IF(J11=0,"unstaffed",ROUND(G11/J11,1))</f>
         <v>279</v>
       </c>
-      <c r="M11" s="33" t="n">
+      <c r="M11" s="28" t="n">
         <f aca="false">H11/F11</f>
         <v>0.468409586056645</v>
       </c>
-      <c r="N11" s="34" t="n">
+      <c r="N11" s="19" t="n">
         <v>1294309</v>
       </c>
-      <c r="O11" s="35" t="n">
+      <c r="O11" s="20" t="n">
         <v>97019</v>
       </c>
-      <c r="P11" s="36" t="n">
+      <c r="P11" s="29" t="n">
         <v>42.3</v>
       </c>
-      <c r="Q11" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K11-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L11-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N11-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O11-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>62.8</v>
+      <c r="Q11" s="21" t="n">
+        <f aca="false">IF(J11=0,"unstaffed",ROUND((20*100*(K11-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L11-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N11-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O11-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>75.5</v>
       </c>
       <c r="R11" s="7" t="n">
-        <f aca="false">RANK(Q11,$Q$4:$Q$28)</f>
-        <v>4</v>
+        <f aca="false">IF(J11=0,"n/a",RANK(Q11,$Q$4:$Q$28))</f>
+        <v>2</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E12" s="7" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="F12" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T09",'State Market Summary'!$B$4:$B$54)</f>
@@ -7298,42 +7222,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T09",'State Market Summary'!$O$4:$O$54)</f>
         <v>87</v>
       </c>
-      <c r="J12" s="31" t="n">
+      <c r="J12" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K12" s="8" t="n">
-        <f aca="false">ROUND(F12/J12,0)</f>
+        <f aca="false">IF(J12=0,"unstaffed",ROUND(F12/J12,0))</f>
         <v>758</v>
       </c>
-      <c r="L12" s="32" t="n">
-        <f aca="false">ROUND(G12/J12,1)</f>
+      <c r="L12" s="18" t="n">
+        <f aca="false">IF(J12=0,"unstaffed",ROUND(G12/J12,1))</f>
         <v>176</v>
       </c>
-      <c r="M12" s="33" t="n">
+      <c r="M12" s="28" t="n">
         <f aca="false">H12/F12</f>
         <v>0.492084432717678</v>
       </c>
-      <c r="N12" s="34" t="n">
+      <c r="N12" s="19" t="n">
         <v>1084210</v>
       </c>
-      <c r="O12" s="35" t="n">
+      <c r="O12" s="20" t="n">
         <v>81797</v>
       </c>
-      <c r="P12" s="36" t="n">
+      <c r="P12" s="29" t="n">
         <v>35.1</v>
       </c>
-      <c r="Q12" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K12-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L12-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N12-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O12-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>33.9</v>
+      <c r="Q12" s="21" t="n">
+        <f aca="false">IF(J12=0,"unstaffed",ROUND((20*100*(K12-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L12-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N12-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O12-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>38.1</v>
       </c>
       <c r="R12" s="7" t="n">
-        <f aca="false">RANK(Q12,$Q$4:$Q$28)</f>
-        <v>12</v>
+        <f aca="false">IF(J12=0,"n/a",RANK(Q12,$Q$4:$Q$28))</f>
+        <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E13" s="7" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="F13" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T10",'State Market Summary'!$B$4:$B$54)</f>
@@ -7351,42 +7275,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T10",'State Market Summary'!$O$4:$O$54)</f>
         <v>81</v>
       </c>
-      <c r="J13" s="31" t="n">
+      <c r="J13" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K13" s="8" t="n">
-        <f aca="false">ROUND(F13/J13,0)</f>
+        <f aca="false">IF(J13=0,"unstaffed",ROUND(F13/J13,0))</f>
         <v>664</v>
       </c>
-      <c r="L13" s="32" t="n">
-        <f aca="false">ROUND(G13/J13,1)</f>
+      <c r="L13" s="18" t="n">
+        <f aca="false">IF(J13=0,"unstaffed",ROUND(G13/J13,1))</f>
         <v>200</v>
       </c>
-      <c r="M13" s="33" t="n">
+      <c r="M13" s="28" t="n">
         <f aca="false">H13/F13</f>
         <v>0.412650602409639</v>
       </c>
-      <c r="N13" s="34" t="n">
+      <c r="N13" s="19" t="n">
         <v>995376</v>
       </c>
-      <c r="O13" s="35" t="n">
+      <c r="O13" s="20" t="n">
         <v>67472</v>
       </c>
-      <c r="P13" s="36" t="n">
+      <c r="P13" s="29" t="n">
         <v>29.2</v>
       </c>
-      <c r="Q13" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K13-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L13-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N13-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O13-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>32.1</v>
+      <c r="Q13" s="21" t="n">
+        <f aca="false">IF(J13=0,"unstaffed",ROUND((20*100*(K13-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L13-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N13-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O13-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>36.7</v>
       </c>
       <c r="R13" s="7" t="n">
-        <f aca="false">RANK(Q13,$Q$4:$Q$28)</f>
-        <v>15</v>
+        <f aca="false">IF(J13=0,"n/a",RANK(Q13,$Q$4:$Q$28))</f>
+        <v>13</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E14" s="7" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F14" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T11",'State Market Summary'!$B$4:$B$54)</f>
@@ -7404,42 +7328,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T11",'State Market Summary'!$O$4:$O$54)</f>
         <v>49</v>
       </c>
-      <c r="J14" s="31" t="n">
+      <c r="J14" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K14" s="8" t="n">
-        <f aca="false">ROUND(F14/J14,0)</f>
+        <f aca="false">IF(J14=0,"unstaffed",ROUND(F14/J14,0))</f>
         <v>683</v>
       </c>
-      <c r="L14" s="32" t="n">
-        <f aca="false">ROUND(G14/J14,1)</f>
+      <c r="L14" s="18" t="n">
+        <f aca="false">IF(J14=0,"unstaffed",ROUND(G14/J14,1))</f>
         <v>220</v>
       </c>
-      <c r="M14" s="33" t="n">
+      <c r="M14" s="28" t="n">
         <f aca="false">H14/F14</f>
         <v>0.178623718887262</v>
       </c>
-      <c r="N14" s="34" t="n">
+      <c r="N14" s="19" t="n">
         <v>1070611</v>
       </c>
-      <c r="O14" s="35" t="n">
+      <c r="O14" s="20" t="n">
         <v>75694</v>
       </c>
-      <c r="P14" s="36" t="n">
+      <c r="P14" s="29" t="n">
         <v>33.4</v>
       </c>
-      <c r="Q14" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K14-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L14-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N14-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O14-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>38.9</v>
+      <c r="Q14" s="21" t="n">
+        <f aca="false">IF(J14=0,"unstaffed",ROUND((20*100*(K14-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L14-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N14-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O14-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>44.9</v>
       </c>
       <c r="R14" s="7" t="n">
-        <f aca="false">RANK(Q14,$Q$4:$Q$28)</f>
-        <v>9</v>
+        <f aca="false">IF(J14=0,"n/a",RANK(Q14,$Q$4:$Q$28))</f>
+        <v>6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E15" s="7" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="F15" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T12",'State Market Summary'!$B$4:$B$54)</f>
@@ -7457,42 +7381,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T12",'State Market Summary'!$O$4:$O$54)</f>
         <v>112</v>
       </c>
-      <c r="J15" s="31" t="n">
+      <c r="J15" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K15" s="8" t="n">
-        <f aca="false">ROUND(F15/J15,0)</f>
+        <f aca="false">IF(J15=0,"unstaffed",ROUND(F15/J15,0))</f>
         <v>734</v>
       </c>
-      <c r="L15" s="32" t="n">
-        <f aca="false">ROUND(G15/J15,1)</f>
+      <c r="L15" s="18" t="n">
+        <f aca="false">IF(J15=0,"unstaffed",ROUND(G15/J15,1))</f>
         <v>225</v>
       </c>
-      <c r="M15" s="33" t="n">
+      <c r="M15" s="28" t="n">
         <f aca="false">H15/F15</f>
         <v>0.521798365122616</v>
       </c>
-      <c r="N15" s="34" t="n">
+      <c r="N15" s="19" t="n">
         <v>1119028</v>
       </c>
-      <c r="O15" s="35" t="n">
+      <c r="O15" s="20" t="n">
         <v>90198</v>
       </c>
-      <c r="P15" s="36" t="n">
+      <c r="P15" s="29" t="n">
         <v>36.3</v>
       </c>
-      <c r="Q15" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K15-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L15-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N15-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O15-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>45.1</v>
+      <c r="Q15" s="21" t="n">
+        <f aca="false">IF(J15=0,"unstaffed",ROUND((20*100*(K15-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L15-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N15-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O15-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>52.1</v>
       </c>
       <c r="R15" s="7" t="n">
-        <f aca="false">RANK(Q15,$Q$4:$Q$28)</f>
-        <v>7</v>
+        <f aca="false">IF(J15=0,"n/a",RANK(Q15,$Q$4:$Q$28))</f>
+        <v>5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E16" s="7" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F16" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T13",'State Market Summary'!$B$4:$B$54)</f>
@@ -7510,42 +7434,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T13",'State Market Summary'!$O$4:$O$54)</f>
         <v>72</v>
       </c>
-      <c r="J16" s="31" t="n">
+      <c r="J16" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K16" s="8" t="n">
-        <f aca="false">ROUND(F16/J16,0)</f>
+        <f aca="false">IF(J16=0,"unstaffed",ROUND(F16/J16,0))</f>
         <v>779</v>
       </c>
-      <c r="L16" s="32" t="n">
-        <f aca="false">ROUND(G16/J16,1)</f>
+      <c r="L16" s="18" t="n">
+        <f aca="false">IF(J16=0,"unstaffed",ROUND(G16/J16,1))</f>
         <v>181</v>
       </c>
-      <c r="M16" s="33" t="n">
+      <c r="M16" s="28" t="n">
         <f aca="false">H16/F16</f>
         <v>0.440308087291399</v>
       </c>
-      <c r="N16" s="34" t="n">
+      <c r="N16" s="19" t="n">
         <v>975468</v>
       </c>
-      <c r="O16" s="35" t="n">
+      <c r="O16" s="20" t="n">
         <v>70436</v>
       </c>
-      <c r="P16" s="36" t="n">
+      <c r="P16" s="29" t="n">
         <v>34</v>
       </c>
-      <c r="Q16" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K16-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L16-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N16-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O16-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>32.1</v>
+      <c r="Q16" s="21" t="n">
+        <f aca="false">IF(J16=0,"unstaffed",ROUND((20*100*(K16-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L16-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N16-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O16-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>37</v>
       </c>
       <c r="R16" s="7" t="n">
-        <f aca="false">RANK(Q16,$Q$4:$Q$28)</f>
-        <v>15</v>
+        <f aca="false">IF(J16=0,"n/a",RANK(Q16,$Q$4:$Q$28))</f>
+        <v>12</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E17" s="7" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F17" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T14",'State Market Summary'!$B$4:$B$54)</f>
@@ -7563,42 +7487,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T14",'State Market Summary'!$O$4:$O$54)</f>
         <v>79</v>
       </c>
-      <c r="J17" s="31" t="n">
+      <c r="J17" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K17" s="8" t="n">
-        <f aca="false">ROUND(F17/J17,0)</f>
+        <f aca="false">IF(J17=0,"unstaffed",ROUND(F17/J17,0))</f>
         <v>597</v>
       </c>
-      <c r="L17" s="32" t="n">
-        <f aca="false">ROUND(G17/J17,1)</f>
+      <c r="L17" s="18" t="n">
+        <f aca="false">IF(J17=0,"unstaffed",ROUND(G17/J17,1))</f>
         <v>198</v>
       </c>
-      <c r="M17" s="33" t="n">
+      <c r="M17" s="28" t="n">
         <f aca="false">H17/F17</f>
         <v>0.343383584589615</v>
       </c>
-      <c r="N17" s="34" t="n">
+      <c r="N17" s="19" t="n">
         <v>1097099</v>
       </c>
-      <c r="O17" s="35" t="n">
+      <c r="O17" s="20" t="n">
         <v>68598</v>
       </c>
-      <c r="P17" s="36" t="n">
+      <c r="P17" s="29" t="n">
         <v>30.5</v>
       </c>
-      <c r="Q17" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K17-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L17-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N17-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O17-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>30.5</v>
+      <c r="Q17" s="21" t="n">
+        <f aca="false">IF(J17=0,"unstaffed",ROUND((20*100*(K17-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L17-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N17-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O17-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>34.2</v>
       </c>
       <c r="R17" s="7" t="n">
-        <f aca="false">RANK(Q17,$Q$4:$Q$28)</f>
-        <v>17</v>
+        <f aca="false">IF(J17=0,"n/a",RANK(Q17,$Q$4:$Q$28))</f>
+        <v>15</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E18" s="7" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="F18" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T15",'State Market Summary'!$B$4:$B$54)</f>
@@ -7616,42 +7540,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T15",'State Market Summary'!$O$4:$O$54)</f>
         <v>83</v>
       </c>
-      <c r="J18" s="31" t="n">
+      <c r="J18" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K18" s="8" t="n">
-        <f aca="false">ROUND(F18/J18,0)</f>
+        <f aca="false">IF(J18=0,"unstaffed",ROUND(F18/J18,0))</f>
         <v>594</v>
       </c>
-      <c r="L18" s="32" t="n">
-        <f aca="false">ROUND(G18/J18,1)</f>
+      <c r="L18" s="18" t="n">
+        <f aca="false">IF(J18=0,"unstaffed",ROUND(G18/J18,1))</f>
         <v>231</v>
       </c>
-      <c r="M18" s="33" t="n">
+      <c r="M18" s="28" t="n">
         <f aca="false">H18/F18</f>
         <v>0.335016835016835</v>
       </c>
-      <c r="N18" s="34" t="n">
+      <c r="N18" s="19" t="n">
         <v>1257732</v>
       </c>
-      <c r="O18" s="35" t="n">
+      <c r="O18" s="20" t="n">
         <v>75026</v>
       </c>
-      <c r="P18" s="36" t="n">
+      <c r="P18" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="Q18" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K18-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L18-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N18-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O18-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>39.1</v>
+      <c r="Q18" s="21" t="n">
+        <f aca="false">IF(J18=0,"unstaffed",ROUND((20*100*(K18-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L18-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N18-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O18-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>44.7</v>
       </c>
       <c r="R18" s="7" t="n">
-        <f aca="false">RANK(Q18,$Q$4:$Q$28)</f>
-        <v>8</v>
+        <f aca="false">IF(J18=0,"n/a",RANK(Q18,$Q$4:$Q$28))</f>
+        <v>7</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E19" s="7" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F19" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T16",'State Market Summary'!$B$4:$B$54)</f>
@@ -7669,42 +7593,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T16",'State Market Summary'!$O$4:$O$54)</f>
         <v>79</v>
       </c>
-      <c r="J19" s="31" t="n">
+      <c r="J19" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K19" s="8" t="n">
-        <f aca="false">ROUND(F19/J19,0)</f>
+        <f aca="false">IF(J19=0,"unstaffed",ROUND(F19/J19,0))</f>
         <v>550</v>
       </c>
-      <c r="L19" s="32" t="n">
-        <f aca="false">ROUND(G19/J19,1)</f>
+      <c r="L19" s="18" t="n">
+        <f aca="false">IF(J19=0,"unstaffed",ROUND(G19/J19,1))</f>
         <v>185</v>
       </c>
-      <c r="M19" s="33" t="n">
+      <c r="M19" s="28" t="n">
         <f aca="false">H19/F19</f>
         <v>0.367272727272727</v>
       </c>
-      <c r="N19" s="34" t="n">
+      <c r="N19" s="19" t="n">
         <v>915366</v>
       </c>
-      <c r="O19" s="35" t="n">
+      <c r="O19" s="20" t="n">
         <v>91862</v>
       </c>
-      <c r="P19" s="36" t="n">
+      <c r="P19" s="29" t="n">
         <v>40.7</v>
       </c>
-      <c r="Q19" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K19-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L19-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N19-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O19-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>32.3</v>
+      <c r="Q19" s="21" t="n">
+        <f aca="false">IF(J19=0,"unstaffed",ROUND((20*100*(K19-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L19-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N19-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O19-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>34.5</v>
       </c>
       <c r="R19" s="7" t="n">
-        <f aca="false">RANK(Q19,$Q$4:$Q$28)</f>
+        <f aca="false">IF(J19=0,"n/a",RANK(Q19,$Q$4:$Q$28))</f>
         <v>14</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E20" s="7" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F20" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T17",'State Market Summary'!$B$4:$B$54)</f>
@@ -7722,42 +7646,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T17",'State Market Summary'!$O$4:$O$54)</f>
         <v>81</v>
       </c>
-      <c r="J20" s="31" t="n">
+      <c r="J20" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K20" s="8" t="n">
-        <f aca="false">ROUND(F20/J20,0)</f>
+        <f aca="false">IF(J20=0,"unstaffed",ROUND(F20/J20,0))</f>
         <v>718</v>
       </c>
-      <c r="L20" s="32" t="n">
-        <f aca="false">ROUND(G20/J20,1)</f>
+      <c r="L20" s="18" t="n">
+        <f aca="false">IF(J20=0,"unstaffed",ROUND(G20/J20,1))</f>
         <v>241</v>
       </c>
-      <c r="M20" s="33" t="n">
+      <c r="M20" s="28" t="n">
         <f aca="false">H20/F20</f>
         <v>0.484679665738162</v>
       </c>
-      <c r="N20" s="34" t="n">
+      <c r="N20" s="19" t="n">
         <v>1191812</v>
       </c>
-      <c r="O20" s="35" t="n">
+      <c r="O20" s="20" t="n">
         <v>84033</v>
       </c>
-      <c r="P20" s="36" t="n">
+      <c r="P20" s="29" t="n">
         <v>36.3</v>
       </c>
-      <c r="Q20" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K20-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L20-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N20-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O20-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>46.4</v>
+      <c r="Q20" s="21" t="n">
+        <f aca="false">IF(J20=0,"unstaffed",ROUND((20*100*(K20-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L20-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N20-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O20-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>54.2</v>
       </c>
       <c r="R20" s="7" t="n">
-        <f aca="false">RANK(Q20,$Q$4:$Q$28)</f>
-        <v>6</v>
+        <f aca="false">IF(J20=0,"n/a",RANK(Q20,$Q$4:$Q$28))</f>
+        <v>4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E21" s="7" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="F21" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T18",'State Market Summary'!$B$4:$B$54)</f>
@@ -7775,42 +7699,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T18",'State Market Summary'!$O$4:$O$54)</f>
         <v>37</v>
       </c>
-      <c r="J21" s="31" t="n">
+      <c r="J21" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K21" s="8" t="n">
-        <f aca="false">ROUND(F21/J21,0)</f>
+        <f aca="false">IF(J21=0,"unstaffed",ROUND(F21/J21,0))</f>
         <v>462</v>
       </c>
-      <c r="L21" s="32" t="n">
-        <f aca="false">ROUND(G21/J21,1)</f>
+      <c r="L21" s="18" t="n">
+        <f aca="false">IF(J21=0,"unstaffed",ROUND(G21/J21,1))</f>
         <v>174</v>
       </c>
-      <c r="M21" s="33" t="n">
+      <c r="M21" s="28" t="n">
         <f aca="false">H21/F21</f>
         <v>0.192640692640693</v>
       </c>
-      <c r="N21" s="34" t="n">
+      <c r="N21" s="19" t="n">
         <v>772926</v>
       </c>
-      <c r="O21" s="35" t="n">
+      <c r="O21" s="20" t="n">
         <v>60048</v>
       </c>
-      <c r="P21" s="36" t="n">
+      <c r="P21" s="29" t="n">
         <v>26.1</v>
       </c>
-      <c r="Q21" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K21-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L21-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N21-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O21-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>19.1</v>
+      <c r="Q21" s="21" t="n">
+        <f aca="false">IF(J21=0,"unstaffed",ROUND((20*100*(K21-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L21-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N21-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O21-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>19.6</v>
       </c>
       <c r="R21" s="7" t="n">
-        <f aca="false">RANK(Q21,$Q$4:$Q$28)</f>
-        <v>21</v>
+        <f aca="false">IF(J21=0,"n/a",RANK(Q21,$Q$4:$Q$28))</f>
+        <v>20</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E22" s="7" t="s">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="F22" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T19",'State Market Summary'!$B$4:$B$54)</f>
@@ -7828,42 +7752,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T19",'State Market Summary'!$O$4:$O$54)</f>
         <v>69</v>
       </c>
-      <c r="J22" s="31" t="n">
+      <c r="J22" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K22" s="8" t="n">
-        <f aca="false">ROUND(F22/J22,0)</f>
+        <f aca="false">IF(J22=0,"unstaffed",ROUND(F22/J22,0))</f>
         <v>477</v>
       </c>
-      <c r="L22" s="32" t="n">
-        <f aca="false">ROUND(G22/J22,1)</f>
+      <c r="L22" s="18" t="n">
+        <f aca="false">IF(J22=0,"unstaffed",ROUND(G22/J22,1))</f>
         <v>176</v>
       </c>
-      <c r="M22" s="33" t="n">
+      <c r="M22" s="28" t="n">
         <f aca="false">H22/F22</f>
         <v>0.421383647798742</v>
       </c>
-      <c r="N22" s="34" t="n">
+      <c r="N22" s="19" t="n">
         <v>739152</v>
       </c>
-      <c r="O22" s="35" t="n">
+      <c r="O22" s="20" t="n">
         <v>59699</v>
       </c>
-      <c r="P22" s="36" t="n">
+      <c r="P22" s="29" t="n">
         <v>25.6</v>
       </c>
-      <c r="Q22" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K22-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L22-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N22-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O22-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>19.7</v>
+      <c r="Q22" s="21" t="n">
+        <f aca="false">IF(J22=0,"unstaffed",ROUND((20*100*(K22-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L22-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N22-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O22-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>20.5</v>
       </c>
       <c r="R22" s="7" t="n">
-        <f aca="false">RANK(Q22,$Q$4:$Q$28)</f>
-        <v>20</v>
+        <f aca="false">IF(J22=0,"n/a",RANK(Q22,$Q$4:$Q$28))</f>
+        <v>19</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E23" s="7" t="s">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="F23" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T20",'State Market Summary'!$B$4:$B$54)</f>
@@ -7881,42 +7805,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T20",'State Market Summary'!$O$4:$O$54)</f>
         <v>48</v>
       </c>
-      <c r="J23" s="31" t="n">
+      <c r="J23" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K23" s="8" t="n">
-        <f aca="false">ROUND(F23/J23,0)</f>
+        <f aca="false">IF(J23=0,"unstaffed",ROUND(F23/J23,0))</f>
         <v>442</v>
       </c>
-      <c r="L23" s="32" t="n">
-        <f aca="false">ROUND(G23/J23,1)</f>
+      <c r="L23" s="18" t="n">
+        <f aca="false">IF(J23=0,"unstaffed",ROUND(G23/J23,1))</f>
         <v>111</v>
       </c>
-      <c r="M23" s="33" t="n">
+      <c r="M23" s="28" t="n">
         <f aca="false">H23/F23</f>
         <v>0.391402714932127</v>
       </c>
-      <c r="N23" s="34" t="n">
+      <c r="N23" s="19" t="n">
         <v>663850</v>
       </c>
-      <c r="O23" s="35" t="n">
+      <c r="O23" s="20" t="n">
         <v>70489</v>
       </c>
-      <c r="P23" s="36" t="n">
+      <c r="P23" s="29" t="n">
         <v>28.5</v>
       </c>
-      <c r="Q23" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K23-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L23-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N23-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O23-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>8.7</v>
+      <c r="Q23" s="21" t="n">
+        <f aca="false">IF(J23=0,"unstaffed",ROUND((20*100*(K23-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L23-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N23-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O23-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>5</v>
       </c>
       <c r="R23" s="7" t="n">
-        <f aca="false">RANK(Q23,$Q$4:$Q$28)</f>
+        <f aca="false">IF(J23=0,"n/a",RANK(Q23,$Q$4:$Q$28))</f>
         <v>23</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E24" s="7" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="F24" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T21",'State Market Summary'!$B$4:$B$54)</f>
@@ -7934,42 +7858,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T21",'State Market Summary'!$O$4:$O$54)</f>
         <v>49</v>
       </c>
-      <c r="J24" s="31" t="n">
+      <c r="J24" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K24" s="8" t="n">
-        <f aca="false">ROUND(F24/J24,0)</f>
+        <f aca="false">IF(J24=0,"unstaffed",ROUND(F24/J24,0))</f>
         <v>478</v>
       </c>
-      <c r="L24" s="32" t="n">
-        <f aca="false">ROUND(G24/J24,1)</f>
+      <c r="L24" s="18" t="n">
+        <f aca="false">IF(J24=0,"unstaffed",ROUND(G24/J24,1))</f>
         <v>137</v>
       </c>
-      <c r="M24" s="33" t="n">
+      <c r="M24" s="28" t="n">
         <f aca="false">H24/F24</f>
         <v>0.50418410041841</v>
       </c>
-      <c r="N24" s="34" t="n">
+      <c r="N24" s="19" t="n">
         <v>794462</v>
       </c>
-      <c r="O24" s="35" t="n">
+      <c r="O24" s="20" t="n">
         <v>97828</v>
       </c>
-      <c r="P24" s="36" t="n">
+      <c r="P24" s="29" t="n">
         <v>41.2</v>
       </c>
-      <c r="Q24" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K24-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L24-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N24-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O24-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>22.2</v>
+      <c r="Q24" s="21" t="n">
+        <f aca="false">IF(J24=0,"unstaffed",ROUND((20*100*(K24-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L24-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N24-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O24-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>20.6</v>
       </c>
       <c r="R24" s="7" t="n">
-        <f aca="false">RANK(Q24,$Q$4:$Q$28)</f>
-        <v>19</v>
+        <f aca="false">IF(J24=0,"n/a",RANK(Q24,$Q$4:$Q$28))</f>
+        <v>18</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E25" s="7" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="F25" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T22",'State Market Summary'!$B$4:$B$54)</f>
@@ -7987,42 +7911,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T22",'State Market Summary'!$O$4:$O$54)</f>
         <v>78</v>
       </c>
-      <c r="J25" s="31" t="n">
+      <c r="J25" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K25" s="8" t="n">
-        <f aca="false">ROUND(F25/J25,0)</f>
+        <f aca="false">IF(J25=0,"unstaffed",ROUND(F25/J25,0))</f>
         <v>489</v>
       </c>
-      <c r="L25" s="32" t="n">
-        <f aca="false">ROUND(G25/J25,1)</f>
+      <c r="L25" s="18" t="n">
+        <f aca="false">IF(J25=0,"unstaffed",ROUND(G25/J25,1))</f>
         <v>168</v>
       </c>
-      <c r="M25" s="33" t="n">
+      <c r="M25" s="28" t="n">
         <f aca="false">H25/F25</f>
         <v>0.406952965235174</v>
       </c>
-      <c r="N25" s="34" t="n">
+      <c r="N25" s="19" t="n">
         <v>860620</v>
       </c>
-      <c r="O25" s="35" t="n">
+      <c r="O25" s="20" t="n">
         <v>94114</v>
       </c>
-      <c r="P25" s="36" t="n">
+      <c r="P25" s="29" t="n">
         <v>39.1</v>
       </c>
-      <c r="Q25" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K25-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L25-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N25-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O25-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>27.8</v>
+      <c r="Q25" s="21" t="n">
+        <f aca="false">IF(J25=0,"unstaffed",ROUND((20*100*(K25-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L25-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N25-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O25-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>28.2</v>
       </c>
       <c r="R25" s="7" t="n">
-        <f aca="false">RANK(Q25,$Q$4:$Q$28)</f>
-        <v>18</v>
+        <f aca="false">IF(J25=0,"n/a",RANK(Q25,$Q$4:$Q$28))</f>
+        <v>17</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E26" s="7" t="s">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="F26" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T23",'State Market Summary'!$B$4:$B$54)</f>
@@ -8040,42 +7964,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T23",'State Market Summary'!$O$4:$O$54)</f>
         <v>44</v>
       </c>
-      <c r="J26" s="31" t="n">
+      <c r="J26" s="17" t="n">
         <v>1</v>
       </c>
       <c r="K26" s="8" t="n">
-        <f aca="false">ROUND(F26/J26,0)</f>
+        <f aca="false">IF(J26=0,"unstaffed",ROUND(F26/J26,0))</f>
         <v>401</v>
       </c>
-      <c r="L26" s="32" t="n">
-        <f aca="false">ROUND(G26/J26,1)</f>
+      <c r="L26" s="18" t="n">
+        <f aca="false">IF(J26=0,"unstaffed",ROUND(G26/J26,1))</f>
         <v>124</v>
       </c>
-      <c r="M26" s="33" t="n">
+      <c r="M26" s="28" t="n">
         <f aca="false">H26/F26</f>
         <v>0.396508728179551</v>
       </c>
-      <c r="N26" s="34" t="n">
+      <c r="N26" s="19" t="n">
         <v>634143</v>
       </c>
-      <c r="O26" s="35" t="n">
+      <c r="O26" s="20" t="n">
         <v>67976</v>
       </c>
-      <c r="P26" s="36" t="n">
+      <c r="P26" s="29" t="n">
         <v>29.8</v>
       </c>
-      <c r="Q26" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K26-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L26-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N26-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O26-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>9.4</v>
+      <c r="Q26" s="21" t="n">
+        <f aca="false">IF(J26=0,"unstaffed",ROUND((20*100*(K26-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L26-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N26-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O26-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>6</v>
       </c>
       <c r="R26" s="7" t="n">
-        <f aca="false">RANK(Q26,$Q$4:$Q$28)</f>
+        <f aca="false">IF(J26=0,"n/a",RANK(Q26,$Q$4:$Q$28))</f>
         <v>22</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E27" s="7" t="s">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="F27" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T24",'State Market Summary'!$B$4:$B$54)</f>
@@ -8093,42 +8017,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T24",'State Market Summary'!$O$4:$O$54)</f>
         <v>55</v>
       </c>
-      <c r="J27" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" s="8" t="n">
-        <f aca="false">ROUND(F27/J27,0)</f>
-        <v>345</v>
-      </c>
-      <c r="L27" s="32" t="n">
-        <f aca="false">ROUND(G27/J27,1)</f>
-        <v>111</v>
-      </c>
-      <c r="M27" s="33" t="n">
+      <c r="J27" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="8" t="str">
+        <f aca="false">IF(J27=0,"unstaffed",ROUND(F27/J27,0))</f>
+        <v>unstaffed</v>
+      </c>
+      <c r="L27" s="18" t="str">
+        <f aca="false">IF(J27=0,"unstaffed",ROUND(G27/J27,1))</f>
+        <v>unstaffed</v>
+      </c>
+      <c r="M27" s="28" t="n">
         <f aca="false">H27/F27</f>
         <v>0.48695652173913</v>
       </c>
-      <c r="N27" s="34" t="n">
+      <c r="N27" s="19" t="n">
         <v>528815</v>
       </c>
-      <c r="O27" s="35" t="n">
+      <c r="O27" s="20" t="n">
         <v>73245</v>
       </c>
-      <c r="P27" s="36" t="n">
+      <c r="P27" s="29" t="n">
         <v>30.7</v>
       </c>
-      <c r="Q27" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K27-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L27-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N27-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O27-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>6.4</v>
-      </c>
-      <c r="R27" s="7" t="n">
-        <f aca="false">RANK(Q27,$Q$4:$Q$28)</f>
-        <v>24</v>
+      <c r="Q27" s="21" t="str">
+        <f aca="false">IF(J27=0,"unstaffed",ROUND((20*100*(K27-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L27-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N27-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O27-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>unstaffed</v>
+      </c>
+      <c r="R27" s="7" t="str">
+        <f aca="false">IF(J27=0,"n/a",RANK(Q27,$Q$4:$Q$28))</f>
+        <v>n/a</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E28" s="7" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="F28" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T25",'State Market Summary'!$B$4:$B$54)</f>
@@ -8146,42 +8070,42 @@
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T25",'State Market Summary'!$O$4:$O$54)</f>
         <v>29</v>
       </c>
-      <c r="J28" s="31" t="n">
-        <v>1</v>
-      </c>
-      <c r="K28" s="8" t="n">
-        <f aca="false">ROUND(F28/J28,0)</f>
-        <v>364</v>
-      </c>
-      <c r="L28" s="32" t="n">
-        <f aca="false">ROUND(G28/J28,1)</f>
-        <v>97</v>
-      </c>
-      <c r="M28" s="33" t="n">
+      <c r="J28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="8" t="str">
+        <f aca="false">IF(J28=0,"unstaffed",ROUND(F28/J28,0))</f>
+        <v>unstaffed</v>
+      </c>
+      <c r="L28" s="18" t="str">
+        <f aca="false">IF(J28=0,"unstaffed",ROUND(G28/J28,1))</f>
+        <v>unstaffed</v>
+      </c>
+      <c r="M28" s="28" t="n">
         <f aca="false">H28/F28</f>
         <v>0.431318681318681</v>
       </c>
-      <c r="N28" s="34" t="n">
+      <c r="N28" s="19" t="n">
         <v>473826</v>
       </c>
-      <c r="O28" s="35" t="n">
+      <c r="O28" s="20" t="n">
         <v>65973</v>
       </c>
-      <c r="P28" s="36" t="n">
+      <c r="P28" s="29" t="n">
         <v>30.6</v>
       </c>
-      <c r="Q28" s="37" t="n">
-        <f aca="false">ROUND((20*100*(K28-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L28-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N28-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O28-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1)</f>
-        <v>2.1</v>
-      </c>
-      <c r="R28" s="7" t="n">
-        <f aca="false">RANK(Q28,$Q$4:$Q$28)</f>
-        <v>25</v>
+      <c r="Q28" s="21" t="str">
+        <f aca="false">IF(J28=0,"unstaffed",ROUND((20*100*(K28-MIN($K$4:$K$28))/(MAX($K$4:$K$28)-MIN($K$4:$K$28))+60*100*(L28-MIN($L$4:$L$28))/(MAX($L$4:$L$28)-MIN($L$4:$L$28))+10*100*(N28-MIN($N$4:$N$28))/(MAX($N$4:$N$28)-MIN($N$4:$N$28))+10*100*(O28-MIN($O$4:$O$28))/(MAX($O$4:$O$28)-MIN($O$4:$O$28)))/100,1))</f>
+        <v>unstaffed</v>
+      </c>
+      <c r="R28" s="7" t="str">
+        <f aca="false">IF(J28=0,"n/a",RANK(Q28,$Q$4:$Q$28))</f>
+        <v>n/a</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="E29" s="38" t="s">
-        <v>54</v>
+      <c r="E29" s="22" t="s">
+        <v>47</v>
       </c>
       <c r="F29" s="15" t="n">
         <f aca="false">SUM(F4:F28)</f>
@@ -8199,7 +8123,7 @@
         <f aca="false">SUM(I4:I28)</f>
         <v>2215</v>
       </c>
-      <c r="J29" s="38" t="n">
+      <c r="J29" s="22" t="n">
         <f aca="false">SUM(J4:J28)</f>
         <v>28</v>
       </c>
@@ -8207,23 +8131,23 @@
         <f aca="false">ROUND(F29/J29,0)</f>
         <v>657</v>
       </c>
-      <c r="L29" s="39" t="n">
+      <c r="L29" s="23" t="n">
         <f aca="false">ROUND(G29/J29,1)</f>
         <v>209.4</v>
       </c>
-      <c r="M29" s="40" t="n">
+      <c r="M29" s="30" t="n">
         <f aca="false">H29/F29</f>
         <v>0.414561260527031</v>
       </c>
-      <c r="N29" s="38"/>
-      <c r="O29" s="38"/>
-      <c r="P29" s="38"/>
-      <c r="Q29" s="38"/>
-      <c r="R29" s="38"/>
+      <c r="N29" s="22"/>
+      <c r="O29" s="22"/>
+      <c r="P29" s="22"/>
+      <c r="Q29" s="22"/>
+      <c r="R29" s="22"/>
     </row>
     <row r="31" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E31" s="9" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>

--- a/docs/deliverables/Femasys_Territory_Plan_v4.xlsx
+++ b/docs/deliverables/Femasys_Territory_Plan_v4.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="248">
   <si>
     <t xml:space="preserve">FemaSeed U.S. Territory Plan — v4 (ALL-MD Universe, 28-Rep Hard Cap)</t>
   </si>
@@ -81,10 +81,10 @@
     <t xml:space="preserve">No source provides volume for the full ALL-MD universe (row-level volume exists only for the &gt;=10 subset), so v3's 15% volume weight is redistributed proportionally rather than reusing partial-coverage volume.</t>
   </si>
   <si>
-    <t xml:space="preserve">Weights: All MDs 47.06% / All Clinics 29.41% / Women 25-44 11.76% / Income 11.76% (= 40/25/10/10 renormalized over 85). Each component scored as share of territory maximum, weighted, rescaled to 0-100 max. Education retained for reference at 0%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Result vs v3: 18 of 25 rankings changed. Top 8: CA-HI, TX, NY, PA-NJ, FL, New England, WA-OR-AK, IL.</t>
+    <t xml:space="preserve">Reference score (Territory Plan tab, rep-independent): All MDs 47.06% / All Clinics 29.41% / Women 25-44 11.76% / Income 11.76% (= 40/25/10/10 renormalized over 85), share-of-max method. Retained for reference; it does NOT drive prioritization.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRIORITIZATION uses the Kathy - ALL Universe score (per Rajiv, 2026-07-22): All MDs/Rep 20% / All Clinics/Rep 60% / Women 25-44 10% / Median Income 10% / Education 0%, min-max normalized 0-100 across staffed territories. Top 8: CA-HI, New England, TX, IL, WA-OR-AK, GA, AZ-NV-ID-MT, MI. Because components are per-rep, ranks depend on the rep allocation.</t>
   </si>
   <si>
     <t xml:space="preserve">KATHY - ALL UNIVERSE TAB</t>
@@ -96,7 +96,7 @@
     <t xml:space="preserve">HIRING WAVES</t>
   </si>
   <si>
-    <t xml:space="preserve">Territories ranked by v4 score, wave sizes 7/5/7/6. Cumulative reps 12 / 17 / 24 / 28. Wave 4 includes the two unstaffed territories at 0 reps.</t>
+    <t xml:space="preserve">Territories ranked by the Kathy - ALL Universe score, wave sizes 7/5/7/6. Cumulative reps 9 / 15 / 23 / 28. Wave 4 includes the two unstaffed territories at 0 reps. Wave membership recalculates from the Kathy tab if reps are edited (lists in column B are a snapshot).</t>
   </si>
   <si>
     <t xml:space="preserve">STRATEGIC CAVEAT — MANDATE STATES (carried from v3, still open): rankings are pure opportunity, not mandate-adjusted. Northeast (incl. mandate states) remains in early waves. Verify the current mandate list and re-sequence before committing hires — statuses have changed recently.</t>
@@ -462,7 +462,7 @@
     <t xml:space="preserve">Rank Change</t>
   </si>
   <si>
-    <t xml:space="preserve">Hire Wave (v4)</t>
+    <t xml:space="preserve">Hire Wave (Kathy weights)</t>
   </si>
   <si>
     <t xml:space="preserve">Houston, Dallas, Austin</t>
@@ -579,7 +579,7 @@
     <t xml:space="preserve">Greenville, Florence, Spartanburg</t>
   </si>
   <si>
-    <t xml:space="preserve">HARD CAP: 28 reps. Allocation (blue, adjustable — keep the column total at 28): 2 reps each for TX, CA-HI, NY, FL, PA-NJ; 1 rep for 18 territories; 0 reps for T24 IA-SD-ND-WY and T25 SC (unstaffed at the cap). Per-rep loads, Score, Rank, and Hiring Wave figures recalculate. Against the ALL-MD universe (18,405) the 28 reps average ~657 MDs each — use with the &gt;=10 / &gt;=20 tiers on State Market Summary as a prioritization model. Women 25-44 and Wtd Income carried from v3 unchanged (blue = input). Score v4 weights: All MDs 47.06% / All Clinics 29.41% / Women 25-44 11.76% / Income 11.76% (see Read Me). Score does not depend on Reps.</t>
+    <t xml:space="preserve">HARD CAP: 28 reps. Allocation (blue, adjustable — keep the column total at 28): 2 reps each for TX, CA-HI, NY, FL, PA-NJ; 1 rep for 18 territories; 0 reps for T24 IA-SD-ND-WY and T25 SC (unstaffed at the cap). Per-rep loads and dependent figures recalculate. PRIORITIZATION: hiring waves are driven by the Kathy - ALL Universe score/rank (per-rep weights 20/60/10/10); the Score v4 column here (market-size weights, rep-independent) is retained for reference only. Against the ALL-MD universe (18,405) the 28 reps average ~657 MDs each — use with the &gt;=10 / &gt;=20 tiers on State Market Summary as a prioritization model. Women 25-44 and Wtd Income carried from v3 unchanged (blue = input).</t>
   </si>
   <si>
     <t xml:space="preserve">Wave</t>
@@ -600,16 +600,16 @@
     <t xml:space="preserve">Wave 1</t>
   </si>
   <si>
-    <t xml:space="preserve">T02 CA-HI; T01 TX; T03 NY; T06 PA-NJ; T05 FL; T08 MA-CT-NH-ME-VT-RI; T12 WA-OR-AK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Highest v4 opportunity; staff first</t>
+    <t xml:space="preserve">T02 CA-HI; T08 MA-CT-NH-ME-VT-RI; T01 TX; T17 IL; T12 WA-OR-AK; T11 GA; T15 AZ-NV-ID-MT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Highest Kathy-weighted score; staff first</t>
   </si>
   <si>
     <t xml:space="preserve">Wave 2</t>
   </si>
   <si>
-    <t xml:space="preserve">T17 IL; T09 MN-WI; T04 OH; T07 MI; T13 NC</t>
+    <t xml:space="preserve">T07 MI; T03 NY; T09 MN-WI; T04 OH; T13 NC</t>
   </si>
   <si>
     <t xml:space="preserve">Second tier</t>
@@ -618,7 +618,7 @@
     <t xml:space="preserve">Wave 3</t>
   </si>
   <si>
-    <t xml:space="preserve">T11 GA; T15 AZ-NV-ID-MT; T10 MO-KY; T16 CO-UT; T14 KS-OK-NE-NM; T22 MD-WV-DE-DC; T21 VA</t>
+    <t xml:space="preserve">T10 MO-KY; T16 CO-UT; T14 KS-OK-NE-NM; T06 PA-NJ; T22 MD-WV-DE-DC; T21 VA; T19 LA-AR</t>
   </si>
   <si>
     <t xml:space="preserve">Regional completion</t>
@@ -627,16 +627,16 @@
     <t xml:space="preserve">Wave 4</t>
   </si>
   <si>
-    <t xml:space="preserve">T19 LA-AR; T18 AL-MS; T20 IN; T23 TN; T24 IA-SD-ND-WY; T25 SC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full national at the 28 cap</t>
+    <t xml:space="preserve">T18 AL-MS; T05 FL; T23 TN; T20 IN; T24 IA-SD-ND-WY (0 reps); T25 SC (0 reps)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balance of the 28; includes the two unstaffed territories</t>
   </si>
   <si>
     <t xml:space="preserve">CAVEAT: rankings are pure opportunity, not mandate-adjusted. Northeast (incl. mandate states) remains in early waves under v3 weights. Verify the current mandate list (Phase 2) and re-sequence before committing hires.</t>
   </si>
   <si>
-    <t xml:space="preserve">v4 notes: waves ranked by v4 score, wave sizes 7/5/7/6 territories. Rep counts use the hard 28-cap allocation (2 each: TX, CA-HI, NY, FL, PA-NJ; 1 each: 18 territories). Wave 4 lists T24 IA-SD-ND-WY and T25 SC at 0 reps — unstaffed at the cap. Cumulative total = 28.</t>
+    <t xml:space="preserve">v4 notes: waves ranked by the Kathy - ALL Universe score (All MDs/Rep 20% / All Clinics/Rep 60% / Women 25-44 10% / Median Income 10%), wave sizes 7/5/7/6. Rep counts use the hard 28-cap allocation (2 each: TX, CA-HI, NY, FL, PA-NJ; 1 each: 18 territories). Wave 4 lists T24 IA-SD-ND-WY and T25 SC at 0 reps — unstaffed at the cap. Cumulative total = 28. NOTE: because the score weights per-rep load, editing the Reps column re-shuffles ranks and wave membership; the wave lists in column B are a snapshot of the current allocation — re-check after any rep change.</t>
   </si>
   <si>
     <t xml:space="preserve">Kathy - ALL Universe: all counts sum Waterfall A rev1 labeled columns only (via State Market Summary). Reps (J, blue) = the 28-rep hard-cap allocation (2 each: TX, CA-HI, NY, FL, PA-NJ; 1 each: 18 territories; 0: IA-SD-ND-WY, SC) — overwrite freely, keep total 28; per-rep loads, Academic Share, Score, and Rank recalculate. Unstaffed territories show no per-rep figures or score.</t>
@@ -688,6 +688,9 @@
   </si>
   <si>
     <t xml:space="preserve">Rank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hire Wave</t>
   </si>
   <si>
     <t xml:space="preserve">T01 TX</t>
@@ -772,13 +775,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="6">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="\$#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
+    <numFmt numFmtId="170" formatCode="General"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -922,7 +926,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1040,6 +1044,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -5141,7 +5149,7 @@
         <v>-1</v>
       </c>
       <c r="O2" s="7" t="n">
-        <f aca="false">IF(L2&lt;=7,1,IF(L2&lt;=12,2,IF(L2&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S4</f>
         <v>1</v>
       </c>
     </row>
@@ -5196,7 +5204,7 @@
         <v>1</v>
       </c>
       <c r="O3" s="7" t="n">
-        <f aca="false">IF(L3&lt;=7,1,IF(L3&lt;=12,2,IF(L3&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S5</f>
         <v>1</v>
       </c>
     </row>
@@ -5251,8 +5259,8 @@
         <v>0</v>
       </c>
       <c r="O4" s="7" t="n">
-        <f aca="false">IF(L4&lt;=7,1,IF(L4&lt;=12,2,IF(L4&lt;=19,3,4)))</f>
-        <v>1</v>
+        <f aca="false">'Kathy - ALL Universe'!S6</f>
+        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5306,7 +5314,7 @@
         <v>-6</v>
       </c>
       <c r="O5" s="7" t="n">
-        <f aca="false">IF(L5&lt;=7,1,IF(L5&lt;=12,2,IF(L5&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S7</f>
         <v>2</v>
       </c>
     </row>
@@ -5361,8 +5369,8 @@
         <v>0</v>
       </c>
       <c r="O6" s="7" t="n">
-        <f aca="false">IF(L6&lt;=7,1,IF(L6&lt;=12,2,IF(L6&lt;=19,3,4)))</f>
-        <v>1</v>
+        <f aca="false">'Kathy - ALL Universe'!S8</f>
+        <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5416,8 +5424,8 @@
         <v>2</v>
       </c>
       <c r="O7" s="7" t="n">
-        <f aca="false">IF(L7&lt;=7,1,IF(L7&lt;=12,2,IF(L7&lt;=19,3,4)))</f>
-        <v>1</v>
+        <f aca="false">'Kathy - ALL Universe'!S9</f>
+        <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5471,7 +5479,7 @@
         <v>-4</v>
       </c>
       <c r="O8" s="7" t="n">
-        <f aca="false">IF(L8&lt;=7,1,IF(L8&lt;=12,2,IF(L8&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S10</f>
         <v>2</v>
       </c>
     </row>
@@ -5526,7 +5534,7 @@
         <v>2</v>
       </c>
       <c r="O9" s="7" t="n">
-        <f aca="false">IF(L9&lt;=7,1,IF(L9&lt;=12,2,IF(L9&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S11</f>
         <v>1</v>
       </c>
     </row>
@@ -5581,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="7" t="n">
-        <f aca="false">IF(L10&lt;=7,1,IF(L10&lt;=12,2,IF(L10&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S12</f>
         <v>2</v>
       </c>
     </row>
@@ -5636,7 +5644,7 @@
         <v>-5</v>
       </c>
       <c r="O11" s="7" t="n">
-        <f aca="false">IF(L11&lt;=7,1,IF(L11&lt;=12,2,IF(L11&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S13</f>
         <v>3</v>
       </c>
     </row>
@@ -5691,8 +5699,8 @@
         <v>-2</v>
       </c>
       <c r="O12" s="7" t="n">
-        <f aca="false">IF(L12&lt;=7,1,IF(L12&lt;=12,2,IF(L12&lt;=19,3,4)))</f>
-        <v>3</v>
+        <f aca="false">'Kathy - ALL Universe'!S14</f>
+        <v>1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5746,7 +5754,7 @@
         <v>5</v>
       </c>
       <c r="O13" s="7" t="n">
-        <f aca="false">IF(L13&lt;=7,1,IF(L13&lt;=12,2,IF(L13&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S15</f>
         <v>1</v>
       </c>
     </row>
@@ -5801,7 +5809,7 @@
         <v>1</v>
       </c>
       <c r="O14" s="7" t="n">
-        <f aca="false">IF(L14&lt;=7,1,IF(L14&lt;=12,2,IF(L14&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S16</f>
         <v>2</v>
       </c>
     </row>
@@ -5856,7 +5864,7 @@
         <v>-3</v>
       </c>
       <c r="O15" s="7" t="n">
-        <f aca="false">IF(L15&lt;=7,1,IF(L15&lt;=12,2,IF(L15&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S17</f>
         <v>3</v>
       </c>
     </row>
@@ -5911,8 +5919,8 @@
         <v>1</v>
       </c>
       <c r="O16" s="7" t="n">
-        <f aca="false">IF(L16&lt;=7,1,IF(L16&lt;=12,2,IF(L16&lt;=19,3,4)))</f>
-        <v>3</v>
+        <f aca="false">'Kathy - ALL Universe'!S18</f>
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5966,7 +5974,7 @@
         <v>0</v>
       </c>
       <c r="O17" s="7" t="n">
-        <f aca="false">IF(L17&lt;=7,1,IF(L17&lt;=12,2,IF(L17&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S19</f>
         <v>3</v>
       </c>
     </row>
@@ -6021,8 +6029,8 @@
         <v>9</v>
       </c>
       <c r="O18" s="7" t="n">
-        <f aca="false">IF(L18&lt;=7,1,IF(L18&lt;=12,2,IF(L18&lt;=19,3,4)))</f>
-        <v>2</v>
+        <f aca="false">'Kathy - ALL Universe'!S20</f>
+        <v>1</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6076,7 +6084,7 @@
         <v>-3</v>
       </c>
       <c r="O19" s="7" t="n">
-        <f aca="false">IF(L19&lt;=7,1,IF(L19&lt;=12,2,IF(L19&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S21</f>
         <v>4</v>
       </c>
     </row>
@@ -6131,8 +6139,8 @@
         <v>-1</v>
       </c>
       <c r="O20" s="7" t="n">
-        <f aca="false">IF(L20&lt;=7,1,IF(L20&lt;=12,2,IF(L20&lt;=19,3,4)))</f>
-        <v>4</v>
+        <f aca="false">'Kathy - ALL Universe'!S22</f>
+        <v>3</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6186,7 +6194,7 @@
         <v>-2</v>
       </c>
       <c r="O21" s="7" t="n">
-        <f aca="false">IF(L21&lt;=7,1,IF(L21&lt;=12,2,IF(L21&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S23</f>
         <v>4</v>
       </c>
     </row>
@@ -6241,7 +6249,7 @@
         <v>2</v>
       </c>
       <c r="O22" s="7" t="n">
-        <f aca="false">IF(L22&lt;=7,1,IF(L22&lt;=12,2,IF(L22&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S24</f>
         <v>3</v>
       </c>
     </row>
@@ -6296,7 +6304,7 @@
         <v>4</v>
       </c>
       <c r="O23" s="7" t="n">
-        <f aca="false">IF(L23&lt;=7,1,IF(L23&lt;=12,2,IF(L23&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S25</f>
         <v>3</v>
       </c>
     </row>
@@ -6351,7 +6359,7 @@
         <v>0</v>
       </c>
       <c r="O24" s="7" t="n">
-        <f aca="false">IF(L24&lt;=7,1,IF(L24&lt;=12,2,IF(L24&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S26</f>
         <v>4</v>
       </c>
     </row>
@@ -6406,7 +6414,7 @@
         <v>0</v>
       </c>
       <c r="O25" s="7" t="n">
-        <f aca="false">IF(L25&lt;=7,1,IF(L25&lt;=12,2,IF(L25&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S27</f>
         <v>4</v>
       </c>
     </row>
@@ -6461,7 +6469,7 @@
         <v>0</v>
       </c>
       <c r="O26" s="7" t="n">
-        <f aca="false">IF(L26&lt;=7,1,IF(L26&lt;=12,2,IF(L26&lt;=19,3,4)))</f>
+        <f aca="false">'Kathy - ALL Universe'!S28</f>
         <v>4</v>
       </c>
     </row>
@@ -6575,12 +6583,12 @@
         <v>191</v>
       </c>
       <c r="C2" s="8" t="n">
-        <f aca="false">SUMIF('Territory Plan'!$O$2:$O$26,1,'Territory Plan'!$F$2:$F$26)</f>
-        <v>12</v>
+        <f aca="false">SUMIF('Kathy - ALL Universe'!$S$4:$S$28,1,'Kathy - ALL Universe'!$J$4:$J$28)</f>
+        <v>9</v>
       </c>
       <c r="D2" s="8" t="n">
         <f aca="false">SUM($C$2:$C2)</f>
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>192</v>
@@ -6594,12 +6602,12 @@
         <v>194</v>
       </c>
       <c r="C3" s="8" t="n">
-        <f aca="false">SUMIF('Territory Plan'!$O$2:$O$26,2,'Territory Plan'!$F$2:$F$26)</f>
-        <v>5</v>
+        <f aca="false">SUMIF('Kathy - ALL Universe'!$S$4:$S$28,2,'Kathy - ALL Universe'!$J$4:$J$28)</f>
+        <v>6</v>
       </c>
       <c r="D3" s="8" t="n">
         <f aca="false">SUM($C$2:$C3)</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>195</v>
@@ -6613,12 +6621,12 @@
         <v>197</v>
       </c>
       <c r="C4" s="8" t="n">
-        <f aca="false">SUMIF('Territory Plan'!$O$2:$O$26,3,'Territory Plan'!$F$2:$F$26)</f>
-        <v>7</v>
+        <f aca="false">SUMIF('Kathy - ALL Universe'!$S$4:$S$28,3,'Kathy - ALL Universe'!$J$4:$J$28)</f>
+        <v>8</v>
       </c>
       <c r="D4" s="8" t="n">
         <f aca="false">SUM($C$2:$C4)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>198</v>
@@ -6632,8 +6640,8 @@
         <v>200</v>
       </c>
       <c r="C5" s="8" t="n">
-        <f aca="false">SUMIF('Territory Plan'!$O$2:$O$26,4,'Territory Plan'!$F$2:$F$26)</f>
-        <v>4</v>
+        <f aca="false">SUMIF('Kathy - ALL Universe'!$S$4:$S$28,4,'Kathy - ALL Universe'!$J$4:$J$28)</f>
+        <v>5</v>
       </c>
       <c r="D5" s="8" t="n">
         <f aca="false">SUM($C$2:$C5)</f>
@@ -6681,7 +6689,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="E1:R31"/>
+  <dimension ref="E1:S31"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
@@ -6694,6 +6702,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6777,10 +6786,13 @@
       <c r="R3" s="16" t="s">
         <v>220</v>
       </c>
+      <c r="S3" s="16" t="s">
+        <v>221</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E4" s="7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F4" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T01",'State Market Summary'!$B$4:$B$54)</f>
@@ -6830,10 +6842,14 @@
         <f aca="false">IF(J4=0,"n/a",RANK(Q4,$Q$4:$Q$28))</f>
         <v>3</v>
       </c>
+      <c r="S4" s="30" t="n">
+        <f aca="false">IF(J4=0,4,IF(R4&lt;=7,1,IF(R4&lt;=12,2,IF(R4&lt;=19,3,4))))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E5" s="7" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F5" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T02",'State Market Summary'!$B$4:$B$54)</f>
@@ -6883,10 +6899,14 @@
         <f aca="false">IF(J5=0,"n/a",RANK(Q5,$Q$4:$Q$28))</f>
         <v>1</v>
       </c>
+      <c r="S5" s="30" t="n">
+        <f aca="false">IF(J5=0,4,IF(R5&lt;=7,1,IF(R5&lt;=12,2,IF(R5&lt;=19,3,4))))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E6" s="7" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F6" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T03",'State Market Summary'!$B$4:$B$54)</f>
@@ -6936,10 +6956,14 @@
         <f aca="false">IF(J6=0,"n/a",RANK(Q6,$Q$4:$Q$28))</f>
         <v>9</v>
       </c>
+      <c r="S6" s="30" t="n">
+        <f aca="false">IF(J6=0,4,IF(R6&lt;=7,1,IF(R6&lt;=12,2,IF(R6&lt;=19,3,4))))</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E7" s="7" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F7" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T04",'State Market Summary'!$B$4:$B$54)</f>
@@ -6989,10 +7013,14 @@
         <f aca="false">IF(J7=0,"n/a",RANK(Q7,$Q$4:$Q$28))</f>
         <v>11</v>
       </c>
+      <c r="S7" s="30" t="n">
+        <f aca="false">IF(J7=0,4,IF(R7&lt;=7,1,IF(R7&lt;=12,2,IF(R7&lt;=19,3,4))))</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E8" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F8" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T05",'State Market Summary'!$B$4:$B$54)</f>
@@ -7042,10 +7070,14 @@
         <f aca="false">IF(J8=0,"n/a",RANK(Q8,$Q$4:$Q$28))</f>
         <v>21</v>
       </c>
+      <c r="S8" s="30" t="n">
+        <f aca="false">IF(J8=0,4,IF(R8&lt;=7,1,IF(R8&lt;=12,2,IF(R8&lt;=19,3,4))))</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E9" s="7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F9" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T06",'State Market Summary'!$B$4:$B$54)</f>
@@ -7095,10 +7127,14 @@
         <f aca="false">IF(J9=0,"n/a",RANK(Q9,$Q$4:$Q$28))</f>
         <v>16</v>
       </c>
+      <c r="S9" s="30" t="n">
+        <f aca="false">IF(J9=0,4,IF(R9&lt;=7,1,IF(R9&lt;=12,2,IF(R9&lt;=19,3,4))))</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E10" s="7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F10" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T07",'State Market Summary'!$B$4:$B$54)</f>
@@ -7148,10 +7184,14 @@
         <f aca="false">IF(J10=0,"n/a",RANK(Q10,$Q$4:$Q$28))</f>
         <v>8</v>
       </c>
+      <c r="S10" s="30" t="n">
+        <f aca="false">IF(J10=0,4,IF(R10&lt;=7,1,IF(R10&lt;=12,2,IF(R10&lt;=19,3,4))))</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E11" s="7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F11" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T08",'State Market Summary'!$B$4:$B$54)</f>
@@ -7201,10 +7241,14 @@
         <f aca="false">IF(J11=0,"n/a",RANK(Q11,$Q$4:$Q$28))</f>
         <v>2</v>
       </c>
+      <c r="S11" s="30" t="n">
+        <f aca="false">IF(J11=0,4,IF(R11&lt;=7,1,IF(R11&lt;=12,2,IF(R11&lt;=19,3,4))))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E12" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F12" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T09",'State Market Summary'!$B$4:$B$54)</f>
@@ -7254,10 +7298,14 @@
         <f aca="false">IF(J12=0,"n/a",RANK(Q12,$Q$4:$Q$28))</f>
         <v>10</v>
       </c>
+      <c r="S12" s="30" t="n">
+        <f aca="false">IF(J12=0,4,IF(R12&lt;=7,1,IF(R12&lt;=12,2,IF(R12&lt;=19,3,4))))</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E13" s="7" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F13" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T10",'State Market Summary'!$B$4:$B$54)</f>
@@ -7307,10 +7355,14 @@
         <f aca="false">IF(J13=0,"n/a",RANK(Q13,$Q$4:$Q$28))</f>
         <v>13</v>
       </c>
+      <c r="S13" s="30" t="n">
+        <f aca="false">IF(J13=0,4,IF(R13&lt;=7,1,IF(R13&lt;=12,2,IF(R13&lt;=19,3,4))))</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E14" s="7" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="F14" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T11",'State Market Summary'!$B$4:$B$54)</f>
@@ -7360,10 +7412,14 @@
         <f aca="false">IF(J14=0,"n/a",RANK(Q14,$Q$4:$Q$28))</f>
         <v>6</v>
       </c>
+      <c r="S14" s="30" t="n">
+        <f aca="false">IF(J14=0,4,IF(R14&lt;=7,1,IF(R14&lt;=12,2,IF(R14&lt;=19,3,4))))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E15" s="7" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F15" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T12",'State Market Summary'!$B$4:$B$54)</f>
@@ -7413,10 +7469,14 @@
         <f aca="false">IF(J15=0,"n/a",RANK(Q15,$Q$4:$Q$28))</f>
         <v>5</v>
       </c>
+      <c r="S15" s="30" t="n">
+        <f aca="false">IF(J15=0,4,IF(R15&lt;=7,1,IF(R15&lt;=12,2,IF(R15&lt;=19,3,4))))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E16" s="7" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F16" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T13",'State Market Summary'!$B$4:$B$54)</f>
@@ -7466,10 +7526,14 @@
         <f aca="false">IF(J16=0,"n/a",RANK(Q16,$Q$4:$Q$28))</f>
         <v>12</v>
       </c>
+      <c r="S16" s="30" t="n">
+        <f aca="false">IF(J16=0,4,IF(R16&lt;=7,1,IF(R16&lt;=12,2,IF(R16&lt;=19,3,4))))</f>
+        <v>2</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E17" s="7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F17" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T14",'State Market Summary'!$B$4:$B$54)</f>
@@ -7519,10 +7583,14 @@
         <f aca="false">IF(J17=0,"n/a",RANK(Q17,$Q$4:$Q$28))</f>
         <v>15</v>
       </c>
+      <c r="S17" s="30" t="n">
+        <f aca="false">IF(J17=0,4,IF(R17&lt;=7,1,IF(R17&lt;=12,2,IF(R17&lt;=19,3,4))))</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E18" s="7" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F18" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T15",'State Market Summary'!$B$4:$B$54)</f>
@@ -7572,10 +7640,14 @@
         <f aca="false">IF(J18=0,"n/a",RANK(Q18,$Q$4:$Q$28))</f>
         <v>7</v>
       </c>
+      <c r="S18" s="30" t="n">
+        <f aca="false">IF(J18=0,4,IF(R18&lt;=7,1,IF(R18&lt;=12,2,IF(R18&lt;=19,3,4))))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E19" s="7" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F19" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T16",'State Market Summary'!$B$4:$B$54)</f>
@@ -7625,10 +7697,14 @@
         <f aca="false">IF(J19=0,"n/a",RANK(Q19,$Q$4:$Q$28))</f>
         <v>14</v>
       </c>
+      <c r="S19" s="30" t="n">
+        <f aca="false">IF(J19=0,4,IF(R19&lt;=7,1,IF(R19&lt;=12,2,IF(R19&lt;=19,3,4))))</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E20" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F20" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T17",'State Market Summary'!$B$4:$B$54)</f>
@@ -7678,10 +7754,14 @@
         <f aca="false">IF(J20=0,"n/a",RANK(Q20,$Q$4:$Q$28))</f>
         <v>4</v>
       </c>
+      <c r="S20" s="30" t="n">
+        <f aca="false">IF(J20=0,4,IF(R20&lt;=7,1,IF(R20&lt;=12,2,IF(R20&lt;=19,3,4))))</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E21" s="7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F21" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T18",'State Market Summary'!$B$4:$B$54)</f>
@@ -7731,10 +7811,14 @@
         <f aca="false">IF(J21=0,"n/a",RANK(Q21,$Q$4:$Q$28))</f>
         <v>20</v>
       </c>
+      <c r="S21" s="30" t="n">
+        <f aca="false">IF(J21=0,4,IF(R21&lt;=7,1,IF(R21&lt;=12,2,IF(R21&lt;=19,3,4))))</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E22" s="7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F22" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T19",'State Market Summary'!$B$4:$B$54)</f>
@@ -7784,10 +7868,14 @@
         <f aca="false">IF(J22=0,"n/a",RANK(Q22,$Q$4:$Q$28))</f>
         <v>19</v>
       </c>
+      <c r="S22" s="30" t="n">
+        <f aca="false">IF(J22=0,4,IF(R22&lt;=7,1,IF(R22&lt;=12,2,IF(R22&lt;=19,3,4))))</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E23" s="7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F23" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T20",'State Market Summary'!$B$4:$B$54)</f>
@@ -7837,10 +7925,14 @@
         <f aca="false">IF(J23=0,"n/a",RANK(Q23,$Q$4:$Q$28))</f>
         <v>23</v>
       </c>
+      <c r="S23" s="30" t="n">
+        <f aca="false">IF(J23=0,4,IF(R23&lt;=7,1,IF(R23&lt;=12,2,IF(R23&lt;=19,3,4))))</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E24" s="7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="F24" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T21",'State Market Summary'!$B$4:$B$54)</f>
@@ -7890,10 +7982,14 @@
         <f aca="false">IF(J24=0,"n/a",RANK(Q24,$Q$4:$Q$28))</f>
         <v>18</v>
       </c>
+      <c r="S24" s="30" t="n">
+        <f aca="false">IF(J24=0,4,IF(R24&lt;=7,1,IF(R24&lt;=12,2,IF(R24&lt;=19,3,4))))</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E25" s="7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F25" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T22",'State Market Summary'!$B$4:$B$54)</f>
@@ -7943,10 +8039,14 @@
         <f aca="false">IF(J25=0,"n/a",RANK(Q25,$Q$4:$Q$28))</f>
         <v>17</v>
       </c>
+      <c r="S25" s="30" t="n">
+        <f aca="false">IF(J25=0,4,IF(R25&lt;=7,1,IF(R25&lt;=12,2,IF(R25&lt;=19,3,4))))</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E26" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F26" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T23",'State Market Summary'!$B$4:$B$54)</f>
@@ -7996,10 +8096,14 @@
         <f aca="false">IF(J26=0,"n/a",RANK(Q26,$Q$4:$Q$28))</f>
         <v>22</v>
       </c>
+      <c r="S26" s="30" t="n">
+        <f aca="false">IF(J26=0,4,IF(R26&lt;=7,1,IF(R26&lt;=12,2,IF(R26&lt;=19,3,4))))</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E27" s="7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="F27" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T24",'State Market Summary'!$B$4:$B$54)</f>
@@ -8049,10 +8153,14 @@
         <f aca="false">IF(J27=0,"n/a",RANK(Q27,$Q$4:$Q$28))</f>
         <v>n/a</v>
       </c>
+      <c r="S27" s="30" t="n">
+        <f aca="false">IF(J27=0,4,IF(R27&lt;=7,1,IF(R27&lt;=12,2,IF(R27&lt;=19,3,4))))</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E28" s="7" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F28" s="8" t="n">
         <f aca="false">SUMIF('State Market Summary'!$T$4:$T$54,"T25",'State Market Summary'!$B$4:$B$54)</f>
@@ -8102,6 +8210,10 @@
         <f aca="false">IF(J28=0,"n/a",RANK(Q28,$Q$4:$Q$28))</f>
         <v>n/a</v>
       </c>
+      <c r="S28" s="30" t="n">
+        <f aca="false">IF(J28=0,4,IF(R28&lt;=7,1,IF(R28&lt;=12,2,IF(R28&lt;=19,3,4))))</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E29" s="22" t="s">
@@ -8135,7 +8247,7 @@
         <f aca="false">ROUND(G29/J29,1)</f>
         <v>209.4</v>
       </c>
-      <c r="M29" s="30" t="n">
+      <c r="M29" s="31" t="n">
         <f aca="false">H29/F29</f>
         <v>0.414561260527031</v>
       </c>
@@ -8147,7 +8259,7 @@
     </row>
     <row r="31" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="E31" s="9" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F31" s="9"/>
       <c r="G31" s="9"/>

--- a/docs/deliverables/Femasys_Territory_Plan_v4.xlsx
+++ b/docs/deliverables/Femasys_Territory_Plan_v4.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="249">
   <si>
     <t xml:space="preserve">FemaSeed U.S. Territory Plan — v4 (ALL-MD Universe, 28-Rep Hard Cap)</t>
   </si>
@@ -769,20 +769,22 @@
   </si>
   <si>
     <t xml:space="preserve">Score = min-max normalization (0-100 across staffed territories) of All MDs/Rep (20%), All Clinics/Rep (60%), Women 25-44 (10%), Median Income (10%); Education 0% (displayed, not scored). Blue cells are inputs: Reps carries the 28-rep hard-cap allocation; Women 25-44 / Median Income / Education carried from v3 Territory Plan unchanged (v3 census data-quality caveats apply). All MD/clinic counts (F-I) are sums of member states from Waterfall A rev1 labeled columns only; stray unlabeled scratch columns in the source were excluded.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACADEMIC SHARE (column M) = All Academic/Group MDs / All MDs (column H / column F), both summed from Waterfall A rev1. It is the percent of a territory's total physician universe practicing in academic, hospital/system, or MSO-affiliated group settings versus private practice. Classification per the Data Request waterfall method: CMS facility IDs, hospital/system/university name tokens, and MSO rosters (incl. Unified Women's Healthcare, Axia, Privia, Pediatrix). National benchmark: 7,630 / 18,405 = 41.5%. Display only (0% score weight) - shown because access and selling motion differ materially between academic/group and private accounts. Note: metro-level academic splits are not available for the full ALL-MD universe (no row-level data exists below volume 10); metro detail is available only for the &gt;=10 tier.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0.0"/>
     <numFmt numFmtId="167" formatCode="\$#,##0"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
-    <numFmt numFmtId="170" formatCode="General"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -926,7 +928,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1044,10 +1046,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="168" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6689,7 +6687,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="E1:S31"/>
+  <dimension ref="E1:S33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="20"/>
@@ -6702,7 +6700,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="8"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6842,7 +6840,7 @@
         <f aca="false">IF(J4=0,"n/a",RANK(Q4,$Q$4:$Q$28))</f>
         <v>3</v>
       </c>
-      <c r="S4" s="30" t="n">
+      <c r="S4" s="7" t="n">
         <f aca="false">IF(J4=0,4,IF(R4&lt;=7,1,IF(R4&lt;=12,2,IF(R4&lt;=19,3,4))))</f>
         <v>1</v>
       </c>
@@ -6899,7 +6897,7 @@
         <f aca="false">IF(J5=0,"n/a",RANK(Q5,$Q$4:$Q$28))</f>
         <v>1</v>
       </c>
-      <c r="S5" s="30" t="n">
+      <c r="S5" s="7" t="n">
         <f aca="false">IF(J5=0,4,IF(R5&lt;=7,1,IF(R5&lt;=12,2,IF(R5&lt;=19,3,4))))</f>
         <v>1</v>
       </c>
@@ -6956,7 +6954,7 @@
         <f aca="false">IF(J6=0,"n/a",RANK(Q6,$Q$4:$Q$28))</f>
         <v>9</v>
       </c>
-      <c r="S6" s="30" t="n">
+      <c r="S6" s="7" t="n">
         <f aca="false">IF(J6=0,4,IF(R6&lt;=7,1,IF(R6&lt;=12,2,IF(R6&lt;=19,3,4))))</f>
         <v>2</v>
       </c>
@@ -7013,7 +7011,7 @@
         <f aca="false">IF(J7=0,"n/a",RANK(Q7,$Q$4:$Q$28))</f>
         <v>11</v>
       </c>
-      <c r="S7" s="30" t="n">
+      <c r="S7" s="7" t="n">
         <f aca="false">IF(J7=0,4,IF(R7&lt;=7,1,IF(R7&lt;=12,2,IF(R7&lt;=19,3,4))))</f>
         <v>2</v>
       </c>
@@ -7070,7 +7068,7 @@
         <f aca="false">IF(J8=0,"n/a",RANK(Q8,$Q$4:$Q$28))</f>
         <v>21</v>
       </c>
-      <c r="S8" s="30" t="n">
+      <c r="S8" s="7" t="n">
         <f aca="false">IF(J8=0,4,IF(R8&lt;=7,1,IF(R8&lt;=12,2,IF(R8&lt;=19,3,4))))</f>
         <v>4</v>
       </c>
@@ -7127,7 +7125,7 @@
         <f aca="false">IF(J9=0,"n/a",RANK(Q9,$Q$4:$Q$28))</f>
         <v>16</v>
       </c>
-      <c r="S9" s="30" t="n">
+      <c r="S9" s="7" t="n">
         <f aca="false">IF(J9=0,4,IF(R9&lt;=7,1,IF(R9&lt;=12,2,IF(R9&lt;=19,3,4))))</f>
         <v>3</v>
       </c>
@@ -7184,7 +7182,7 @@
         <f aca="false">IF(J10=0,"n/a",RANK(Q10,$Q$4:$Q$28))</f>
         <v>8</v>
       </c>
-      <c r="S10" s="30" t="n">
+      <c r="S10" s="7" t="n">
         <f aca="false">IF(J10=0,4,IF(R10&lt;=7,1,IF(R10&lt;=12,2,IF(R10&lt;=19,3,4))))</f>
         <v>2</v>
       </c>
@@ -7241,7 +7239,7 @@
         <f aca="false">IF(J11=0,"n/a",RANK(Q11,$Q$4:$Q$28))</f>
         <v>2</v>
       </c>
-      <c r="S11" s="30" t="n">
+      <c r="S11" s="7" t="n">
         <f aca="false">IF(J11=0,4,IF(R11&lt;=7,1,IF(R11&lt;=12,2,IF(R11&lt;=19,3,4))))</f>
         <v>1</v>
       </c>
@@ -7298,7 +7296,7 @@
         <f aca="false">IF(J12=0,"n/a",RANK(Q12,$Q$4:$Q$28))</f>
         <v>10</v>
       </c>
-      <c r="S12" s="30" t="n">
+      <c r="S12" s="7" t="n">
         <f aca="false">IF(J12=0,4,IF(R12&lt;=7,1,IF(R12&lt;=12,2,IF(R12&lt;=19,3,4))))</f>
         <v>2</v>
       </c>
@@ -7355,7 +7353,7 @@
         <f aca="false">IF(J13=0,"n/a",RANK(Q13,$Q$4:$Q$28))</f>
         <v>13</v>
       </c>
-      <c r="S13" s="30" t="n">
+      <c r="S13" s="7" t="n">
         <f aca="false">IF(J13=0,4,IF(R13&lt;=7,1,IF(R13&lt;=12,2,IF(R13&lt;=19,3,4))))</f>
         <v>3</v>
       </c>
@@ -7412,7 +7410,7 @@
         <f aca="false">IF(J14=0,"n/a",RANK(Q14,$Q$4:$Q$28))</f>
         <v>6</v>
       </c>
-      <c r="S14" s="30" t="n">
+      <c r="S14" s="7" t="n">
         <f aca="false">IF(J14=0,4,IF(R14&lt;=7,1,IF(R14&lt;=12,2,IF(R14&lt;=19,3,4))))</f>
         <v>1</v>
       </c>
@@ -7469,7 +7467,7 @@
         <f aca="false">IF(J15=0,"n/a",RANK(Q15,$Q$4:$Q$28))</f>
         <v>5</v>
       </c>
-      <c r="S15" s="30" t="n">
+      <c r="S15" s="7" t="n">
         <f aca="false">IF(J15=0,4,IF(R15&lt;=7,1,IF(R15&lt;=12,2,IF(R15&lt;=19,3,4))))</f>
         <v>1</v>
       </c>
@@ -7526,7 +7524,7 @@
         <f aca="false">IF(J16=0,"n/a",RANK(Q16,$Q$4:$Q$28))</f>
         <v>12</v>
       </c>
-      <c r="S16" s="30" t="n">
+      <c r="S16" s="7" t="n">
         <f aca="false">IF(J16=0,4,IF(R16&lt;=7,1,IF(R16&lt;=12,2,IF(R16&lt;=19,3,4))))</f>
         <v>2</v>
       </c>
@@ -7583,7 +7581,7 @@
         <f aca="false">IF(J17=0,"n/a",RANK(Q17,$Q$4:$Q$28))</f>
         <v>15</v>
       </c>
-      <c r="S17" s="30" t="n">
+      <c r="S17" s="7" t="n">
         <f aca="false">IF(J17=0,4,IF(R17&lt;=7,1,IF(R17&lt;=12,2,IF(R17&lt;=19,3,4))))</f>
         <v>3</v>
       </c>
@@ -7640,7 +7638,7 @@
         <f aca="false">IF(J18=0,"n/a",RANK(Q18,$Q$4:$Q$28))</f>
         <v>7</v>
       </c>
-      <c r="S18" s="30" t="n">
+      <c r="S18" s="7" t="n">
         <f aca="false">IF(J18=0,4,IF(R18&lt;=7,1,IF(R18&lt;=12,2,IF(R18&lt;=19,3,4))))</f>
         <v>1</v>
       </c>
@@ -7697,7 +7695,7 @@
         <f aca="false">IF(J19=0,"n/a",RANK(Q19,$Q$4:$Q$28))</f>
         <v>14</v>
       </c>
-      <c r="S19" s="30" t="n">
+      <c r="S19" s="7" t="n">
         <f aca="false">IF(J19=0,4,IF(R19&lt;=7,1,IF(R19&lt;=12,2,IF(R19&lt;=19,3,4))))</f>
         <v>3</v>
       </c>
@@ -7754,7 +7752,7 @@
         <f aca="false">IF(J20=0,"n/a",RANK(Q20,$Q$4:$Q$28))</f>
         <v>4</v>
       </c>
-      <c r="S20" s="30" t="n">
+      <c r="S20" s="7" t="n">
         <f aca="false">IF(J20=0,4,IF(R20&lt;=7,1,IF(R20&lt;=12,2,IF(R20&lt;=19,3,4))))</f>
         <v>1</v>
       </c>
@@ -7811,7 +7809,7 @@
         <f aca="false">IF(J21=0,"n/a",RANK(Q21,$Q$4:$Q$28))</f>
         <v>20</v>
       </c>
-      <c r="S21" s="30" t="n">
+      <c r="S21" s="7" t="n">
         <f aca="false">IF(J21=0,4,IF(R21&lt;=7,1,IF(R21&lt;=12,2,IF(R21&lt;=19,3,4))))</f>
         <v>4</v>
       </c>
@@ -7868,7 +7866,7 @@
         <f aca="false">IF(J22=0,"n/a",RANK(Q22,$Q$4:$Q$28))</f>
         <v>19</v>
       </c>
-      <c r="S22" s="30" t="n">
+      <c r="S22" s="7" t="n">
         <f aca="false">IF(J22=0,4,IF(R22&lt;=7,1,IF(R22&lt;=12,2,IF(R22&lt;=19,3,4))))</f>
         <v>3</v>
       </c>
@@ -7925,7 +7923,7 @@
         <f aca="false">IF(J23=0,"n/a",RANK(Q23,$Q$4:$Q$28))</f>
         <v>23</v>
       </c>
-      <c r="S23" s="30" t="n">
+      <c r="S23" s="7" t="n">
         <f aca="false">IF(J23=0,4,IF(R23&lt;=7,1,IF(R23&lt;=12,2,IF(R23&lt;=19,3,4))))</f>
         <v>4</v>
       </c>
@@ -7982,7 +7980,7 @@
         <f aca="false">IF(J24=0,"n/a",RANK(Q24,$Q$4:$Q$28))</f>
         <v>18</v>
       </c>
-      <c r="S24" s="30" t="n">
+      <c r="S24" s="7" t="n">
         <f aca="false">IF(J24=0,4,IF(R24&lt;=7,1,IF(R24&lt;=12,2,IF(R24&lt;=19,3,4))))</f>
         <v>3</v>
       </c>
@@ -8039,7 +8037,7 @@
         <f aca="false">IF(J25=0,"n/a",RANK(Q25,$Q$4:$Q$28))</f>
         <v>17</v>
       </c>
-      <c r="S25" s="30" t="n">
+      <c r="S25" s="7" t="n">
         <f aca="false">IF(J25=0,4,IF(R25&lt;=7,1,IF(R25&lt;=12,2,IF(R25&lt;=19,3,4))))</f>
         <v>3</v>
       </c>
@@ -8096,7 +8094,7 @@
         <f aca="false">IF(J26=0,"n/a",RANK(Q26,$Q$4:$Q$28))</f>
         <v>22</v>
       </c>
-      <c r="S26" s="30" t="n">
+      <c r="S26" s="7" t="n">
         <f aca="false">IF(J26=0,4,IF(R26&lt;=7,1,IF(R26&lt;=12,2,IF(R26&lt;=19,3,4))))</f>
         <v>4</v>
       </c>
@@ -8153,7 +8151,7 @@
         <f aca="false">IF(J27=0,"n/a",RANK(Q27,$Q$4:$Q$28))</f>
         <v>n/a</v>
       </c>
-      <c r="S27" s="30" t="n">
+      <c r="S27" s="7" t="n">
         <f aca="false">IF(J27=0,4,IF(R27&lt;=7,1,IF(R27&lt;=12,2,IF(R27&lt;=19,3,4))))</f>
         <v>4</v>
       </c>
@@ -8210,7 +8208,7 @@
         <f aca="false">IF(J28=0,"n/a",RANK(Q28,$Q$4:$Q$28))</f>
         <v>n/a</v>
       </c>
-      <c r="S28" s="30" t="n">
+      <c r="S28" s="7" t="n">
         <f aca="false">IF(J28=0,4,IF(R28&lt;=7,1,IF(R28&lt;=12,2,IF(R28&lt;=19,3,4))))</f>
         <v>4</v>
       </c>
@@ -8247,7 +8245,7 @@
         <f aca="false">ROUND(G29/J29,1)</f>
         <v>209.4</v>
       </c>
-      <c r="M29" s="31" t="n">
+      <c r="M29" s="30" t="n">
         <f aca="false">H29/F29</f>
         <v>0.414561260527031</v>
       </c>
@@ -8275,10 +8273,29 @@
       <c r="Q31" s="9"/>
       <c r="R31" s="9"/>
     </row>
+    <row r="33" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E33" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+      <c r="M33" s="9"/>
+      <c r="N33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="P33" s="9"/>
+      <c r="Q33" s="9"/>
+      <c r="R33" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="E1:R1"/>
     <mergeCell ref="E31:R31"/>
+    <mergeCell ref="E33:R33"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
